--- a/Rescatables20231.xlsx
+++ b/Rescatables20231.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1694" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="499">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -144,18 +144,12 @@
     <t>Lengua y comunicación I</t>
   </si>
   <si>
-    <t>ECHAVARRIA</t>
-  </si>
-  <si>
     <t>LOBATO</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>DURAND</t>
-  </si>
-  <si>
     <t>HUERTA</t>
   </si>
   <si>
@@ -168,9 +162,6 @@
     <t>SOLANO</t>
   </si>
   <si>
-    <t>KEVIN SANTIAGO</t>
-  </si>
-  <si>
     <t>JOSE LUIS</t>
   </si>
   <si>
@@ -429,6 +420,9 @@
     <t>TETLA</t>
   </si>
   <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
     <t>CORREA</t>
   </si>
   <si>
@@ -459,6 +453,9 @@
     <t>SALMA JANET</t>
   </si>
   <si>
+    <t>VICTOR JESUS</t>
+  </si>
+  <si>
     <t>KAORY AYELEN</t>
   </si>
   <si>
@@ -561,9 +558,6 @@
     <t>ORTEGA</t>
   </si>
   <si>
-    <t>AVALOS</t>
-  </si>
-  <si>
     <t>LEON</t>
   </si>
   <si>
@@ -579,9 +573,6 @@
     <t>JESUS EMMANUEL</t>
   </si>
   <si>
-    <t>GIOVANNI</t>
-  </si>
-  <si>
     <t>TONALLI</t>
   </si>
   <si>
@@ -606,6 +597,9 @@
     <t>VELAZQUEZ</t>
   </si>
   <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
     <t>AYOHUA</t>
   </si>
   <si>
@@ -624,9 +618,6 @@
     <t>CARRASCO</t>
   </si>
   <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
     <t>JOSE MANUEL</t>
   </si>
   <si>
@@ -657,6 +648,9 @@
     <t>JOSE MIGUEL</t>
   </si>
   <si>
+    <t>CLAUDIA PAOLA</t>
+  </si>
+  <si>
     <t>FRANCISCO JAVIER</t>
   </si>
   <si>
@@ -717,807 +711,744 @@
     <t>PELLICO</t>
   </si>
   <si>
+    <t>PIÑA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>ODALIS SOFIA</t>
+  </si>
+  <si>
+    <t>KARENT LILIANA</t>
+  </si>
+  <si>
+    <t>ABIGAIL ANTONIA</t>
+  </si>
+  <si>
+    <t>ZURI GABRIELA</t>
+  </si>
+  <si>
+    <t>LUISA MARIA</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS BACTERIOLÓGICAS</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>LOYO</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>MAYO</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>NERI</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>AYLIN MELISSA</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>LUIS OMAR</t>
+  </si>
+  <si>
+    <t>CHARBEL</t>
+  </si>
+  <si>
+    <t>CANDIDO</t>
+  </si>
+  <si>
+    <t>CÁLCULO INTEGRAL</t>
+  </si>
+  <si>
+    <t>CIENCIA, TECNOLOGÍA, SOCIEDAD Y VALORES</t>
+  </si>
+  <si>
+    <t>FÍSICA II</t>
+  </si>
+  <si>
+    <t>DISEÑA Y MANTIENE LOS SISTEMAS DE ILUMINACIÓN</t>
+  </si>
+  <si>
+    <t>ARGÜELLO</t>
+  </si>
+  <si>
+    <t>VENEGAS</t>
+  </si>
+  <si>
+    <t>NARANJO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>AMECA</t>
+  </si>
+  <si>
+    <t>ESTEFANIA</t>
+  </si>
+  <si>
+    <t>ATZIN HEFZIBA</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>EZEQUIEL</t>
+  </si>
+  <si>
+    <t>ABAD</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>INGLÉS V</t>
+  </si>
+  <si>
+    <t>TEHUINTLE</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
+    <t>LIZBETH JOSELYN</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>GETSEMANI GUADALUPE</t>
+  </si>
+  <si>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>ALEMAN</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>CUICAHUA</t>
+  </si>
+  <si>
+    <t>CHRISTIAN YAIR</t>
+  </si>
+  <si>
+    <t>JORGE GUILLERMO</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>DIEGO HUMBERTO</t>
+  </si>
+  <si>
+    <t>ZURIEL ELIHU</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>DARINKA</t>
+  </si>
+  <si>
+    <t>IMPLEMENTA Y MANTIENE LOS SISTEMAS DE ENERGÍA RENOVABLE</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>MONGE</t>
+  </si>
+  <si>
+    <t>NAHOMY</t>
+  </si>
+  <si>
+    <t>JOSE RAFAEL</t>
+  </si>
+  <si>
+    <t>YAMILET MONSERRAT</t>
+  </si>
+  <si>
+    <t>DIANA CRISTINA</t>
+  </si>
+  <si>
+    <t>ANA LAURA</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
+  </si>
+  <si>
+    <t>IVANNA DANIELA</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>BUSTOS</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>DAMIAN</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>AUTRAN</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>JOSE EMILIANO</t>
+  </si>
+  <si>
+    <t>JESUS JAREF</t>
+  </si>
+  <si>
+    <t>NATANAHEL</t>
+  </si>
+  <si>
+    <t>AXEL AARON</t>
+  </si>
+  <si>
+    <t>LUIS FABIAN</t>
+  </si>
+  <si>
+    <t>ALEX URIEL</t>
+  </si>
+  <si>
+    <t>SABDY</t>
+  </si>
+  <si>
+    <t>Pensamiento matemático I</t>
+  </si>
+  <si>
+    <t>CALVA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>PIÑA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>ODALIS SOFIA</t>
-  </si>
-  <si>
-    <t>KARENT LILIANA</t>
-  </si>
-  <si>
-    <t>KARINA</t>
-  </si>
-  <si>
-    <t>MELISA VIANNEY</t>
-  </si>
-  <si>
-    <t>JOSE ALBIN</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>NORMA ANGELICA</t>
-  </si>
-  <si>
-    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS BACTERIOLÓGICAS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>LOYO</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>MAYO</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>NERI</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>AYLIN MELISSA</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>LUIS OMAR</t>
-  </si>
-  <si>
-    <t>CHARBEL</t>
-  </si>
-  <si>
-    <t>CANDIDO</t>
-  </si>
-  <si>
-    <t>CÁLCULO INTEGRAL</t>
-  </si>
-  <si>
-    <t>CIENCIA, TECNOLOGÍA, SOCIEDAD Y VALORES</t>
-  </si>
-  <si>
-    <t>FÍSICA II</t>
-  </si>
-  <si>
-    <t>DISEÑA Y MANTIENE LOS SISTEMAS DE ILUMINACIÓN</t>
-  </si>
-  <si>
-    <t>ARGÜELLO</t>
-  </si>
-  <si>
-    <t>VENEGAS</t>
-  </si>
-  <si>
-    <t>NARANJO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>AMECA</t>
-  </si>
-  <si>
-    <t>ESTEFANIA</t>
-  </si>
-  <si>
-    <t>ATZIN HEFZIBA</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>EZEQUIEL</t>
-  </si>
-  <si>
-    <t>ABAD</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>INGLÉS V</t>
-  </si>
-  <si>
-    <t>ZACAMECAHUA</t>
-  </si>
-  <si>
-    <t>MADRIGAL</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>MARES</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>HARUMI</t>
-  </si>
-  <si>
-    <t>ALONDRA VANNESSA</t>
-  </si>
-  <si>
-    <t>LIZBETH JOSELYN</t>
-  </si>
-  <si>
-    <t>AMERICA PAOLA</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>GETSEMANI GUADALUPE</t>
-  </si>
-  <si>
-    <t>NUBE</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>ALEMAN</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>CUICAHUA</t>
-  </si>
-  <si>
-    <t>CHRISTIAN YAIR</t>
-  </si>
-  <si>
-    <t>JORGE GUILLERMO</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>DIEGO HUMBERTO</t>
-  </si>
-  <si>
-    <t>ZURIEL ELIHU</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>DARINKA</t>
-  </si>
-  <si>
-    <t>IMPLEMENTA Y MANTIENE LOS SISTEMAS DE ENERGÍA RENOVABLE</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>NAHOMY</t>
-  </si>
-  <si>
-    <t>JOSE RAFAEL</t>
-  </si>
-  <si>
-    <t>YAMILET MONSERRAT</t>
-  </si>
-  <si>
-    <t>DIANA CRISTINA</t>
-  </si>
-  <si>
-    <t>SAYURI BETSABE</t>
-  </si>
-  <si>
-    <t>ANA LAURA</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>IVANNA DANIELA</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>BUSTOS</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>AUTRAN</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>JOSE EMILIANO</t>
-  </si>
-  <si>
-    <t>JESUS JAREF</t>
-  </si>
-  <si>
-    <t>NATANAHEL</t>
-  </si>
-  <si>
-    <t>AXEL AARON</t>
-  </si>
-  <si>
-    <t>LUIS FABIAN</t>
-  </si>
-  <si>
-    <t>ALEX URIEL</t>
-  </si>
-  <si>
-    <t>SABDY</t>
-  </si>
-  <si>
-    <t>Pensamiento matemático I</t>
-  </si>
-  <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
     <t>ZACARIAS</t>
   </si>
   <si>
-    <t>MOSCOSO</t>
-  </si>
-  <si>
     <t>BERMUDEZ</t>
   </si>
   <si>
     <t>FERRER</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
     <t>MONTERROSAS</t>
   </si>
   <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>DORIAN</t>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>YAMILETH</t>
+  </si>
+  <si>
+    <t>INGRID ISABEL</t>
+  </si>
+  <si>
+    <t>VANESA</t>
+  </si>
+  <si>
+    <t>VALERY MIRANDA</t>
+  </si>
+  <si>
+    <t>LUZ YESENIA</t>
+  </si>
+  <si>
+    <t>MIGUEL ENRIQUE</t>
+  </si>
+  <si>
+    <t>ANEL</t>
+  </si>
+  <si>
+    <t>VICTORIA VIANNEY</t>
+  </si>
+  <si>
+    <t>ANGEL ABRAHAM</t>
+  </si>
+  <si>
+    <t>GISELA GUADALUPE</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>Inglés I</t>
+  </si>
+  <si>
+    <t>ALMANZA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CUAPIO</t>
+  </si>
+  <si>
+    <t>DORANTES</t>
+  </si>
+  <si>
+    <t>GILES</t>
+  </si>
+  <si>
+    <t>LAGUNA</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>MACUIXTLE</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>FIGUEROA</t>
+  </si>
+  <si>
+    <t>NATH</t>
+  </si>
+  <si>
+    <t>MONDRAGON</t>
+  </si>
+  <si>
+    <t>VANESA BETHSABE</t>
+  </si>
+  <si>
+    <t>RAMSES</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>JAIRO</t>
+  </si>
+  <si>
+    <t>ALEXA YAMILET</t>
+  </si>
+  <si>
+    <t>AARON ZACHARY</t>
+  </si>
+  <si>
+    <t>DIEGO GREGORIO</t>
+  </si>
+  <si>
+    <t>ANGEL ADRIAN</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>GARZA</t>
+  </si>
+  <si>
+    <t>MICHEL LEONEL</t>
+  </si>
+  <si>
+    <t>JESHUA</t>
+  </si>
+  <si>
+    <t>HUGO ANTONIO</t>
+  </si>
+  <si>
+    <t>IVETTE</t>
+  </si>
+  <si>
+    <t>JENNYFER ARIANA</t>
+  </si>
+  <si>
+    <t>AARON</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>ANA ISABEL</t>
+  </si>
+  <si>
+    <t>NOHEMI ANGELICA</t>
+  </si>
+  <si>
+    <t>ESTEBAN</t>
+  </si>
+  <si>
+    <t>COBOS</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>TIZA</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>ALEXIS YAIR</t>
+  </si>
+  <si>
+    <t>YOLET</t>
+  </si>
+  <si>
+    <t>PATRICIO</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>ERIK OMAR</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>NAHUM HIRAM</t>
+  </si>
+  <si>
+    <t>ERIK</t>
+  </si>
+  <si>
+    <t>JOSUE GUSTAVO</t>
+  </si>
+  <si>
+    <t>CRISTIAN OSMAR</t>
+  </si>
+  <si>
+    <t>OSMAR</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
+  </si>
+  <si>
+    <t>FABIAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>MANTIENE LOS GENERADORES DE CA Y CC</t>
+  </si>
+  <si>
+    <t>MANTIENE LOS MOTORES DE CA Y CC</t>
+  </si>
+  <si>
+    <t>DECTOR</t>
+  </si>
+  <si>
+    <t>ESCOBAR</t>
+  </si>
+  <si>
+    <t>MENA</t>
+  </si>
+  <si>
+    <t>TETLACTLE</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>KEVIN ALEXIS</t>
+  </si>
+  <si>
+    <t>LUZ ALONDRA</t>
+  </si>
+  <si>
+    <t>AMALIA PAULINA</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>BRENDA JANELY</t>
+  </si>
+  <si>
+    <t>JARET</t>
+  </si>
+  <si>
+    <t>AILYN</t>
+  </si>
+  <si>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>OSCAR</t>
+  </si>
+  <si>
+    <t>ABRAHAM</t>
+  </si>
+  <si>
+    <t>JONATAN GILBERTO</t>
+  </si>
+  <si>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>ESMERALDA</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>EMILIANO GERARDO</t>
+  </si>
+  <si>
+    <t>EVELYN ROSALIA</t>
+  </si>
+  <si>
+    <t>REALIZA EL PROCESO DE ADMISIÓN Y EMPLEO</t>
+  </si>
+  <si>
+    <t>CONTRIBUYE A LA INTEGRACIÓN Y DESARROLLO DEL PERSONAL EN LA ORGANIZACIÓN</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>JOSE CARMELO</t>
+  </si>
+  <si>
+    <t>GAMALIEL</t>
+  </si>
+  <si>
+    <t>GUILLERMO ALEXANDER</t>
+  </si>
+  <si>
+    <t>REALIZA MANTENIMIENTO CORRECTIVO</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>NAZARIO</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>DULIAM</t>
+  </si>
+  <si>
+    <t>ELI ANTONIO</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
+    <t>LUIS EDUARDO</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
+  </si>
+  <si>
+    <t>VICTOR ISRAEL</t>
+  </si>
+  <si>
+    <t>NEMESIO NAHIM</t>
+  </si>
+  <si>
+    <t>REALIZA MANTENIMIENTO A LAS INSTALACIONES ELÉCTRICAS RESIDENCIALES, COMERCIALES E INDUSTRIALES</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>NEGRETE</t>
+  </si>
+  <si>
+    <t>VANESSA AMAIRANY</t>
+  </si>
+  <si>
+    <t>FATIMA MARILYN</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>ITZEL ABIGAIL</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>LUIS REY</t>
+  </si>
+  <si>
+    <t>ALONDRA YURIDIA</t>
+  </si>
+  <si>
+    <t>CITLALI ESPERANZA</t>
   </si>
   <si>
     <t>ANGEL DAVID</t>
   </si>
   <si>
-    <t>YAMILETH</t>
-  </si>
-  <si>
-    <t>VANESA</t>
-  </si>
-  <si>
-    <t>VALERY MIRANDA</t>
-  </si>
-  <si>
-    <t>LUZ YESENIA</t>
-  </si>
-  <si>
-    <t>MIGUEL ENRIQUE</t>
-  </si>
-  <si>
-    <t>BRISEIDA</t>
-  </si>
-  <si>
-    <t>ANEL</t>
-  </si>
-  <si>
-    <t>VICTORIA VIANNEY</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>ANGEL ABRAHAM</t>
-  </si>
-  <si>
-    <t>GISELA GUADALUPE</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>BRISSIA SINAHI</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>Inglés I</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CUAPIO</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MACUIXTLE</t>
-  </si>
-  <si>
-    <t>MONDRAGON</t>
-  </si>
-  <si>
-    <t>RAMSES</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>JAIRO</t>
-  </si>
-  <si>
-    <t>RAYMUNDO</t>
-  </si>
-  <si>
-    <t>DIEGO GREGORIO</t>
-  </si>
-  <si>
-    <t>ANGEL ADRIAN</t>
-  </si>
-  <si>
-    <t>IBARRA</t>
-  </si>
-  <si>
-    <t>DEL VALLE</t>
-  </si>
-  <si>
-    <t>GARZA</t>
-  </si>
-  <si>
-    <t>ZAYAS</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>ARMANDO</t>
-  </si>
-  <si>
-    <t>MICHEL LEONEL</t>
-  </si>
-  <si>
-    <t>JESHUA</t>
-  </si>
-  <si>
-    <t>IVETTE</t>
-  </si>
-  <si>
-    <t>ALDRICH ARMANDO</t>
-  </si>
-  <si>
-    <t>JENNYFER ARIANA</t>
-  </si>
-  <si>
-    <t>AARON</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>GIANCARLO</t>
-  </si>
-  <si>
-    <t>ANA ISABEL</t>
-  </si>
-  <si>
-    <t>NOHEMI ANGELICA</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>SERGIO JOSUE</t>
-  </si>
-  <si>
-    <t>COBOS</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>NOLASCO</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>TIZA</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>ALEXIS YAIR</t>
-  </si>
-  <si>
-    <t>YOLET</t>
-  </si>
-  <si>
-    <t>PATRICIO</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
-    <t>ERIK OMAR</t>
-  </si>
-  <si>
-    <t>VICTOR MANUEL</t>
-  </si>
-  <si>
-    <t>NAHUM HIRAM</t>
-  </si>
-  <si>
-    <t>ERIK</t>
-  </si>
-  <si>
-    <t>JOSUE GUSTAVO</t>
-  </si>
-  <si>
-    <t>CRISTIAN OSMAR</t>
-  </si>
-  <si>
-    <t>OSMAR</t>
-  </si>
-  <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
-    <t>FABIAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>MANTIENE LOS GENERADORES DE CA Y CC</t>
-  </si>
-  <si>
-    <t>MANTIENE LOS MOTORES DE CA Y CC</t>
-  </si>
-  <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
-    <t>ESCOBAR</t>
-  </si>
-  <si>
-    <t>MENA</t>
-  </si>
-  <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>KEVIN ALEXIS</t>
-  </si>
-  <si>
-    <t>LUZ ALONDRA</t>
-  </si>
-  <si>
-    <t>AMALIA PAULINA</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>BRENDA JANELY</t>
-  </si>
-  <si>
-    <t>JARET</t>
-  </si>
-  <si>
-    <t>AILYN</t>
-  </si>
-  <si>
-    <t>NIDIA GABRIELA</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>OSCAR</t>
-  </si>
-  <si>
-    <t>ABRAHAM</t>
-  </si>
-  <si>
-    <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>ESMERALDA</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
-    <t>REALIZA EL PROCESO DE ADMISIÓN Y EMPLEO</t>
-  </si>
-  <si>
-    <t>CONTRIBUYE A LA INTEGRACIÓN Y DESARROLLO DEL PERSONAL EN LA ORGANIZACIÓN</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>JOSE CARMELO</t>
-  </si>
-  <si>
-    <t>GAMALIEL</t>
-  </si>
-  <si>
-    <t>GUILLERMO ALEXANDER</t>
-  </si>
-  <si>
-    <t>REALIZA MANTENIMIENTO CORRECTIVO</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>NAZARIO</t>
-  </si>
-  <si>
-    <t>ATENOGENES</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>DULIAM</t>
-  </si>
-  <si>
-    <t>ELI ANTONIO</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>NEMESIO NAHIM</t>
-  </si>
-  <si>
-    <t>REALIZA MANTENIMIENTO A LAS INSTALACIONES ELÉCTRICAS RESIDENCIALES, COMERCIALES E INDUSTRIALES</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>QUIÑONES</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>NEGRETE</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
-    <t>VANESSA AMAIRANY</t>
-  </si>
-  <si>
-    <t>FATIMA MARILYN</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>ITZEL ABIGAIL</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>LUIS REY</t>
-  </si>
-  <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
-    <t>CITLALI ESPERANZA</t>
-  </si>
-  <si>
     <t>ALMA KAREN</t>
   </si>
   <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
     <t>RUBI</t>
   </si>
   <si>
@@ -1605,25 +1536,13 @@
     <t>SUPERVISA EL CUMPLIMIENTO DE LAS MEDIDAS DE HIGIENE Y SEGURIDAD EN LA ORGANIZACIÓN</t>
   </si>
   <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
     <t>GALICIA</t>
   </si>
   <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
     <t>ALBERTO SHAKIB</t>
   </si>
   <si>
-    <t>RONALDO</t>
-  </si>
-  <si>
     <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO</t>
   </si>
 </sst>
 </file>
@@ -2178,7 +2097,7 @@
         <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2198,7 +2117,7 @@
         <v>28</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2211,7 +2130,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2239,16 +2158,16 @@
         <v>21330051920053</v>
       </c>
       <c r="B2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E2" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2259,16 +2178,16 @@
         <v>21330051920053</v>
       </c>
       <c r="B3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E3" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2279,16 +2198,16 @@
         <v>22330051920053</v>
       </c>
       <c r="B4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E4" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2299,16 +2218,16 @@
         <v>22330051920053</v>
       </c>
       <c r="B5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E5" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2319,16 +2238,16 @@
         <v>22330051920054</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2339,16 +2258,16 @@
         <v>22330051920054</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D7" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2362,13 +2281,13 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D8" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2382,13 +2301,13 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2402,13 +2321,13 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2422,13 +2341,13 @@
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D11" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2439,16 +2358,16 @@
         <v>22330051920068</v>
       </c>
       <c r="B12" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -2459,16 +2378,16 @@
         <v>22330051920068</v>
       </c>
       <c r="B13" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -2479,16 +2398,16 @@
         <v>22330051920079</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -2499,16 +2418,16 @@
         <v>22330051920081</v>
       </c>
       <c r="B15" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C15" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D15" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -2519,16 +2438,16 @@
         <v>22330051920084</v>
       </c>
       <c r="B16" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C16" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D16" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -2539,16 +2458,16 @@
         <v>22330051920084</v>
       </c>
       <c r="B17" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C17" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D17" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -2556,19 +2475,19 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>22330051920333</v>
+        <v>22330051920212</v>
       </c>
       <c r="B18" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C18" t="s">
-        <v>192</v>
+        <v>48</v>
       </c>
       <c r="D18" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E18" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -2576,21 +2495,41 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>22330051920333</v>
+        <v>22330051920212</v>
       </c>
       <c r="B19" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C19" t="s">
-        <v>192</v>
+        <v>48</v>
       </c>
       <c r="D19" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E19" t="s">
         <v>154</v>
       </c>
       <c r="F19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>22330051920333</v>
+      </c>
+      <c r="B20" t="s">
+        <v>184</v>
+      </c>
+      <c r="C20" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" t="s">
+        <v>201</v>
+      </c>
+      <c r="E20" t="s">
+        <v>154</v>
+      </c>
+      <c r="F20">
         <v>5</v>
       </c>
     </row>
@@ -2629,16 +2568,16 @@
         <v>22330051920034</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2649,16 +2588,16 @@
         <v>22330051920034</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2669,16 +2608,16 @@
         <v>22330051920038</v>
       </c>
       <c r="B4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2689,16 +2628,16 @@
         <v>22330051920039</v>
       </c>
       <c r="B5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2709,16 +2648,16 @@
         <v>22330051920043</v>
       </c>
       <c r="B6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2729,16 +2668,16 @@
         <v>22330051920043</v>
       </c>
       <c r="B7" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2749,16 +2688,16 @@
         <v>22330051920045</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2769,16 +2708,16 @@
         <v>22330051920047</v>
       </c>
       <c r="B9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2792,13 +2731,13 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2812,13 +2751,13 @@
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D11" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2829,16 +2768,16 @@
         <v>22330051920189</v>
       </c>
       <c r="B12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -2849,16 +2788,16 @@
         <v>22330051920189</v>
       </c>
       <c r="B13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -2869,16 +2808,16 @@
         <v>22330051920191</v>
       </c>
       <c r="B14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -2919,16 +2858,16 @@
         <v>22330051920110</v>
       </c>
       <c r="B2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C2" t="s">
         <v>222</v>
       </c>
-      <c r="C2" t="s">
-        <v>226</v>
-      </c>
       <c r="D2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2939,16 +2878,16 @@
         <v>22330051920128</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2956,19 +2895,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920133</v>
+        <v>22330051920130</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D4" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E4" t="s">
-        <v>238</v>
+        <v>164</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2976,19 +2915,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920133</v>
+        <v>22330051920130</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D5" t="s">
+        <v>229</v>
+      </c>
+      <c r="E5" t="s">
         <v>233</v>
-      </c>
-      <c r="E5" t="s">
-        <v>165</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2996,19 +2935,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920145</v>
+        <v>22330051920138</v>
       </c>
       <c r="B6" t="s">
-        <v>223</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>228</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E6" t="s">
-        <v>238</v>
+        <v>164</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3016,19 +2955,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920248</v>
+        <v>22330051920138</v>
       </c>
       <c r="B7" t="s">
-        <v>224</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>229</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E7" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3036,19 +2975,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920352</v>
+        <v>22330051920246</v>
       </c>
       <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
         <v>225</v>
       </c>
-      <c r="C8" t="s">
-        <v>11</v>
-      </c>
       <c r="D8" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E8" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3059,16 +2998,16 @@
         <v>22330051920352</v>
       </c>
       <c r="B9" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E9" t="s">
-        <v>238</v>
+        <v>154</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3076,19 +3015,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920354</v>
+        <v>22330051920352</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>221</v>
       </c>
       <c r="C10" t="s">
-        <v>224</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>152</v>
+        <v>232</v>
       </c>
       <c r="E10" t="s">
-        <v>165</v>
+        <v>233</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3096,19 +3035,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330061460548</v>
+        <v>22330051920354</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D11" t="s">
-        <v>237</v>
+        <v>151</v>
       </c>
       <c r="E11" t="s">
-        <v>238</v>
+        <v>164</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3149,16 +3088,16 @@
         <v>20330051920069</v>
       </c>
       <c r="B2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="E2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3169,16 +3108,16 @@
         <v>20330051920069</v>
       </c>
       <c r="B3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="E3" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3189,16 +3128,16 @@
         <v>21330051920001</v>
       </c>
       <c r="B4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" t="s">
         <v>59</v>
       </c>
-      <c r="C4" t="s">
-        <v>62</v>
-      </c>
       <c r="D4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E4" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3209,16 +3148,16 @@
         <v>21330051920001</v>
       </c>
       <c r="B5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" t="s">
         <v>59</v>
       </c>
-      <c r="C5" t="s">
-        <v>62</v>
-      </c>
       <c r="D5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E5" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3229,16 +3168,16 @@
         <v>21330051920153</v>
       </c>
       <c r="B6" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E6" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3249,16 +3188,16 @@
         <v>21330051920164</v>
       </c>
       <c r="B7" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E7" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3269,16 +3208,16 @@
         <v>21330051920165</v>
       </c>
       <c r="B8" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C8" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D8" t="s">
+        <v>246</v>
+      </c>
+      <c r="E8" t="s">
         <v>251</v>
-      </c>
-      <c r="E8" t="s">
-        <v>256</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3289,16 +3228,16 @@
         <v>21330051920166</v>
       </c>
       <c r="B9" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C9" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D9" t="s">
+        <v>247</v>
+      </c>
+      <c r="E9" t="s">
         <v>252</v>
-      </c>
-      <c r="E9" t="s">
-        <v>257</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3309,16 +3248,16 @@
         <v>21330051920167</v>
       </c>
       <c r="B10" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C10" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D10" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E10" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3329,16 +3268,16 @@
         <v>21330051920167</v>
       </c>
       <c r="B11" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C11" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D11" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E11" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3349,16 +3288,16 @@
         <v>21330051920169</v>
       </c>
       <c r="B12" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C12" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D12" t="s">
+        <v>249</v>
+      </c>
+      <c r="E12" t="s">
         <v>254</v>
-      </c>
-      <c r="E12" t="s">
-        <v>257</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3369,16 +3308,16 @@
         <v>21330051920169</v>
       </c>
       <c r="B13" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C13" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D13" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E13" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -3389,16 +3328,16 @@
         <v>21330051920176</v>
       </c>
       <c r="B14" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C14" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D14" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E14" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -3409,16 +3348,16 @@
         <v>21330051920176</v>
       </c>
       <c r="B15" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C15" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D15" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E15" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -3462,13 +3401,13 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="E2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3479,16 +3418,16 @@
         <v>21330051920253</v>
       </c>
       <c r="B3" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C3" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="E3" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3502,13 +3441,13 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="E4" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3519,16 +3458,16 @@
         <v>21330051920287</v>
       </c>
       <c r="B5" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C5" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="E5" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3541,7 +3480,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3569,16 +3508,16 @@
         <v>21330051920331</v>
       </c>
       <c r="B2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2" t="s">
         <v>271</v>
-      </c>
-      <c r="D2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E2" t="s">
-        <v>274</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3586,21 +3525,61 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
+        <v>21330051920347</v>
+      </c>
+      <c r="B3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
         <v>21330051920353</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
+        <v>265</v>
+      </c>
+      <c r="C4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D4" t="s">
         <v>270</v>
       </c>
-      <c r="C3" t="s">
-        <v>272</v>
-      </c>
-      <c r="D3" t="s">
-        <v>273</v>
-      </c>
-      <c r="E3" t="s">
-        <v>258</v>
-      </c>
-      <c r="F3">
+      <c r="E4" t="s">
+        <v>253</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>21330051920353</v>
+      </c>
+      <c r="B5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C5" t="s">
+        <v>268</v>
+      </c>
+      <c r="D5" t="s">
+        <v>270</v>
+      </c>
+      <c r="E5" t="s">
+        <v>251</v>
+      </c>
+      <c r="F5">
         <v>5</v>
       </c>
     </row>
@@ -3611,7 +3590,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3639,16 +3618,16 @@
         <v>21330051920222</v>
       </c>
       <c r="B2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D2" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="E2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3656,19 +3635,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920223</v>
+        <v>21330051920230</v>
       </c>
       <c r="B3" t="s">
-        <v>275</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>279</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>283</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3676,19 +3655,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920230</v>
+        <v>21330051920235</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>243</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>276</v>
       </c>
       <c r="E4" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3696,19 +3675,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920232</v>
+        <v>21330051920249</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>272</v>
       </c>
       <c r="C5" t="s">
-        <v>280</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="E5" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3716,81 +3695,21 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920235</v>
+        <v>21330051920250</v>
       </c>
       <c r="B6" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>274</v>
       </c>
       <c r="D6" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="E6" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="F6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920239</v>
-      </c>
-      <c r="B7" t="s">
-        <v>276</v>
-      </c>
-      <c r="C7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" t="s">
-        <v>286</v>
-      </c>
-      <c r="E7" t="s">
-        <v>258</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920249</v>
-      </c>
-      <c r="B8" t="s">
-        <v>277</v>
-      </c>
-      <c r="C8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" t="s">
-        <v>287</v>
-      </c>
-      <c r="E8" t="s">
-        <v>258</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920250</v>
-      </c>
-      <c r="B9" t="s">
-        <v>226</v>
-      </c>
-      <c r="C9" t="s">
-        <v>281</v>
-      </c>
-      <c r="D9" t="s">
-        <v>288</v>
-      </c>
-      <c r="E9" t="s">
-        <v>256</v>
-      </c>
-      <c r="F9">
         <v>5</v>
       </c>
     </row>
@@ -3801,7 +3720,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3829,16 +3748,16 @@
         <v>20330051920100</v>
       </c>
       <c r="B2" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="C2" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="D2" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="E2" t="s">
-        <v>302</v>
+        <v>271</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3846,19 +3765,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920190</v>
+        <v>20330051920100</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>279</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>281</v>
       </c>
       <c r="D3" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="E3" t="s">
-        <v>258</v>
+        <v>292</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3872,13 +3791,13 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="E4" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3886,19 +3805,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920201</v>
+        <v>21330051920190</v>
       </c>
       <c r="B5" t="s">
-        <v>290</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>292</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="E5" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3906,19 +3825,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920205</v>
+        <v>21330051920201</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>280</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>282</v>
       </c>
       <c r="D6" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="E6" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3926,19 +3845,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920208</v>
+        <v>21330051920205</v>
       </c>
       <c r="B7" t="s">
-        <v>245</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="E7" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3946,19 +3865,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920213</v>
+        <v>21330051920208</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="C8" t="s">
-        <v>293</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E8" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3972,13 +3891,13 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="D9" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="E9" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3986,21 +3905,41 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
+        <v>21330051920213</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>283</v>
+      </c>
+      <c r="D10" t="s">
+        <v>290</v>
+      </c>
+      <c r="E10" t="s">
+        <v>253</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
         <v>21330051920214</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>13</v>
       </c>
-      <c r="C10" t="s">
-        <v>294</v>
-      </c>
-      <c r="D10" t="s">
-        <v>301</v>
-      </c>
-      <c r="E10" t="s">
-        <v>256</v>
-      </c>
-      <c r="F10">
+      <c r="C11" t="s">
+        <v>284</v>
+      </c>
+      <c r="D11" t="s">
+        <v>291</v>
+      </c>
+      <c r="E11" t="s">
+        <v>251</v>
+      </c>
+      <c r="F11">
         <v>5</v>
       </c>
     </row>
@@ -4011,7 +3950,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4039,36 +3978,36 @@
         <v>19330051920208</v>
       </c>
       <c r="B2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="D2" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="E2" t="s">
-        <v>274</v>
+        <v>253</v>
       </c>
       <c r="F2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920208</v>
+        <v>20330051920235</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="E3" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4079,16 +4018,16 @@
         <v>20330051920235</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="E4" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4102,13 +4041,13 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E5" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4122,13 +4061,13 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D6" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="E6" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4136,19 +4075,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920302</v>
+        <v>21330051920307</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="D7" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="E7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4156,19 +4095,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920307</v>
+        <v>21330051920316</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>293</v>
       </c>
       <c r="C8" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="D8" t="s">
-        <v>312</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4176,19 +4115,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920316</v>
+        <v>21330051920321</v>
       </c>
       <c r="B9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
         <v>303</v>
       </c>
-      <c r="C9" t="s">
-        <v>308</v>
-      </c>
-      <c r="D9" t="s">
-        <v>27</v>
-      </c>
       <c r="E9" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4196,19 +4135,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920319</v>
+        <v>21330051920323</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="E10" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4216,19 +4155,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920321</v>
+        <v>21330051920323</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E11" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -4236,19 +4175,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920323</v>
+        <v>21330051920326</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>294</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="E12" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -4256,61 +4195,21 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920323</v>
+        <v>21330051920337</v>
       </c>
       <c r="B13" t="s">
-        <v>95</v>
+        <v>295</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="E13" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920326</v>
-      </c>
-      <c r="B14" t="s">
-        <v>304</v>
-      </c>
-      <c r="C14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" t="s">
-        <v>316</v>
-      </c>
-      <c r="E14" t="s">
-        <v>256</v>
-      </c>
-      <c r="F14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920337</v>
-      </c>
-      <c r="B15" t="s">
-        <v>305</v>
-      </c>
-      <c r="C15" t="s">
-        <v>62</v>
-      </c>
-      <c r="D15" t="s">
-        <v>317</v>
-      </c>
-      <c r="E15" t="s">
-        <v>258</v>
-      </c>
-      <c r="F15">
         <v>5</v>
       </c>
     </row>
@@ -4321,7 +4220,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4349,16 +4248,16 @@
         <v>23330051920180</v>
       </c>
       <c r="B2" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="C2" t="s">
         <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4369,16 +4268,16 @@
         <v>23330051920180</v>
       </c>
       <c r="B3" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4389,13 +4288,13 @@
         <v>23330051920181</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="D4" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="E4" t="s">
         <v>30</v>
@@ -4409,16 +4308,16 @@
         <v>23330051920181</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="D5" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="E5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4432,10 +4331,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="D6" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="E6" t="s">
         <v>30</v>
@@ -4452,13 +4351,13 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="D7" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="E7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4472,13 +4371,13 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="D8" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="E8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4486,19 +4385,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>23330051920199</v>
+        <v>23330051920190</v>
       </c>
       <c r="B9" t="s">
-        <v>319</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>278</v>
+        <v>312</v>
       </c>
       <c r="D9" t="s">
-        <v>149</v>
+        <v>317</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>321</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4509,16 +4408,16 @@
         <v>23330051920199</v>
       </c>
       <c r="B10" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="C10" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4526,19 +4425,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>23330051920203</v>
+        <v>23330051920199</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>308</v>
       </c>
       <c r="C11" t="s">
-        <v>143</v>
+        <v>273</v>
       </c>
       <c r="D11" t="s">
-        <v>330</v>
+        <v>148</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -4549,16 +4448,16 @@
         <v>23330051920203</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D12" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -4566,19 +4465,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>23330051920212</v>
+        <v>23330051920203</v>
       </c>
       <c r="B13" t="s">
-        <v>320</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
-        <v>324</v>
+        <v>142</v>
       </c>
       <c r="D13" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="E13" t="s">
-        <v>333</v>
+        <v>30</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -4589,13 +4488,13 @@
         <v>23330051920212</v>
       </c>
       <c r="B14" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="C14" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="D14" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="E14" t="s">
         <v>30</v>
@@ -4606,21 +4505,41 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
+        <v>23330051920212</v>
+      </c>
+      <c r="B15" t="s">
+        <v>309</v>
+      </c>
+      <c r="C15" t="s">
+        <v>313</v>
+      </c>
+      <c r="D15" t="s">
+        <v>319</v>
+      </c>
+      <c r="E15" t="s">
+        <v>321</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
         <v>23330051920329</v>
       </c>
-      <c r="B15" t="s">
-        <v>169</v>
-      </c>
-      <c r="C15" t="s">
-        <v>325</v>
-      </c>
-      <c r="D15" t="s">
-        <v>332</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="B16" t="s">
+        <v>168</v>
+      </c>
+      <c r="C16" t="s">
+        <v>225</v>
+      </c>
+      <c r="D16" t="s">
+        <v>320</v>
+      </c>
+      <c r="E16" t="s">
         <v>30</v>
       </c>
-      <c r="F15">
+      <c r="F16">
         <v>5</v>
       </c>
     </row>
@@ -4631,7 +4550,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4656,19 +4575,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>23330051920033</v>
+        <v>23330051920035</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4676,19 +4595,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>23330051920033</v>
+        <v>23330051920037</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
         <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4696,16 +4615,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>23330051920035</v>
+        <v>23330051920039</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
         <v>30</v>
@@ -4716,16 +4635,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>23330051920037</v>
+        <v>23330051920043</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
         <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
         <v>30</v>
@@ -4736,61 +4655,21 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>23330051920039</v>
+        <v>23330051920043</v>
       </c>
       <c r="B6" t="s">
         <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>23330051920043</v>
-      </c>
-      <c r="B7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>23330051920043</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8">
         <v>5</v>
       </c>
     </row>
@@ -4801,7 +4680,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4826,16 +4705,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>23330051920207</v>
+        <v>23330051920215</v>
       </c>
       <c r="B2" t="s">
-        <v>293</v>
+        <v>322</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>242</v>
       </c>
       <c r="D2" t="s">
-        <v>347</v>
+        <v>331</v>
       </c>
       <c r="E2" t="s">
         <v>31</v>
@@ -4846,19 +4725,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>23330051920213</v>
+        <v>23330051920215</v>
       </c>
       <c r="B3" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="C3" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="D3" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4872,10 +4751,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="D4" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="E4" t="s">
         <v>31</v>
@@ -4892,13 +4771,13 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="D5" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="E5" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4906,19 +4785,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>23330051920237</v>
+        <v>23330051920227</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>323</v>
       </c>
       <c r="C6" t="s">
-        <v>341</v>
+        <v>313</v>
       </c>
       <c r="D6" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="E6" t="s">
-        <v>45</v>
+        <v>321</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4926,19 +4805,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>23330051920242</v>
+        <v>23330051920237</v>
       </c>
       <c r="B7" t="s">
-        <v>335</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>329</v>
       </c>
       <c r="D7" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4946,19 +4825,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>23330051920244</v>
+        <v>23330051920242</v>
       </c>
       <c r="B8" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4966,19 +4845,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>23330051920254</v>
+        <v>23330051920244</v>
       </c>
       <c r="B9" t="s">
-        <v>248</v>
+        <v>325</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4989,16 +4868,16 @@
         <v>23330051920254</v>
       </c>
       <c r="B10" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -5006,19 +4885,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>23330051920257</v>
+        <v>23330051920254</v>
       </c>
       <c r="B11" t="s">
+        <v>243</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
         <v>337</v>
       </c>
-      <c r="C11" t="s">
-        <v>342</v>
-      </c>
-      <c r="D11" t="s">
-        <v>354</v>
-      </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -5026,19 +4905,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>23330051920260</v>
+        <v>23330051920270</v>
       </c>
       <c r="B12" t="s">
-        <v>97</v>
+        <v>204</v>
       </c>
       <c r="C12" t="s">
-        <v>343</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>195</v>
+        <v>84</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -5046,19 +4925,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>23330051920260</v>
+        <v>23330051920275</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>326</v>
       </c>
       <c r="C13" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="D13" t="s">
-        <v>195</v>
+        <v>338</v>
       </c>
       <c r="E13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -5066,19 +4945,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>23330051920270</v>
+        <v>23330051920275</v>
       </c>
       <c r="B14" t="s">
-        <v>206</v>
+        <v>326</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>330</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>338</v>
       </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -5086,19 +4965,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>23330051920275</v>
+        <v>23330051920276</v>
       </c>
       <c r="B15" t="s">
-        <v>223</v>
+        <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>344</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -5106,19 +4985,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>23330051920276</v>
+        <v>23330051920280</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>327</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="E16" t="s">
-        <v>45</v>
+        <v>321</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -5126,19 +5005,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>23330051920277</v>
+        <v>23330051920328</v>
       </c>
       <c r="B17" t="s">
-        <v>226</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>345</v>
+        <v>225</v>
       </c>
       <c r="D17" t="s">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="E17" t="s">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -5146,19 +5025,19 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>23330051920280</v>
+        <v>23330051920328</v>
       </c>
       <c r="B18" t="s">
-        <v>338</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>225</v>
       </c>
       <c r="D18" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="E18" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -5166,201 +5045,21 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>23330051920280</v>
+        <v>23330051920330</v>
       </c>
       <c r="B19" t="s">
-        <v>338</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="D19" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>23330051920327</v>
-      </c>
-      <c r="B20" t="s">
-        <v>187</v>
-      </c>
-      <c r="C20" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" t="s">
-        <v>350</v>
-      </c>
-      <c r="E20" t="s">
-        <v>45</v>
-      </c>
-      <c r="F20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>23330051920327</v>
-      </c>
-      <c r="B21" t="s">
-        <v>187</v>
-      </c>
-      <c r="C21" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" t="s">
-        <v>350</v>
-      </c>
-      <c r="E21" t="s">
-        <v>141</v>
-      </c>
-      <c r="F21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>23330051920328</v>
-      </c>
-      <c r="B22" t="s">
-        <v>50</v>
-      </c>
-      <c r="C22" t="s">
-        <v>325</v>
-      </c>
-      <c r="D22" t="s">
-        <v>359</v>
-      </c>
-      <c r="E22" t="s">
-        <v>333</v>
-      </c>
-      <c r="F22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>23330051920328</v>
-      </c>
-      <c r="B23" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23" t="s">
-        <v>325</v>
-      </c>
-      <c r="D23" t="s">
-        <v>359</v>
-      </c>
-      <c r="E23" t="s">
-        <v>363</v>
-      </c>
-      <c r="F23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>23330051920330</v>
-      </c>
-      <c r="B24" t="s">
-        <v>94</v>
-      </c>
-      <c r="C24" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" t="s">
-        <v>360</v>
-      </c>
-      <c r="E24" t="s">
-        <v>45</v>
-      </c>
-      <c r="F24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>23330051920344</v>
-      </c>
-      <c r="B25" t="s">
-        <v>339</v>
-      </c>
-      <c r="C25" t="s">
-        <v>346</v>
-      </c>
-      <c r="D25" t="s">
-        <v>361</v>
-      </c>
-      <c r="E25" t="s">
-        <v>31</v>
-      </c>
-      <c r="F25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>23330051920344</v>
-      </c>
-      <c r="B26" t="s">
-        <v>339</v>
-      </c>
-      <c r="C26" t="s">
-        <v>346</v>
-      </c>
-      <c r="D26" t="s">
-        <v>361</v>
-      </c>
-      <c r="E26" t="s">
-        <v>363</v>
-      </c>
-      <c r="F26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>23330051920357</v>
-      </c>
-      <c r="B27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" t="s">
-        <v>362</v>
-      </c>
-      <c r="E27" t="s">
-        <v>333</v>
-      </c>
-      <c r="F27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>23330051920357</v>
-      </c>
-      <c r="B28" t="s">
-        <v>93</v>
-      </c>
-      <c r="C28" t="s">
-        <v>14</v>
-      </c>
-      <c r="D28" t="s">
-        <v>362</v>
-      </c>
-      <c r="E28" t="s">
-        <v>363</v>
-      </c>
-      <c r="F28">
         <v>5</v>
       </c>
     </row>
@@ -5371,7 +5070,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5396,19 +5095,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>23330051920220</v>
+        <v>23330051920218</v>
       </c>
       <c r="B2" t="s">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="C2" t="s">
-        <v>368</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>357</v>
       </c>
       <c r="E2" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5416,19 +5115,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>23330051920221</v>
+        <v>23330051920220</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>345</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>352</v>
       </c>
       <c r="D3" t="s">
-        <v>370</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5436,19 +5135,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>23330051920222</v>
+        <v>23330051920220</v>
       </c>
       <c r="B4" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>352</v>
       </c>
       <c r="D4" t="s">
-        <v>371</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>321</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5456,19 +5155,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>23330051920229</v>
+        <v>23330051920221</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>271</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="E5" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5476,19 +5175,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>23330051920229</v>
+        <v>23330051920222</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>346</v>
       </c>
       <c r="C6" t="s">
-        <v>271</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>321</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5496,19 +5195,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>23330051920230</v>
+        <v>23330051920222</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>346</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="E7" t="s">
-        <v>333</v>
+        <v>30</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5516,19 +5215,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>23330051920247</v>
+        <v>23330051920224</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>347</v>
       </c>
       <c r="C8" t="s">
-        <v>271</v>
+        <v>353</v>
       </c>
       <c r="D8" t="s">
-        <v>374</v>
+        <v>246</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>343</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5536,19 +5235,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>23330051920247</v>
+        <v>23330051920229</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="C9" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="D9" t="s">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="E9" t="s">
-        <v>141</v>
+        <v>30</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5556,19 +5255,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>23330051920251</v>
+        <v>23330051920229</v>
       </c>
       <c r="B10" t="s">
-        <v>366</v>
+        <v>101</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>266</v>
       </c>
       <c r="D10" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="E10" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -5576,19 +5275,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>23330051920251</v>
+        <v>23330051920230</v>
       </c>
       <c r="B11" t="s">
-        <v>366</v>
+        <v>101</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>321</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -5596,21 +5295,121 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
+        <v>23330051920231</v>
+      </c>
+      <c r="B12" t="s">
+        <v>348</v>
+      </c>
+      <c r="C12" t="s">
+        <v>354</v>
+      </c>
+      <c r="D12" t="s">
+        <v>362</v>
+      </c>
+      <c r="E12" t="s">
+        <v>321</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>23330051920243</v>
+      </c>
+      <c r="B13" t="s">
+        <v>349</v>
+      </c>
+      <c r="C13" t="s">
+        <v>355</v>
+      </c>
+      <c r="D13" t="s">
+        <v>363</v>
+      </c>
+      <c r="E13" t="s">
+        <v>343</v>
+      </c>
+      <c r="F13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>23330051920251</v>
+      </c>
+      <c r="B14" t="s">
+        <v>350</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s">
+        <v>364</v>
+      </c>
+      <c r="E14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>23330051920251</v>
+      </c>
+      <c r="B15" t="s">
+        <v>350</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>364</v>
+      </c>
+      <c r="E15" t="s">
+        <v>321</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
         <v>23330051920253</v>
       </c>
-      <c r="B12" t="s">
-        <v>367</v>
-      </c>
-      <c r="C12" t="s">
-        <v>369</v>
-      </c>
-      <c r="D12" t="s">
-        <v>376</v>
-      </c>
-      <c r="E12" t="s">
-        <v>333</v>
-      </c>
-      <c r="F12">
+      <c r="B16" t="s">
+        <v>351</v>
+      </c>
+      <c r="C16" t="s">
+        <v>356</v>
+      </c>
+      <c r="D16" t="s">
+        <v>365</v>
+      </c>
+      <c r="E16" t="s">
+        <v>321</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>23330051920265</v>
+      </c>
+      <c r="B17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" t="s">
+        <v>351</v>
+      </c>
+      <c r="D17" t="s">
+        <v>366</v>
+      </c>
+      <c r="E17" t="s">
+        <v>343</v>
+      </c>
+      <c r="F17">
         <v>5</v>
       </c>
     </row>
@@ -5621,7 +5420,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5646,19 +5445,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>23330051920292</v>
+        <v>23330051920299</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>258</v>
       </c>
       <c r="C2" t="s">
         <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5666,16 +5465,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>23330051920295</v>
+        <v>23330051920299</v>
       </c>
       <c r="B3" t="s">
-        <v>377</v>
+        <v>258</v>
       </c>
       <c r="C3" t="s">
-        <v>380</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="E3" t="s">
         <v>30</v>
@@ -5686,19 +5485,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>23330051920299</v>
+        <v>23330051920310</v>
       </c>
       <c r="B4" t="s">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="D4" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="E4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5706,19 +5505,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>23330051920299</v>
+        <v>23330051920310</v>
       </c>
       <c r="B5" t="s">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="D5" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5726,19 +5525,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>23330051920310</v>
+        <v>23330051920311</v>
       </c>
       <c r="B6" t="s">
-        <v>303</v>
+        <v>242</v>
       </c>
       <c r="C6" t="s">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="E6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5746,19 +5545,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>23330051920310</v>
+        <v>23330051920311</v>
       </c>
       <c r="B7" t="s">
-        <v>303</v>
+        <v>242</v>
       </c>
       <c r="C7" t="s">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>343</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5775,10 +5574,10 @@
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E8" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5789,16 +5588,16 @@
         <v>23330051920336</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="E9" t="s">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5806,19 +5605,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>23330051920345</v>
+        <v>23330051920348</v>
       </c>
       <c r="B10" t="s">
-        <v>378</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>386</v>
+        <v>148</v>
       </c>
       <c r="E10" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -5826,19 +5625,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>23330051920345</v>
+        <v>23330051920356</v>
       </c>
       <c r="B11" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>266</v>
       </c>
       <c r="D11" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>321</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -5846,19 +5645,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>23330051920348</v>
+        <v>23330051920363</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>149</v>
+        <v>373</v>
       </c>
       <c r="E12" t="s">
-        <v>45</v>
+        <v>140</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -5866,81 +5665,21 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>23330051920356</v>
+        <v>23330051920363</v>
       </c>
       <c r="B13" t="s">
-        <v>379</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>271</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="E13" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
       <c r="F13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>23330051920356</v>
-      </c>
-      <c r="B14" t="s">
-        <v>379</v>
-      </c>
-      <c r="C14" t="s">
-        <v>271</v>
-      </c>
-      <c r="D14" t="s">
-        <v>387</v>
-      </c>
-      <c r="E14" t="s">
-        <v>333</v>
-      </c>
-      <c r="F14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>23330051920363</v>
-      </c>
-      <c r="B15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C15" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" t="s">
-        <v>388</v>
-      </c>
-      <c r="E15" t="s">
-        <v>141</v>
-      </c>
-      <c r="F15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>23330051920363</v>
-      </c>
-      <c r="B16" t="s">
-        <v>95</v>
-      </c>
-      <c r="C16" t="s">
-        <v>93</v>
-      </c>
-      <c r="D16" t="s">
-        <v>388</v>
-      </c>
-      <c r="E16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16">
         <v>5</v>
       </c>
     </row>
@@ -5951,7 +5690,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5976,19 +5715,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>23330051920300</v>
+        <v>23330051920302</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>273</v>
       </c>
       <c r="C2" t="s">
-        <v>187</v>
+        <v>374</v>
       </c>
       <c r="D2" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5996,19 +5735,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>23330051920300</v>
+        <v>23330051920302</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>273</v>
       </c>
       <c r="C3" t="s">
-        <v>187</v>
+        <v>374</v>
       </c>
       <c r="D3" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6016,19 +5755,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>23330051920302</v>
+        <v>23330051920303</v>
       </c>
       <c r="B4" t="s">
-        <v>278</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>389</v>
+        <v>120</v>
       </c>
       <c r="D4" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6036,121 +5775,21 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>23330051920302</v>
+        <v>23330051920305</v>
       </c>
       <c r="B5" t="s">
-        <v>278</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>389</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="E5" t="s">
-        <v>45</v>
+        <v>343</v>
       </c>
       <c r="F5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>23330051920303</v>
-      </c>
-      <c r="B6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" t="s">
-        <v>123</v>
-      </c>
-      <c r="D6" t="s">
-        <v>393</v>
-      </c>
-      <c r="E6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>23330051920319</v>
-      </c>
-      <c r="B7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C7" t="s">
-        <v>145</v>
-      </c>
-      <c r="D7" t="s">
-        <v>394</v>
-      </c>
-      <c r="E7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>23330051920319</v>
-      </c>
-      <c r="B8" t="s">
-        <v>188</v>
-      </c>
-      <c r="C8" t="s">
-        <v>145</v>
-      </c>
-      <c r="D8" t="s">
-        <v>394</v>
-      </c>
-      <c r="E8" t="s">
-        <v>363</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>23330051920332</v>
-      </c>
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>390</v>
-      </c>
-      <c r="D9" t="s">
-        <v>395</v>
-      </c>
-      <c r="E9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>23330051920332</v>
-      </c>
-      <c r="B10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" t="s">
-        <v>390</v>
-      </c>
-      <c r="D10" t="s">
-        <v>395</v>
-      </c>
-      <c r="E10" t="s">
-        <v>141</v>
-      </c>
-      <c r="F10">
         <v>5</v>
       </c>
     </row>
@@ -6189,16 +5828,16 @@
         <v>19330051920067</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="D2" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="E2" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6209,16 +5848,16 @@
         <v>19330051920067</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="D3" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="E3" t="s">
-        <v>418</v>
+        <v>400</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6229,16 +5868,16 @@
         <v>21330051920007</v>
       </c>
       <c r="B4" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="C4" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="D4" t="s">
-        <v>404</v>
+        <v>386</v>
       </c>
       <c r="E4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6249,16 +5888,16 @@
         <v>21330051920197</v>
       </c>
       <c r="B5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C5" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D5" t="s">
-        <v>405</v>
+        <v>387</v>
       </c>
       <c r="E5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6272,13 +5911,13 @@
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="E6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6289,16 +5928,16 @@
         <v>22330051920190</v>
       </c>
       <c r="B7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C7" t="s">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="D7" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="E7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6309,16 +5948,16 @@
         <v>22330051920190</v>
       </c>
       <c r="B8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C8" t="s">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="D8" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="E8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6329,16 +5968,16 @@
         <v>22330051920192</v>
       </c>
       <c r="B9" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>408</v>
+        <v>390</v>
       </c>
       <c r="E9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6349,16 +5988,16 @@
         <v>22330051920193</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D10" t="s">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="E10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6369,16 +6008,16 @@
         <v>22330051920200</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D11" t="s">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="E11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6392,13 +6031,13 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="E12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -6409,16 +6048,16 @@
         <v>22330051920356</v>
       </c>
       <c r="B13" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C13" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="D13" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="E13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -6429,16 +6068,16 @@
         <v>22330051920359</v>
       </c>
       <c r="B14" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="C14" t="s">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="D14" t="s">
-        <v>413</v>
+        <v>395</v>
       </c>
       <c r="E14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -6449,16 +6088,16 @@
         <v>22330051920363</v>
       </c>
       <c r="B15" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="C15" t="s">
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="E15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -6469,16 +6108,16 @@
         <v>22330051920378</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="D16" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
       <c r="E16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -6489,16 +6128,16 @@
         <v>22330051920378</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="D17" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
       <c r="E17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -6509,16 +6148,16 @@
         <v>22330051920413</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D18" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
       <c r="E18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -6559,16 +6198,16 @@
         <v>21330051920105</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="D2" t="s">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="E2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6579,16 +6218,16 @@
         <v>21330051920105</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="D3" t="s">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="E3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6599,16 +6238,16 @@
         <v>22330051920236</v>
       </c>
       <c r="B4" t="s">
-        <v>419</v>
+        <v>401</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="E4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6619,16 +6258,16 @@
         <v>22330051920236</v>
       </c>
       <c r="B5" t="s">
-        <v>419</v>
+        <v>401</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="E5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6639,16 +6278,16 @@
         <v>22330051920237</v>
       </c>
       <c r="B6" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="E6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6659,16 +6298,16 @@
         <v>22330051920240</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C7" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="D7" t="s">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="E7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6679,16 +6318,16 @@
         <v>22330051920240</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C8" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="D8" t="s">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="E8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6699,16 +6338,16 @@
         <v>22330051920256</v>
       </c>
       <c r="B9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C9" t="s">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="D9" t="s">
-        <v>427</v>
+        <v>409</v>
       </c>
       <c r="E9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6722,13 +6361,13 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="D10" t="s">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="E10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6742,13 +6381,13 @@
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="E11" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6759,16 +6398,16 @@
         <v>22330051920366</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
       <c r="E12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -6779,16 +6418,16 @@
         <v>22330051920369</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="E13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -6801,7 +6440,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6832,13 +6471,13 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="E2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6852,13 +6491,13 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="E3" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6869,16 +6508,16 @@
         <v>22330051920273</v>
       </c>
       <c r="B4" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="C4" t="s">
-        <v>230</v>
+        <v>323</v>
       </c>
       <c r="D4" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="E4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6889,16 +6528,16 @@
         <v>22330051920273</v>
       </c>
       <c r="B5" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="C5" t="s">
-        <v>230</v>
+        <v>323</v>
       </c>
       <c r="D5" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="E5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6906,19 +6545,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920277</v>
+        <v>22330051920276</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>432</v>
+        <v>222</v>
       </c>
       <c r="D6" t="s">
-        <v>435</v>
+        <v>393</v>
       </c>
       <c r="E6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6926,19 +6565,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920286</v>
+        <v>22330051920277</v>
       </c>
       <c r="B7" t="s">
-        <v>226</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>185</v>
+        <v>414</v>
       </c>
       <c r="D7" t="s">
-        <v>436</v>
+        <v>417</v>
       </c>
       <c r="E7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6946,19 +6585,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920405</v>
+        <v>22330051920286</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>222</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>182</v>
       </c>
       <c r="D8" t="s">
-        <v>437</v>
+        <v>418</v>
       </c>
       <c r="E8" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6975,12 +6614,32 @@
         <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="E9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>22330051920405</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>419</v>
+      </c>
+      <c r="E10" t="s">
+        <v>163</v>
+      </c>
+      <c r="F10">
         <v>5</v>
       </c>
     </row>
@@ -7025,10 +6684,10 @@
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="E2" t="s">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7045,10 +6704,10 @@
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="E3" t="s">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7059,16 +6718,16 @@
         <v>21330051920002</v>
       </c>
       <c r="B4" t="s">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="C4" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="D4" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="E4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7079,16 +6738,16 @@
         <v>22330051920205</v>
       </c>
       <c r="B5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C5" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="D5" t="s">
-        <v>443</v>
+        <v>425</v>
       </c>
       <c r="E5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7102,13 +6761,13 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="D6" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="E6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7122,13 +6781,13 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="D7" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="E7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7139,16 +6798,16 @@
         <v>22330051920394</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C8" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7159,16 +6818,16 @@
         <v>22330051920394</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C9" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7209,16 +6868,16 @@
         <v>22330051920298</v>
       </c>
       <c r="B2" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="C2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D2" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="E2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7232,13 +6891,13 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>449</v>
+        <v>431</v>
       </c>
       <c r="E3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7249,16 +6908,16 @@
         <v>22330051920314</v>
       </c>
       <c r="B4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>450</v>
+        <v>432</v>
       </c>
       <c r="E4" t="s">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7299,16 +6958,16 @@
         <v>20330051920018</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C2" t="s">
-        <v>455</v>
+        <v>436</v>
       </c>
       <c r="D2" t="s">
-        <v>457</v>
+        <v>437</v>
       </c>
       <c r="E2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7316,19 +6975,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920049</v>
+        <v>20330051920078</v>
       </c>
       <c r="B3" t="s">
-        <v>452</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>144</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="E3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7336,19 +6995,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920078</v>
+        <v>20330051920366</v>
       </c>
       <c r="B4" t="s">
+        <v>434</v>
+      </c>
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
       <c r="D4" t="s">
-        <v>459</v>
+        <v>439</v>
       </c>
       <c r="E4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7359,16 +7018,16 @@
         <v>20330051920366</v>
       </c>
       <c r="B5" t="s">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>460</v>
+        <v>439</v>
       </c>
       <c r="E5" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7376,19 +7035,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920366</v>
+        <v>20330051920367</v>
       </c>
       <c r="B6" t="s">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="E6" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7396,19 +7055,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920367</v>
+        <v>21330051920003</v>
       </c>
       <c r="B7" t="s">
-        <v>453</v>
+        <v>166</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>461</v>
+        <v>441</v>
       </c>
       <c r="E7" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7416,19 +7075,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920003</v>
+        <v>21330051920012</v>
       </c>
       <c r="B8" t="s">
-        <v>167</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>462</v>
+        <v>442</v>
       </c>
       <c r="E8" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7445,10 +7104,10 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>463</v>
+        <v>442</v>
       </c>
       <c r="E9" t="s">
-        <v>466</v>
+        <v>445</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7456,19 +7115,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920022</v>
+        <v>21330051920015</v>
       </c>
       <c r="B10" t="s">
-        <v>271</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>456</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>464</v>
+        <v>443</v>
       </c>
       <c r="E10" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7479,16 +7138,16 @@
         <v>21330051920023</v>
       </c>
       <c r="B11" t="s">
-        <v>454</v>
+        <v>435</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>465</v>
+        <v>444</v>
       </c>
       <c r="E11" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -7499,16 +7158,16 @@
         <v>21330051920023</v>
       </c>
       <c r="B12" t="s">
-        <v>454</v>
+        <v>435</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>465</v>
+        <v>444</v>
       </c>
       <c r="E12" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -7549,13 +7208,13 @@
         <v>23330051920049</v>
       </c>
       <c r="B2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" t="s">
         <v>46</v>
       </c>
-      <c r="C2" t="s">
-        <v>49</v>
-      </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
         <v>30</v>
@@ -7572,10 +7231,10 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
         <v>30</v>
@@ -7589,13 +7248,13 @@
         <v>23330051920067</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
         <v>30</v>
@@ -7609,13 +7268,13 @@
         <v>23330051920072</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
         <v>30</v>
@@ -7632,10 +7291,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
         <v>30</v>
@@ -7651,7 +7310,7 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7676,19 +7335,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920071</v>
+        <v>21330051920077</v>
       </c>
       <c r="B2" t="s">
-        <v>188</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>451</v>
       </c>
       <c r="D2" t="s">
-        <v>273</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>274</v>
+        <v>253</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7696,19 +7355,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920071</v>
+        <v>21330051920080</v>
       </c>
       <c r="B3" t="s">
-        <v>188</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>168</v>
       </c>
       <c r="D3" t="s">
-        <v>273</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7716,19 +7375,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920077</v>
+        <v>21330051920082</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>142</v>
       </c>
       <c r="C4" t="s">
-        <v>472</v>
+        <v>452</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>457</v>
       </c>
       <c r="E4" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7736,19 +7395,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920078</v>
+        <v>21330051920089</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>273</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>479</v>
+        <v>458</v>
       </c>
       <c r="E5" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7756,19 +7415,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920078</v>
+        <v>21330051920092</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>446</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>453</v>
       </c>
       <c r="D6" t="s">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="E6" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7776,19 +7435,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920080</v>
+        <v>21330051920093</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>447</v>
       </c>
       <c r="C7" t="s">
-        <v>169</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>460</v>
       </c>
       <c r="E7" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7796,19 +7455,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920080</v>
+        <v>21330051920097</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>220</v>
       </c>
       <c r="C8" t="s">
-        <v>169</v>
+        <v>454</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>461</v>
       </c>
       <c r="E8" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7816,19 +7475,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920082</v>
+        <v>21330051920099</v>
       </c>
       <c r="B9" t="s">
-        <v>143</v>
+        <v>95</v>
       </c>
       <c r="C9" t="s">
-        <v>473</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>480</v>
+        <v>462</v>
       </c>
       <c r="E9" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7836,19 +7495,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920089</v>
+        <v>21330051920100</v>
       </c>
       <c r="B10" t="s">
-        <v>278</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
       <c r="E10" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7856,19 +7515,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920092</v>
+        <v>21330051920101</v>
       </c>
       <c r="B11" t="s">
-        <v>467</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>474</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>482</v>
+        <v>464</v>
       </c>
       <c r="E11" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -7876,19 +7535,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920093</v>
+        <v>21330051920102</v>
       </c>
       <c r="B12" t="s">
-        <v>468</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D12" t="s">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="E12" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -7896,19 +7555,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920097</v>
+        <v>21330051920102</v>
       </c>
       <c r="B13" t="s">
-        <v>222</v>
+        <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>475</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>484</v>
+        <v>465</v>
       </c>
       <c r="E13" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -7916,19 +7575,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920099</v>
+        <v>21330051920103</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>448</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>485</v>
+        <v>466</v>
       </c>
       <c r="E14" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -7936,19 +7595,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920100</v>
+        <v>21330051920107</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>449</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>170</v>
       </c>
       <c r="D15" t="s">
-        <v>486</v>
+        <v>467</v>
       </c>
       <c r="E15" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -7956,19 +7615,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920101</v>
+        <v>21330051920107</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>449</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>170</v>
       </c>
       <c r="D16" t="s">
-        <v>487</v>
+        <v>467</v>
       </c>
       <c r="E16" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -7976,19 +7635,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920102</v>
+        <v>21330051920260</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>455</v>
       </c>
       <c r="D17" t="s">
-        <v>348</v>
+        <v>468</v>
       </c>
       <c r="E17" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -7996,19 +7655,19 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920102</v>
+        <v>21330051920305</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>450</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>456</v>
       </c>
       <c r="D18" t="s">
-        <v>348</v>
+        <v>469</v>
       </c>
       <c r="E18" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -8016,121 +7675,21 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920103</v>
+        <v>21330051920305</v>
       </c>
       <c r="B19" t="s">
+        <v>450</v>
+      </c>
+      <c r="C19" t="s">
+        <v>456</v>
+      </c>
+      <c r="D19" t="s">
         <v>469</v>
       </c>
-      <c r="C19" t="s">
-        <v>93</v>
-      </c>
-      <c r="D19" t="s">
-        <v>488</v>
-      </c>
       <c r="E19" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920104</v>
-      </c>
-      <c r="B20" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" t="s">
-        <v>476</v>
-      </c>
-      <c r="D20" t="s">
-        <v>489</v>
-      </c>
-      <c r="E20" t="s">
-        <v>274</v>
-      </c>
-      <c r="F20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920107</v>
-      </c>
-      <c r="B21" t="s">
-        <v>470</v>
-      </c>
-      <c r="C21" t="s">
-        <v>172</v>
-      </c>
-      <c r="D21" t="s">
-        <v>490</v>
-      </c>
-      <c r="E21" t="s">
-        <v>256</v>
-      </c>
-      <c r="F21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920107</v>
-      </c>
-      <c r="B22" t="s">
-        <v>470</v>
-      </c>
-      <c r="C22" t="s">
-        <v>172</v>
-      </c>
-      <c r="D22" t="s">
-        <v>490</v>
-      </c>
-      <c r="E22" t="s">
-        <v>274</v>
-      </c>
-      <c r="F22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920260</v>
-      </c>
-      <c r="B23" t="s">
-        <v>19</v>
-      </c>
-      <c r="C23" t="s">
-        <v>477</v>
-      </c>
-      <c r="D23" t="s">
-        <v>491</v>
-      </c>
-      <c r="E23" t="s">
-        <v>256</v>
-      </c>
-      <c r="F23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920305</v>
-      </c>
-      <c r="B24" t="s">
-        <v>471</v>
-      </c>
-      <c r="C24" t="s">
-        <v>478</v>
-      </c>
-      <c r="D24" t="s">
-        <v>492</v>
-      </c>
-      <c r="E24" t="s">
-        <v>256</v>
-      </c>
-      <c r="F24">
         <v>5</v>
       </c>
     </row>
@@ -8169,16 +7728,16 @@
         <v>19330051920241</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>497</v>
+        <v>474</v>
       </c>
       <c r="E2" t="s">
-        <v>502</v>
+        <v>479</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8189,16 +7748,16 @@
         <v>21330051920111</v>
       </c>
       <c r="B3" t="s">
-        <v>364</v>
+        <v>345</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>498</v>
+        <v>475</v>
       </c>
       <c r="E3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8209,16 +7768,16 @@
         <v>21330051920111</v>
       </c>
       <c r="B4" t="s">
-        <v>364</v>
+        <v>345</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>498</v>
+        <v>475</v>
       </c>
       <c r="E4" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8229,16 +7788,16 @@
         <v>21330051920120</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>499</v>
+        <v>476</v>
       </c>
       <c r="E5" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8249,16 +7808,16 @@
         <v>21330051920123</v>
       </c>
       <c r="B6" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="C6" t="s">
-        <v>495</v>
+        <v>472</v>
       </c>
       <c r="D6" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="E6" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -8269,16 +7828,16 @@
         <v>21330051920125</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>500</v>
+        <v>477</v>
       </c>
       <c r="E7" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -8289,16 +7848,16 @@
         <v>21330051920125</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>500</v>
+        <v>477</v>
       </c>
       <c r="E8" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -8309,16 +7868,16 @@
         <v>21330051920126</v>
       </c>
       <c r="B9" t="s">
-        <v>494</v>
+        <v>471</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -8329,16 +7888,16 @@
         <v>21330051920126</v>
       </c>
       <c r="B10" t="s">
-        <v>494</v>
+        <v>471</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
         <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -8349,16 +7908,16 @@
         <v>21330051920132</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>496</v>
+        <v>473</v>
       </c>
       <c r="D11" t="s">
-        <v>501</v>
+        <v>478</v>
       </c>
       <c r="E11" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -8399,16 +7958,16 @@
         <v>21330051920031</v>
       </c>
       <c r="B2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>508</v>
+        <v>485</v>
       </c>
       <c r="E2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8419,16 +7978,16 @@
         <v>21330051920031</v>
       </c>
       <c r="B3" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>508</v>
+        <v>485</v>
       </c>
       <c r="E3" t="s">
-        <v>517</v>
+        <v>494</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8439,16 +7998,16 @@
         <v>21330051920035</v>
       </c>
       <c r="B4" t="s">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>509</v>
+        <v>486</v>
       </c>
       <c r="E4" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8459,16 +8018,16 @@
         <v>21330051920036</v>
       </c>
       <c r="B5" t="s">
-        <v>503</v>
+        <v>480</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>510</v>
+        <v>487</v>
       </c>
       <c r="E5" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8479,16 +8038,16 @@
         <v>21330051920046</v>
       </c>
       <c r="B6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C6" t="s">
-        <v>505</v>
+        <v>482</v>
       </c>
       <c r="D6" t="s">
-        <v>511</v>
+        <v>488</v>
       </c>
       <c r="E6" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -8499,16 +8058,16 @@
         <v>21330051920048</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D7" t="s">
-        <v>512</v>
+        <v>489</v>
       </c>
       <c r="E7" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -8519,16 +8078,16 @@
         <v>21330051920057</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
         <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>513</v>
+        <v>490</v>
       </c>
       <c r="E8" t="s">
-        <v>517</v>
+        <v>494</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -8539,16 +8098,16 @@
         <v>21330051920057</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>513</v>
+        <v>490</v>
       </c>
       <c r="E9" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -8559,16 +8118,16 @@
         <v>21330051920062</v>
       </c>
       <c r="B10" t="s">
-        <v>504</v>
+        <v>481</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>514</v>
+        <v>491</v>
       </c>
       <c r="E10" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -8579,16 +8138,16 @@
         <v>21330051920063</v>
       </c>
       <c r="B11" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D11" t="s">
-        <v>515</v>
+        <v>492</v>
       </c>
       <c r="E11" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -8599,16 +8158,16 @@
         <v>21330051920063</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C12" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D12" t="s">
-        <v>515</v>
+        <v>492</v>
       </c>
       <c r="E12" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -8619,16 +8178,16 @@
         <v>21330051920065</v>
       </c>
       <c r="B13" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C13" t="s">
-        <v>506</v>
+        <v>483</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E13" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -8642,13 +8201,13 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>507</v>
+        <v>484</v>
       </c>
       <c r="D14" t="s">
-        <v>516</v>
+        <v>493</v>
       </c>
       <c r="E14" t="s">
-        <v>518</v>
+        <v>495</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -8662,13 +8221,13 @@
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>507</v>
+        <v>484</v>
       </c>
       <c r="D15" t="s">
-        <v>516</v>
+        <v>493</v>
       </c>
       <c r="E15" t="s">
-        <v>517</v>
+        <v>494</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -8681,7 +8240,7 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -8706,19 +8265,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920135</v>
+        <v>21330051920141</v>
       </c>
       <c r="B2" t="s">
-        <v>342</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>434</v>
       </c>
       <c r="D2" t="s">
-        <v>521</v>
+        <v>497</v>
       </c>
       <c r="E2" t="s">
-        <v>274</v>
+        <v>253</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8726,19 +8285,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920135</v>
+        <v>21330051920141</v>
       </c>
       <c r="B3" t="s">
-        <v>342</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>434</v>
       </c>
       <c r="D3" t="s">
-        <v>521</v>
+        <v>497</v>
       </c>
       <c r="E3" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8746,141 +8305,21 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920141</v>
+        <v>21330051920148</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>453</v>
+        <v>496</v>
       </c>
       <c r="D4" t="s">
-        <v>522</v>
+        <v>498</v>
       </c>
       <c r="E4" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="F4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920141</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>453</v>
-      </c>
-      <c r="D5" t="s">
-        <v>522</v>
-      </c>
-      <c r="E5" t="s">
-        <v>256</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920147</v>
-      </c>
-      <c r="B6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" t="s">
-        <v>345</v>
-      </c>
-      <c r="D6" t="s">
-        <v>523</v>
-      </c>
-      <c r="E6" t="s">
-        <v>256</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920147</v>
-      </c>
-      <c r="B7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" t="s">
-        <v>345</v>
-      </c>
-      <c r="D7" t="s">
-        <v>523</v>
-      </c>
-      <c r="E7" t="s">
-        <v>274</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920148</v>
-      </c>
-      <c r="B8" t="s">
-        <v>94</v>
-      </c>
-      <c r="C8" t="s">
-        <v>520</v>
-      </c>
-      <c r="D8" t="s">
-        <v>524</v>
-      </c>
-      <c r="E8" t="s">
-        <v>256</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920382</v>
-      </c>
-      <c r="B9" t="s">
-        <v>519</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" t="s">
-        <v>525</v>
-      </c>
-      <c r="E9" t="s">
-        <v>257</v>
-      </c>
-      <c r="F9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920382</v>
-      </c>
-      <c r="B10" t="s">
-        <v>519</v>
-      </c>
-      <c r="C10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" t="s">
-        <v>525</v>
-      </c>
-      <c r="E10" t="s">
-        <v>274</v>
-      </c>
-      <c r="F10">
         <v>5</v>
       </c>
     </row>
@@ -8919,13 +8358,13 @@
         <v>23330051920077</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
         <v>30</v>
@@ -8939,13 +8378,13 @@
         <v>23330051920079</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
         <v>30</v>
@@ -8959,13 +8398,13 @@
         <v>23330051920081</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
         <v>29</v>
@@ -8979,13 +8418,13 @@
         <v>23330051920082</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
         <v>30</v>
@@ -8999,13 +8438,13 @@
         <v>23330051920083</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
         <v>30</v>
@@ -9019,13 +8458,13 @@
         <v>23330051920084</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
         <v>30</v>
@@ -9039,13 +8478,13 @@
         <v>23330051920086</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
         <v>30</v>
@@ -9062,10 +8501,10 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
         <v>30</v>
@@ -9079,16 +8518,16 @@
         <v>23330051920095</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -9099,16 +8538,16 @@
         <v>23330051920095</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -9119,13 +8558,13 @@
         <v>23330051920104</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E12" t="s">
         <v>30</v>
@@ -9139,16 +8578,16 @@
         <v>23330051920105</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -9159,16 +8598,16 @@
         <v>23330051920105</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -9179,13 +8618,13 @@
         <v>23330051920112</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E15" t="s">
         <v>30</v>
@@ -9229,13 +8668,13 @@
         <v>23330051920118</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
         <v>30</v>
@@ -9249,16 +8688,16 @@
         <v>23330051920118</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -9269,13 +8708,13 @@
         <v>23330051920121</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E4" t="s">
         <v>30</v>
@@ -9289,16 +8728,16 @@
         <v>23330051920123</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -9309,13 +8748,13 @@
         <v>23330051920123</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
         <v>30</v>
@@ -9332,10 +8771,10 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
         <v>30</v>
@@ -9349,13 +8788,13 @@
         <v>23330051920133</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
         <v>30</v>
@@ -9375,7 +8814,7 @@
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
         <v>30</v>
@@ -9389,13 +8828,13 @@
         <v>23330051920139</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E10" t="s">
         <v>29</v>
@@ -9409,13 +8848,13 @@
         <v>23330051920139</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E11" t="s">
         <v>30</v>
@@ -9432,10 +8871,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E12" t="s">
         <v>30</v>
@@ -9449,13 +8888,13 @@
         <v>23330051920142</v>
       </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E13" t="s">
         <v>30</v>
@@ -9469,13 +8908,13 @@
         <v>23330051920144</v>
       </c>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E14" t="s">
         <v>30</v>
@@ -9489,13 +8928,13 @@
         <v>23330051920145</v>
       </c>
       <c r="B15" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E15" t="s">
         <v>30</v>
@@ -9512,10 +8951,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E16" t="s">
         <v>30</v>
@@ -9532,10 +8971,10 @@
         <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E17" t="s">
         <v>30</v>
@@ -9549,13 +8988,13 @@
         <v>23330051920255</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E18" t="s">
         <v>30</v>
@@ -9569,13 +9008,13 @@
         <v>23330051920315</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E19" t="s">
         <v>30</v>
@@ -9591,7 +9030,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -9619,13 +9058,13 @@
         <v>23330051920154</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E2" t="s">
         <v>29</v>
@@ -9639,13 +9078,13 @@
         <v>23330051920154</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E3" t="s">
         <v>30</v>
@@ -9659,16 +9098,16 @@
         <v>23330051920155</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -9679,16 +9118,16 @@
         <v>23330051920155</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -9702,10 +9141,10 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E6" t="s">
         <v>30</v>
@@ -9725,7 +9164,7 @@
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E7" t="s">
         <v>30</v>
@@ -9742,13 +9181,13 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>140</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -9756,19 +9195,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>23330051920165</v>
+        <v>23330051920160</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -9779,16 +9218,16 @@
         <v>23330051920165</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E10" t="s">
-        <v>141</v>
+        <v>30</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -9799,16 +9238,16 @@
         <v>23330051920166</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -9819,16 +9258,16 @@
         <v>23330051920166</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -9839,13 +9278,13 @@
         <v>23330051920167</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E13" t="s">
         <v>30</v>
@@ -9856,16 +9295,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>23330051920170</v>
+        <v>23330051920169</v>
       </c>
       <c r="B14" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D14" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E14" t="s">
         <v>30</v>
@@ -9876,19 +9315,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>23330051920171</v>
+        <v>23330051920169</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="D15" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -9896,19 +9335,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>23330051920174</v>
+        <v>23330051920170</v>
       </c>
       <c r="B16" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D16" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E16" t="s">
-        <v>141</v>
+        <v>30</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -9916,21 +9355,81 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>23330051920354</v>
+        <v>23330051920171</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>128</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E17" t="s">
         <v>30</v>
       </c>
       <c r="F17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>23330051920171</v>
+      </c>
+      <c r="B18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
+        <v>137</v>
+      </c>
+      <c r="E18" t="s">
+        <v>140</v>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>23330051920174</v>
+      </c>
+      <c r="B19" t="s">
+        <v>121</v>
+      </c>
+      <c r="C19" t="s">
+        <v>121</v>
+      </c>
+      <c r="D19" t="s">
+        <v>138</v>
+      </c>
+      <c r="E19" t="s">
+        <v>140</v>
+      </c>
+      <c r="F19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>23330051920354</v>
+      </c>
+      <c r="B20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" t="s">
+        <v>126</v>
+      </c>
+      <c r="D20" t="s">
+        <v>139</v>
+      </c>
+      <c r="E20" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20">
         <v>5</v>
       </c>
     </row>
@@ -9969,16 +9468,16 @@
         <v>22330051920006</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -9989,16 +9488,16 @@
         <v>22330051920010</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -10012,13 +9511,13 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -10029,16 +9528,16 @@
         <v>22330051920015</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -10049,16 +9548,16 @@
         <v>22330051920018</v>
       </c>
       <c r="B6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -10069,16 +9568,16 @@
         <v>22330051920173</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -10122,13 +9621,13 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -10142,13 +9641,13 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -10159,16 +9658,16 @@
         <v>22330051920108</v>
       </c>
       <c r="B4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -10179,16 +9678,16 @@
         <v>22330051920108</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -10199,16 +9698,16 @@
         <v>22330051920114</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -10219,16 +9718,16 @@
         <v>22330051920116</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -10239,16 +9738,16 @@
         <v>22330051920122</v>
       </c>
       <c r="B8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -10261,7 +9760,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -10289,16 +9788,16 @@
         <v>22330051920150</v>
       </c>
       <c r="B2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -10309,16 +9808,16 @@
         <v>22330051920153</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -10329,16 +9828,16 @@
         <v>22330051920157</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -10346,19 +9845,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920284</v>
+        <v>22330051920299</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E5" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -10366,81 +9865,21 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920284</v>
+        <v>22330051920426</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>167</v>
       </c>
       <c r="C6" t="s">
         <v>171</v>
       </c>
       <c r="D6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E6" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="F6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920299</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>172</v>
-      </c>
-      <c r="D7" t="s">
-        <v>178</v>
-      </c>
-      <c r="E7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920299</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" t="s">
-        <v>172</v>
-      </c>
-      <c r="D8" t="s">
-        <v>178</v>
-      </c>
-      <c r="E8" t="s">
-        <v>166</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920426</v>
-      </c>
-      <c r="B9" t="s">
-        <v>168</v>
-      </c>
-      <c r="C9" t="s">
-        <v>173</v>
-      </c>
-      <c r="D9" t="s">
-        <v>179</v>
-      </c>
-      <c r="E9" t="s">
-        <v>181</v>
-      </c>
-      <c r="F9">
         <v>5</v>
       </c>
     </row>

--- a/Rescatables20231.xlsx
+++ b/Rescatables20231.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="498">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -180,6 +180,9 @@
     <t>ARENAS</t>
   </si>
   <si>
+    <t>CERON</t>
+  </si>
+  <si>
     <t>PAZ</t>
   </si>
   <si>
@@ -189,6 +192,9 @@
     <t>CALCANEO</t>
   </si>
   <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
@@ -204,6 +210,9 @@
     <t>YAELIS</t>
   </si>
   <si>
+    <t>HUGO ISAI</t>
+  </si>
+  <si>
     <t>DENISSE</t>
   </si>
   <si>
@@ -312,9 +321,6 @@
     <t>BAROJAS</t>
   </si>
   <si>
-    <t>CERON</t>
-  </si>
-  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
@@ -471,685 +477,676 @@
     <t>Ciencias sociales I</t>
   </si>
   <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>JERONIMO</t>
+  </si>
+  <si>
+    <t>EDER</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>DIEGO JESUS</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>ANGEL GUILLERMO</t>
+  </si>
+  <si>
+    <t>BIOLOGÍA</t>
+  </si>
+  <si>
+    <t>INGLÉS III</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>PRADO</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>ANETTE</t>
+  </si>
+  <si>
+    <t>BARUCH BOSET</t>
+  </si>
+  <si>
+    <t>ILEANA</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>GEOMETRÍA ANALÍTICA</t>
+  </si>
+  <si>
+    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS PARASITOLÓGICAS</t>
+  </si>
+  <si>
+    <t>ÉTICA</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>QUINTANA</t>
+  </si>
+  <si>
+    <t>EDUARDO EMER</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>TONALLI</t>
+  </si>
+  <si>
+    <t>CRISTIAN</t>
+  </si>
+  <si>
+    <t>APLICA LA METODOLOGÍA DE DESARROLLO RÁPIDO DE APLICACIONES CON PROGRAMACIÓN ORIENTADA A EVENTOS</t>
+  </si>
+  <si>
+    <t>APLICA LA METODOLOGÍA ESPIRAL CON PROGRAMACIÓN ORIENTADA A OBJETOS</t>
+  </si>
+  <si>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>AYOHUA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>CHIMALHUA</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>LUIS FELIPE</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>SALMA AISHA</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
+    <t>JIMENA</t>
+  </si>
+  <si>
+    <t>MELANIE SOFIA</t>
+  </si>
+  <si>
+    <t>ALEXANDRA</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>CLAUDIA PAOLA</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>PALOMINO</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>JENKINS</t>
+  </si>
+  <si>
+    <t>MELCHOR</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>SALOMON</t>
+  </si>
+  <si>
+    <t>CARLOS YAEL</t>
+  </si>
+  <si>
+    <t>ROGGER JUSEFH</t>
+  </si>
+  <si>
+    <t>AARON MIGUEL</t>
+  </si>
+  <si>
+    <t>JULIAN DAVID</t>
+  </si>
+  <si>
+    <t>ABIEL NEFTALI</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>ARTHUR RICHARD</t>
+  </si>
+  <si>
+    <t>ALDAHIR</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>PIÑA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>ODALIS SOFIA</t>
+  </si>
+  <si>
+    <t>KARENT LILIANA</t>
+  </si>
+  <si>
+    <t>ABIGAIL ANTONIA</t>
+  </si>
+  <si>
+    <t>ZURI GABRIELA</t>
+  </si>
+  <si>
+    <t>LUISA MARIA</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
+    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS BACTERIOLÓGICAS</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>LOYO</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>MAYO</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>NERI</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>AYLIN MELISSA</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>LUIS OMAR</t>
+  </si>
+  <si>
+    <t>CHARBEL</t>
+  </si>
+  <si>
+    <t>CANDIDO</t>
+  </si>
+  <si>
+    <t>CÁLCULO INTEGRAL</t>
+  </si>
+  <si>
+    <t>CIENCIA, TECNOLOGÍA, SOCIEDAD Y VALORES</t>
+  </si>
+  <si>
+    <t>FÍSICA II</t>
+  </si>
+  <si>
+    <t>DISEÑA Y MANTIENE LOS SISTEMAS DE ILUMINACIÓN</t>
+  </si>
+  <si>
+    <t>ARGÜELLO</t>
+  </si>
+  <si>
+    <t>VENEGAS</t>
+  </si>
+  <si>
+    <t>NARANJO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>AMECA</t>
+  </si>
+  <si>
+    <t>ESTEFANIA</t>
+  </si>
+  <si>
+    <t>ATZIN HEFZIBA</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>EZEQUIEL</t>
+  </si>
+  <si>
+    <t>ABAD</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>INGLÉS V</t>
+  </si>
+  <si>
+    <t>TEHUINTLE</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
+    <t>LIZBETH JOSELYN</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>GETSEMANI GUADALUPE</t>
+  </si>
+  <si>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>ALEMAN</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>CUICAHUA</t>
+  </si>
+  <si>
+    <t>CHRISTIAN YAIR</t>
+  </si>
+  <si>
+    <t>JORGE GUILLERMO</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>DIEGO HUMBERTO</t>
+  </si>
+  <si>
+    <t>ZURIEL ELIHU</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>DARINKA</t>
+  </si>
+  <si>
+    <t>IMPLEMENTA Y MANTIENE LOS SISTEMAS DE ENERGÍA RENOVABLE</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>MONGE</t>
+  </si>
+  <si>
+    <t>NAHOMY</t>
+  </si>
+  <si>
+    <t>JOSE RAFAEL</t>
+  </si>
+  <si>
+    <t>YAMILET MONSERRAT</t>
+  </si>
+  <si>
+    <t>DIANA CRISTINA</t>
+  </si>
+  <si>
+    <t>ANA LAURA</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
+  </si>
+  <si>
+    <t>IVANNA DANIELA</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>BUSTOS</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>DAMIAN</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>AUTRAN</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>JOSE EMILIANO</t>
+  </si>
+  <si>
+    <t>JESUS JAREF</t>
+  </si>
+  <si>
+    <t>NATANAHEL</t>
+  </si>
+  <si>
+    <t>AXEL AARON</t>
+  </si>
+  <si>
+    <t>LUIS FABIAN</t>
+  </si>
+  <si>
+    <t>ALEX URIEL</t>
+  </si>
+  <si>
+    <t>SABDY</t>
+  </si>
+  <si>
+    <t>Pensamiento matemático I</t>
+  </si>
+  <si>
+    <t>CALVA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
+    <t>FERRER</t>
+  </si>
+  <si>
+    <t>MONTERROSAS</t>
+  </si>
+  <si>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>YAMILETH</t>
+  </si>
+  <si>
+    <t>INGRID ISABEL</t>
+  </si>
+  <si>
+    <t>VANESA</t>
+  </si>
+  <si>
+    <t>VALERY MIRANDA</t>
+  </si>
+  <si>
+    <t>LUZ YESENIA</t>
+  </si>
+  <si>
+    <t>MIGUEL ENRIQUE</t>
+  </si>
+  <si>
+    <t>ANEL</t>
+  </si>
+  <si>
+    <t>VICTORIA VIANNEY</t>
+  </si>
+  <si>
+    <t>ANGEL ABRAHAM</t>
+  </si>
+  <si>
+    <t>GISELA GUADALUPE</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>Inglés I</t>
+  </si>
+  <si>
+    <t>ALMANZA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CUAPIO</t>
+  </si>
+  <si>
+    <t>DORANTES</t>
+  </si>
+  <si>
+    <t>GILES</t>
+  </si>
+  <si>
+    <t>LAGUNA</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>MACUIXTLE</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>FIGUEROA</t>
+  </si>
+  <si>
+    <t>NATH</t>
+  </si>
+  <si>
+    <t>MONDRAGON</t>
+  </si>
+  <si>
+    <t>VANESA BETHSABE</t>
+  </si>
+  <si>
+    <t>RAMSES</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>JAIRO</t>
+  </si>
+  <si>
+    <t>ALEXA YAMILET</t>
+  </si>
+  <si>
+    <t>AARON ZACHARY</t>
+  </si>
+  <si>
+    <t>DIEGO GREGORIO</t>
+  </si>
+  <si>
+    <t>ANGEL ADRIAN</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>GARZA</t>
+  </si>
+  <si>
     <t>HERRERA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
-    <t>EDER</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>DIEGO JESUS</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
-  </si>
-  <si>
-    <t>ANGEL GUILLERMO</t>
-  </si>
-  <si>
-    <t>BIOLOGÍA</t>
-  </si>
-  <si>
-    <t>INGLÉS III</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>ANETTE</t>
-  </si>
-  <si>
-    <t>BARUCH BOSET</t>
-  </si>
-  <si>
-    <t>ILEANA</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>GEOMETRÍA ANALÍTICA</t>
-  </si>
-  <si>
-    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS PARASITOLÓGICAS</t>
-  </si>
-  <si>
-    <t>ÉTICA</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>QUINTANA</t>
-  </si>
-  <si>
-    <t>EDUARDO EMER</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>TONALLI</t>
-  </si>
-  <si>
-    <t>CRISTIAN</t>
-  </si>
-  <si>
-    <t>APLICA LA METODOLOGÍA DE DESARROLLO RÁPIDO DE APLICACIONES CON PROGRAMACIÓN ORIENTADA A EVENTOS</t>
-  </si>
-  <si>
-    <t>APLICA LA METODOLOGÍA ESPIRAL CON PROGRAMACIÓN ORIENTADA A OBJETOS</t>
-  </si>
-  <si>
-    <t>OREA</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>AYOHUA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CHIMALHUA</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>LUIS FELIPE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>SALMA AISHA</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>JIMENA</t>
-  </si>
-  <si>
-    <t>MELANIE SOFIA</t>
-  </si>
-  <si>
-    <t>ALEXANDRA</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>CLAUDIA PAOLA</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>PALOMINO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>JENKINS</t>
-  </si>
-  <si>
-    <t>MELCHOR</t>
-  </si>
-  <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
-    <t>CARLOS YAEL</t>
-  </si>
-  <si>
-    <t>MIGUEL ANTONIO</t>
-  </si>
-  <si>
-    <t>ROGGER JUSEFH</t>
-  </si>
-  <si>
-    <t>AARON MIGUEL</t>
-  </si>
-  <si>
-    <t>JULIAN DAVID</t>
-  </si>
-  <si>
-    <t>ABIEL NEFTALI</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>GEOVANNI</t>
-  </si>
-  <si>
-    <t>ARTHUR RICHARD</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>PIÑA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>ODALIS SOFIA</t>
-  </si>
-  <si>
-    <t>KARENT LILIANA</t>
-  </si>
-  <si>
-    <t>ABIGAIL ANTONIA</t>
-  </si>
-  <si>
-    <t>ZURI GABRIELA</t>
-  </si>
-  <si>
-    <t>LUISA MARIA</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS BACTERIOLÓGICAS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>LOYO</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>MAYO</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>NERI</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>AYLIN MELISSA</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>LUIS OMAR</t>
-  </si>
-  <si>
-    <t>CHARBEL</t>
-  </si>
-  <si>
-    <t>CANDIDO</t>
-  </si>
-  <si>
-    <t>CÁLCULO INTEGRAL</t>
-  </si>
-  <si>
-    <t>CIENCIA, TECNOLOGÍA, SOCIEDAD Y VALORES</t>
-  </si>
-  <si>
-    <t>FÍSICA II</t>
-  </si>
-  <si>
-    <t>DISEÑA Y MANTIENE LOS SISTEMAS DE ILUMINACIÓN</t>
-  </si>
-  <si>
-    <t>ARGÜELLO</t>
-  </si>
-  <si>
-    <t>VENEGAS</t>
-  </si>
-  <si>
-    <t>NARANJO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>AMECA</t>
-  </si>
-  <si>
-    <t>ESTEFANIA</t>
-  </si>
-  <si>
-    <t>ATZIN HEFZIBA</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>EZEQUIEL</t>
-  </si>
-  <si>
-    <t>ABAD</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>INGLÉS V</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>LIZBETH JOSELYN</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>GETSEMANI GUADALUPE</t>
-  </si>
-  <si>
-    <t>NUBE</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>ALEMAN</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>CUICAHUA</t>
-  </si>
-  <si>
-    <t>CHRISTIAN YAIR</t>
-  </si>
-  <si>
-    <t>JORGE GUILLERMO</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>DIEGO HUMBERTO</t>
-  </si>
-  <si>
-    <t>ZURIEL ELIHU</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>DARINKA</t>
-  </si>
-  <si>
-    <t>IMPLEMENTA Y MANTIENE LOS SISTEMAS DE ENERGÍA RENOVABLE</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>NAHOMY</t>
-  </si>
-  <si>
-    <t>JOSE RAFAEL</t>
-  </si>
-  <si>
-    <t>YAMILET MONSERRAT</t>
-  </si>
-  <si>
-    <t>DIANA CRISTINA</t>
-  </si>
-  <si>
-    <t>ANA LAURA</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>IVANNA DANIELA</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>BUSTOS</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>AUTRAN</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>JOSE EMILIANO</t>
-  </si>
-  <si>
-    <t>JESUS JAREF</t>
-  </si>
-  <si>
-    <t>NATANAHEL</t>
-  </si>
-  <si>
-    <t>AXEL AARON</t>
-  </si>
-  <si>
-    <t>LUIS FABIAN</t>
-  </si>
-  <si>
-    <t>ALEX URIEL</t>
-  </si>
-  <si>
-    <t>SABDY</t>
-  </si>
-  <si>
-    <t>Pensamiento matemático I</t>
-  </si>
-  <si>
-    <t>CALVA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
-    <t>FERRER</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>YAMILETH</t>
-  </si>
-  <si>
-    <t>INGRID ISABEL</t>
-  </si>
-  <si>
-    <t>VANESA</t>
-  </si>
-  <si>
-    <t>VALERY MIRANDA</t>
-  </si>
-  <si>
-    <t>LUZ YESENIA</t>
-  </si>
-  <si>
-    <t>MIGUEL ENRIQUE</t>
-  </si>
-  <si>
-    <t>ANEL</t>
-  </si>
-  <si>
-    <t>VICTORIA VIANNEY</t>
-  </si>
-  <si>
-    <t>ANGEL ABRAHAM</t>
-  </si>
-  <si>
-    <t>GISELA GUADALUPE</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>Inglés I</t>
-  </si>
-  <si>
-    <t>ALMANZA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CUAPIO</t>
-  </si>
-  <si>
-    <t>DORANTES</t>
-  </si>
-  <si>
-    <t>GILES</t>
-  </si>
-  <si>
-    <t>LAGUNA</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MACUIXTLE</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>FIGUEROA</t>
-  </si>
-  <si>
-    <t>NATH</t>
-  </si>
-  <si>
-    <t>MONDRAGON</t>
-  </si>
-  <si>
-    <t>VANESA BETHSABE</t>
-  </si>
-  <si>
-    <t>RAMSES</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>JAIRO</t>
-  </si>
-  <si>
-    <t>ALEXA YAMILET</t>
-  </si>
-  <si>
-    <t>AARON ZACHARY</t>
-  </si>
-  <si>
-    <t>DIEGO GREGORIO</t>
-  </si>
-  <si>
-    <t>ANGEL ADRIAN</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>GARZA</t>
   </si>
   <si>
     <t>MICHEL LEONEL</t>
@@ -2158,16 +2155,16 @@
         <v>21330051920053</v>
       </c>
       <c r="B2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
         <v>190</v>
       </c>
       <c r="E2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2178,16 +2175,16 @@
         <v>21330051920053</v>
       </c>
       <c r="B3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
         <v>190</v>
       </c>
       <c r="E3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2198,16 +2195,16 @@
         <v>22330051920053</v>
       </c>
       <c r="B4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
         <v>191</v>
       </c>
       <c r="E4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2218,16 +2215,16 @@
         <v>22330051920053</v>
       </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
         <v>191</v>
       </c>
       <c r="E5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2238,7 +2235,7 @@
         <v>22330051920054</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
         <v>185</v>
@@ -2247,7 +2244,7 @@
         <v>192</v>
       </c>
       <c r="E6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2258,7 +2255,7 @@
         <v>22330051920054</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
         <v>185</v>
@@ -2267,7 +2264,7 @@
         <v>192</v>
       </c>
       <c r="E7" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2287,7 +2284,7 @@
         <v>193</v>
       </c>
       <c r="E8" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2307,7 +2304,7 @@
         <v>193</v>
       </c>
       <c r="E9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2327,7 +2324,7 @@
         <v>194</v>
       </c>
       <c r="E10" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2347,7 +2344,7 @@
         <v>195</v>
       </c>
       <c r="E11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2358,16 +2355,16 @@
         <v>22330051920068</v>
       </c>
       <c r="B12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
         <v>196</v>
       </c>
       <c r="E12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -2378,16 +2375,16 @@
         <v>22330051920068</v>
       </c>
       <c r="B13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
         <v>196</v>
       </c>
       <c r="E13" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -2401,13 +2398,13 @@
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
         <v>197</v>
       </c>
       <c r="E14" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -2418,7 +2415,7 @@
         <v>22330051920081</v>
       </c>
       <c r="B15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C15" t="s">
         <v>189</v>
@@ -2427,7 +2424,7 @@
         <v>198</v>
       </c>
       <c r="E15" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -2438,16 +2435,16 @@
         <v>22330051920084</v>
       </c>
       <c r="B16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C16" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D16" t="s">
         <v>199</v>
       </c>
       <c r="E16" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -2458,16 +2455,16 @@
         <v>22330051920084</v>
       </c>
       <c r="B17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C17" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D17" t="s">
         <v>199</v>
       </c>
       <c r="E17" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -2478,16 +2475,16 @@
         <v>22330051920212</v>
       </c>
       <c r="B18" t="s">
-        <v>183</v>
+        <v>143</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
         <v>200</v>
       </c>
       <c r="E18" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -2498,16 +2495,16 @@
         <v>22330051920212</v>
       </c>
       <c r="B19" t="s">
-        <v>183</v>
+        <v>143</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
         <v>200</v>
       </c>
       <c r="E19" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -2521,13 +2518,13 @@
         <v>184</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D20" t="s">
         <v>201</v>
       </c>
       <c r="E20" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -2540,7 +2537,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2568,16 +2565,16 @@
         <v>22330051920034</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2588,16 +2585,16 @@
         <v>22330051920034</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2605,19 +2602,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920038</v>
+        <v>22330051920039</v>
       </c>
       <c r="B4" t="s">
-        <v>141</v>
+        <v>202</v>
       </c>
       <c r="C4" t="s">
         <v>207</v>
       </c>
       <c r="D4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2625,19 +2622,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920039</v>
+        <v>22330051920043</v>
       </c>
       <c r="B5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C5" t="s">
-        <v>208</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E5" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2654,10 +2651,10 @@
         <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2665,19 +2662,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920043</v>
+        <v>22330051920045</v>
       </c>
       <c r="B7" t="s">
-        <v>203</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2685,19 +2682,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920045</v>
+        <v>22330051920047</v>
       </c>
       <c r="B8" t="s">
+        <v>204</v>
+      </c>
+      <c r="C8" t="s">
         <v>49</v>
       </c>
-      <c r="C8" t="s">
-        <v>92</v>
-      </c>
       <c r="D8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2705,19 +2702,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920047</v>
+        <v>22330051920049</v>
       </c>
       <c r="B9" t="s">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>208</v>
       </c>
       <c r="D9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2725,19 +2722,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920049</v>
+        <v>22330051920189</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>205</v>
       </c>
       <c r="C10" t="s">
-        <v>209</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E10" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2745,19 +2742,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920051</v>
+        <v>22330051920189</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>205</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E11" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2765,61 +2762,21 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920189</v>
+        <v>22330051920191</v>
       </c>
       <c r="B12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920189</v>
-      </c>
-      <c r="B13" t="s">
-        <v>205</v>
-      </c>
-      <c r="C13" t="s">
-        <v>101</v>
-      </c>
-      <c r="D13" t="s">
-        <v>218</v>
-      </c>
-      <c r="E13" t="s">
-        <v>154</v>
-      </c>
-      <c r="F13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920191</v>
-      </c>
-      <c r="B14" t="s">
-        <v>206</v>
-      </c>
-      <c r="C14" t="s">
-        <v>69</v>
-      </c>
-      <c r="D14" t="s">
-        <v>219</v>
-      </c>
-      <c r="E14" t="s">
-        <v>153</v>
-      </c>
-      <c r="F14">
         <v>5</v>
       </c>
     </row>
@@ -2858,16 +2815,16 @@
         <v>22330051920110</v>
       </c>
       <c r="B2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2878,16 +2835,16 @@
         <v>22330051920128</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2898,16 +2855,16 @@
         <v>22330051920130</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D4" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2918,16 +2875,16 @@
         <v>22330051920130</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D5" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2941,13 +2898,13 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E6" t="s">
-        <v>164</v>
+        <v>231</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2961,13 +2918,13 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E7" t="s">
-        <v>233</v>
+        <v>166</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2978,16 +2935,16 @@
         <v>22330051920246</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D8" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2998,16 +2955,16 @@
         <v>22330051920352</v>
       </c>
       <c r="B9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3018,16 +2975,16 @@
         <v>22330051920352</v>
       </c>
       <c r="B10" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3041,13 +2998,13 @@
         <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D11" t="s">
-        <v>151</v>
+        <v>230</v>
       </c>
       <c r="E11" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3088,16 +3045,16 @@
         <v>20330051920069</v>
       </c>
       <c r="B2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3108,16 +3065,16 @@
         <v>20330051920069</v>
       </c>
       <c r="B3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3128,16 +3085,16 @@
         <v>21330051920001</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3148,16 +3105,16 @@
         <v>21330051920001</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3168,16 +3125,16 @@
         <v>21330051920153</v>
       </c>
       <c r="B6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3188,16 +3145,16 @@
         <v>21330051920164</v>
       </c>
       <c r="B7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3208,16 +3165,16 @@
         <v>21330051920165</v>
       </c>
       <c r="B8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C8" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D8" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3228,16 +3185,16 @@
         <v>21330051920166</v>
       </c>
       <c r="B9" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C9" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D9" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3248,16 +3205,16 @@
         <v>21330051920167</v>
       </c>
       <c r="B10" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C10" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D10" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E10" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3268,16 +3225,16 @@
         <v>21330051920167</v>
       </c>
       <c r="B11" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C11" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D11" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E11" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3288,16 +3245,16 @@
         <v>21330051920169</v>
       </c>
       <c r="B12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C12" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D12" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E12" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3308,16 +3265,16 @@
         <v>21330051920169</v>
       </c>
       <c r="B13" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C13" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D13" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E13" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -3331,13 +3288,13 @@
         <v>185</v>
       </c>
       <c r="C14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D14" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E14" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -3351,13 +3308,13 @@
         <v>185</v>
       </c>
       <c r="C15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D15" t="s">
+        <v>248</v>
+      </c>
+      <c r="E15" t="s">
         <v>250</v>
-      </c>
-      <c r="E15" t="s">
-        <v>252</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -3401,13 +3358,13 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3418,16 +3375,16 @@
         <v>21330051920253</v>
       </c>
       <c r="B3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C3" t="s">
         <v>255</v>
       </c>
-      <c r="C3" t="s">
-        <v>257</v>
-      </c>
       <c r="D3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3441,13 +3398,13 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3458,16 +3415,16 @@
         <v>21330051920287</v>
       </c>
       <c r="B5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3508,16 +3465,16 @@
         <v>21330051920331</v>
       </c>
       <c r="B2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" t="s">
         <v>264</v>
       </c>
-      <c r="C2" t="s">
-        <v>266</v>
-      </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3528,16 +3485,16 @@
         <v>21330051920347</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D3" t="s">
         <v>267</v>
       </c>
-      <c r="D3" t="s">
-        <v>269</v>
-      </c>
       <c r="E3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3548,16 +3505,16 @@
         <v>21330051920353</v>
       </c>
       <c r="B4" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C4" t="s">
+        <v>266</v>
+      </c>
+      <c r="D4" t="s">
         <v>268</v>
       </c>
-      <c r="D4" t="s">
-        <v>270</v>
-      </c>
       <c r="E4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3568,16 +3525,16 @@
         <v>21330051920353</v>
       </c>
       <c r="B5" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C5" t="s">
+        <v>266</v>
+      </c>
+      <c r="D5" t="s">
         <v>268</v>
       </c>
-      <c r="D5" t="s">
-        <v>270</v>
-      </c>
       <c r="E5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3618,16 +3575,16 @@
         <v>21330051920222</v>
       </c>
       <c r="B2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D2" t="s">
         <v>273</v>
       </c>
-      <c r="D2" t="s">
-        <v>275</v>
-      </c>
       <c r="E2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3638,16 +3595,16 @@
         <v>21330051920230</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
         <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3658,16 +3615,16 @@
         <v>21330051920235</v>
       </c>
       <c r="B4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3678,16 +3635,16 @@
         <v>21330051920249</v>
       </c>
       <c r="B5" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3698,16 +3655,16 @@
         <v>21330051920250</v>
       </c>
       <c r="B6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C6" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3748,16 +3705,16 @@
         <v>20330051920100</v>
       </c>
       <c r="B2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C2" t="s">
         <v>279</v>
       </c>
-      <c r="C2" t="s">
-        <v>281</v>
-      </c>
       <c r="D2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3768,16 +3725,16 @@
         <v>20330051920100</v>
       </c>
       <c r="B3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C3" t="s">
         <v>279</v>
       </c>
-      <c r="C3" t="s">
-        <v>281</v>
-      </c>
       <c r="D3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3791,13 +3748,13 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3811,13 +3768,13 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3828,16 +3785,16 @@
         <v>21330051920201</v>
       </c>
       <c r="B6" t="s">
+        <v>278</v>
+      </c>
+      <c r="C6" t="s">
         <v>280</v>
       </c>
-      <c r="C6" t="s">
-        <v>282</v>
-      </c>
       <c r="D6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E6" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3848,16 +3805,16 @@
         <v>21330051920205</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D7" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3868,16 +3825,16 @@
         <v>21330051920208</v>
       </c>
       <c r="B8" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3891,13 +3848,13 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D9" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E9" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3911,13 +3868,13 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E10" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3931,13 +3888,13 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D11" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3978,16 +3935,16 @@
         <v>19330051920208</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3998,16 +3955,16 @@
         <v>20330051920235</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4018,16 +3975,16 @@
         <v>20330051920235</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E4" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4041,13 +3998,13 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4061,13 +4018,13 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D6" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4078,16 +4035,16 @@
         <v>21330051920307</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E7" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4098,16 +4055,16 @@
         <v>21330051920316</v>
       </c>
       <c r="B8" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C8" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D8" t="s">
         <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4118,16 +4075,16 @@
         <v>21330051920321</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
         <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4138,16 +4095,16 @@
         <v>21330051920323</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E10" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4158,16 +4115,16 @@
         <v>21330051920323</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -4178,16 +4135,16 @@
         <v>21330051920326</v>
       </c>
       <c r="B12" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -4198,16 +4155,16 @@
         <v>21330051920337</v>
       </c>
       <c r="B13" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E13" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -4248,16 +4205,16 @@
         <v>23330051920180</v>
       </c>
       <c r="B2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C2" t="s">
         <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4268,16 +4225,16 @@
         <v>23330051920180</v>
       </c>
       <c r="B3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4288,13 +4245,13 @@
         <v>23330051920181</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E4" t="s">
         <v>30</v>
@@ -4308,13 +4265,13 @@
         <v>23330051920181</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E5" t="s">
         <v>42</v>
@@ -4331,13 +4288,13 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D6" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4351,13 +4308,13 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D7" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E7" t="s">
-        <v>140</v>
+        <v>30</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4371,13 +4328,13 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D8" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E8" t="s">
-        <v>140</v>
+        <v>319</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4391,13 +4348,13 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D9" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E9" t="s">
-        <v>321</v>
+        <v>142</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4408,13 +4365,13 @@
         <v>23330051920199</v>
       </c>
       <c r="B10" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C10" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E10" t="s">
         <v>29</v>
@@ -4428,13 +4385,13 @@
         <v>23330051920199</v>
       </c>
       <c r="B11" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C11" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D11" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E11" t="s">
         <v>42</v>
@@ -4448,13 +4405,13 @@
         <v>23330051920203</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D12" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E12" t="s">
         <v>42</v>
@@ -4468,13 +4425,13 @@
         <v>23330051920203</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D13" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E13" t="s">
         <v>30</v>
@@ -4488,13 +4445,13 @@
         <v>23330051920212</v>
       </c>
       <c r="B14" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C14" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D14" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E14" t="s">
         <v>30</v>
@@ -4508,16 +4465,16 @@
         <v>23330051920212</v>
       </c>
       <c r="B15" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C15" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D15" t="s">
+        <v>317</v>
+      </c>
+      <c r="E15" t="s">
         <v>319</v>
-      </c>
-      <c r="E15" t="s">
-        <v>321</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -4528,13 +4485,13 @@
         <v>23330051920329</v>
       </c>
       <c r="B16" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C16" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D16" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E16" t="s">
         <v>30</v>
@@ -4708,13 +4665,13 @@
         <v>23330051920215</v>
       </c>
       <c r="B2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E2" t="s">
         <v>31</v>
@@ -4728,13 +4685,13 @@
         <v>23330051920215</v>
       </c>
       <c r="B3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E3" t="s">
         <v>42</v>
@@ -4751,10 +4708,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E4" t="s">
         <v>31</v>
@@ -4771,13 +4728,13 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4788,16 +4745,16 @@
         <v>23330051920227</v>
       </c>
       <c r="B6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C6" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D6" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E6" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4808,13 +4765,13 @@
         <v>23330051920237</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D7" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E7" t="s">
         <v>42</v>
@@ -4828,13 +4785,13 @@
         <v>23330051920242</v>
       </c>
       <c r="B8" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C8" t="s">
         <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E8" t="s">
         <v>30</v>
@@ -4848,13 +4805,13 @@
         <v>23330051920244</v>
       </c>
       <c r="B9" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E9" t="s">
         <v>42</v>
@@ -4868,13 +4825,13 @@
         <v>23330051920254</v>
       </c>
       <c r="B10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E10" t="s">
         <v>42</v>
@@ -4888,13 +4845,13 @@
         <v>23330051920254</v>
       </c>
       <c r="B11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E11" t="s">
         <v>31</v>
@@ -4914,7 +4871,7 @@
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E12" t="s">
         <v>42</v>
@@ -4928,13 +4885,13 @@
         <v>23330051920275</v>
       </c>
       <c r="B13" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C13" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D13" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E13" t="s">
         <v>31</v>
@@ -4948,13 +4905,13 @@
         <v>23330051920275</v>
       </c>
       <c r="B14" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C14" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D14" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E14" t="s">
         <v>30</v>
@@ -4974,7 +4931,7 @@
         <v>19</v>
       </c>
       <c r="D15" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E15" t="s">
         <v>42</v>
@@ -4988,16 +4945,16 @@
         <v>23330051920280</v>
       </c>
       <c r="B16" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E16" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -5008,16 +4965,16 @@
         <v>23330051920328</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D17" t="s">
+        <v>339</v>
+      </c>
+      <c r="E17" t="s">
         <v>341</v>
-      </c>
-      <c r="E17" t="s">
-        <v>343</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -5028,16 +4985,16 @@
         <v>23330051920328</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D18" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E18" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -5048,13 +5005,13 @@
         <v>23330051920330</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
         <v>19</v>
       </c>
       <c r="D19" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E19" t="s">
         <v>42</v>
@@ -5098,16 +5055,16 @@
         <v>23330051920218</v>
       </c>
       <c r="B2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5118,16 +5075,16 @@
         <v>23330051920220</v>
       </c>
       <c r="B3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5138,16 +5095,16 @@
         <v>23330051920220</v>
       </c>
       <c r="B4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5158,16 +5115,16 @@
         <v>23330051920221</v>
       </c>
       <c r="B5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" t="s">
         <v>62</v>
       </c>
-      <c r="C5" t="s">
-        <v>59</v>
-      </c>
       <c r="D5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5178,16 +5135,16 @@
         <v>23330051920222</v>
       </c>
       <c r="B6" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C6" t="s">
         <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E6" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5198,13 +5155,13 @@
         <v>23330051920222</v>
       </c>
       <c r="B7" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C7" t="s">
         <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E7" t="s">
         <v>30</v>
@@ -5218,16 +5175,16 @@
         <v>23330051920224</v>
       </c>
       <c r="B8" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C8" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D8" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E8" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5238,13 +5195,13 @@
         <v>23330051920229</v>
       </c>
       <c r="B9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E9" t="s">
         <v>30</v>
@@ -5258,16 +5215,16 @@
         <v>23330051920229</v>
       </c>
       <c r="B10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E10" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -5278,16 +5235,16 @@
         <v>23330051920230</v>
       </c>
       <c r="B11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E11" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -5298,16 +5255,16 @@
         <v>23330051920231</v>
       </c>
       <c r="B12" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C12" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D12" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E12" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -5318,16 +5275,16 @@
         <v>23330051920243</v>
       </c>
       <c r="B13" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C13" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D13" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E13" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -5338,13 +5295,13 @@
         <v>23330051920251</v>
       </c>
       <c r="B14" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E14" t="s">
         <v>31</v>
@@ -5358,16 +5315,16 @@
         <v>23330051920251</v>
       </c>
       <c r="B15" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C15" t="s">
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E15" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -5378,16 +5335,16 @@
         <v>23330051920253</v>
       </c>
       <c r="B16" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C16" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D16" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E16" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -5401,13 +5358,13 @@
         <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D17" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E17" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -5448,16 +5405,16 @@
         <v>23330051920299</v>
       </c>
       <c r="B2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C2" t="s">
         <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5468,13 +5425,13 @@
         <v>23330051920299</v>
       </c>
       <c r="B3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E3" t="s">
         <v>30</v>
@@ -5488,16 +5445,16 @@
         <v>23330051920310</v>
       </c>
       <c r="B4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C4" t="s">
-        <v>141</v>
+        <v>366</v>
       </c>
       <c r="D4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5508,13 +5465,13 @@
         <v>23330051920310</v>
       </c>
       <c r="B5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C5" t="s">
-        <v>141</v>
+        <v>366</v>
       </c>
       <c r="D5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E5" t="s">
         <v>42</v>
@@ -5528,16 +5485,16 @@
         <v>23330051920311</v>
       </c>
       <c r="B6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5548,16 +5505,16 @@
         <v>23330051920311</v>
       </c>
       <c r="B7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E7" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5574,10 +5531,10 @@
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5588,16 +5545,16 @@
         <v>23330051920336</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E9" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5611,10 +5568,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E10" t="s">
         <v>42</v>
@@ -5628,16 +5585,16 @@
         <v>23330051920356</v>
       </c>
       <c r="B11" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C11" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E11" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -5648,16 +5605,16 @@
         <v>23330051920363</v>
       </c>
       <c r="B12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" t="s">
         <v>92</v>
       </c>
-      <c r="C12" t="s">
-        <v>90</v>
-      </c>
       <c r="D12" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E12" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -5668,13 +5625,13 @@
         <v>23330051920363</v>
       </c>
       <c r="B13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" t="s">
         <v>92</v>
       </c>
-      <c r="C13" t="s">
-        <v>90</v>
-      </c>
       <c r="D13" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E13" t="s">
         <v>42</v>
@@ -5718,13 +5675,13 @@
         <v>23330051920302</v>
       </c>
       <c r="B2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C2" t="s">
+        <v>373</v>
+      </c>
+      <c r="D2" t="s">
         <v>374</v>
-      </c>
-      <c r="D2" t="s">
-        <v>375</v>
       </c>
       <c r="E2" t="s">
         <v>29</v>
@@ -5738,13 +5695,13 @@
         <v>23330051920302</v>
       </c>
       <c r="B3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D3" t="s">
         <v>374</v>
-      </c>
-      <c r="D3" t="s">
-        <v>375</v>
       </c>
       <c r="E3" t="s">
         <v>42</v>
@@ -5758,13 +5715,13 @@
         <v>23330051920303</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E4" t="s">
         <v>42</v>
@@ -5781,13 +5738,13 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E5" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5828,16 +5785,16 @@
         <v>19330051920067</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5848,16 +5805,16 @@
         <v>19330051920067</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5868,16 +5825,16 @@
         <v>21330051920007</v>
       </c>
       <c r="B4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5888,16 +5845,16 @@
         <v>21330051920197</v>
       </c>
       <c r="B5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C5" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5911,13 +5868,13 @@
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5928,16 +5885,16 @@
         <v>22330051920190</v>
       </c>
       <c r="B7" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C7" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5948,16 +5905,16 @@
         <v>22330051920190</v>
       </c>
       <c r="B8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C8" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D8" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5968,16 +5925,16 @@
         <v>22330051920192</v>
       </c>
       <c r="B9" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5988,16 +5945,16 @@
         <v>22330051920193</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E10" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6008,16 +5965,16 @@
         <v>22330051920200</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E11" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6031,13 +5988,13 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E12" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -6051,13 +6008,13 @@
         <v>185</v>
       </c>
       <c r="C13" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D13" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -6068,16 +6025,16 @@
         <v>22330051920359</v>
       </c>
       <c r="B14" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C14" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E14" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -6088,16 +6045,16 @@
         <v>22330051920363</v>
       </c>
       <c r="B15" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C15" t="s">
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E15" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -6108,16 +6065,16 @@
         <v>22330051920378</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D16" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E16" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -6128,16 +6085,16 @@
         <v>22330051920378</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D17" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E17" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -6154,10 +6111,10 @@
         <v>186</v>
       </c>
       <c r="D18" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E18" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -6201,13 +6158,13 @@
         <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6221,13 +6178,13 @@
         <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6238,16 +6195,16 @@
         <v>22330051920236</v>
       </c>
       <c r="B4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6258,16 +6215,16 @@
         <v>22330051920236</v>
       </c>
       <c r="B5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6278,16 +6235,16 @@
         <v>22330051920237</v>
       </c>
       <c r="B6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6298,16 +6255,16 @@
         <v>22330051920240</v>
       </c>
       <c r="B7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E7" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6318,16 +6275,16 @@
         <v>22330051920240</v>
       </c>
       <c r="B8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D8" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6338,16 +6295,16 @@
         <v>22330051920256</v>
       </c>
       <c r="B9" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D9" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6361,13 +6318,13 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D10" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E10" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6381,13 +6338,13 @@
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E11" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6404,10 +6361,10 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -6424,10 +6381,10 @@
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -6471,13 +6428,13 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6491,13 +6448,13 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E3" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6508,16 +6465,16 @@
         <v>22330051920273</v>
       </c>
       <c r="B4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6528,16 +6485,16 @@
         <v>22330051920273</v>
       </c>
       <c r="B5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D5" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6548,16 +6505,16 @@
         <v>22330051920276</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6571,13 +6528,13 @@
         <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E7" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6588,16 +6545,16 @@
         <v>22330051920286</v>
       </c>
       <c r="B8" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D8" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E8" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6614,7 +6571,7 @@
         <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E9" t="s">
         <v>165</v>
@@ -6634,10 +6591,10 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E10" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6684,10 +6641,10 @@
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6704,10 +6661,10 @@
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6718,16 +6675,16 @@
         <v>21330051920002</v>
       </c>
       <c r="B4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6741,13 +6698,13 @@
         <v>186</v>
       </c>
       <c r="C5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D5" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6761,13 +6718,13 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6781,13 +6738,13 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6798,16 +6755,16 @@
         <v>22330051920394</v>
       </c>
       <c r="B8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6818,16 +6775,16 @@
         <v>22330051920394</v>
       </c>
       <c r="B9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6868,16 +6825,16 @@
         <v>22330051920298</v>
       </c>
       <c r="B2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D2" t="s">
         <v>429</v>
       </c>
-      <c r="C2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D2" t="s">
-        <v>430</v>
-      </c>
       <c r="E2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6891,13 +6848,13 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6908,16 +6865,16 @@
         <v>22330051920314</v>
       </c>
       <c r="B4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
+        <v>431</v>
+      </c>
+      <c r="E4" t="s">
         <v>432</v>
-      </c>
-      <c r="E4" t="s">
-        <v>433</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6958,16 +6915,16 @@
         <v>20330051920018</v>
       </c>
       <c r="B2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D2" t="s">
         <v>436</v>
       </c>
-      <c r="D2" t="s">
-        <v>437</v>
-      </c>
       <c r="E2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6984,10 +6941,10 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6998,16 +6955,16 @@
         <v>20330051920366</v>
       </c>
       <c r="B4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E4" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7018,16 +6975,16 @@
         <v>20330051920366</v>
       </c>
       <c r="B5" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7038,16 +6995,16 @@
         <v>20330051920367</v>
       </c>
       <c r="B6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7058,16 +7015,16 @@
         <v>21330051920003</v>
       </c>
       <c r="B7" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C7" t="s">
         <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7084,10 +7041,10 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7104,10 +7061,10 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E9" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7118,16 +7075,16 @@
         <v>21330051920015</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E10" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7138,16 +7095,16 @@
         <v>21330051920023</v>
       </c>
       <c r="B11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E11" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -7158,16 +7115,16 @@
         <v>21330051920023</v>
       </c>
       <c r="B12" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E12" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -7180,7 +7137,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7211,10 +7168,10 @@
         <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
         <v>30</v>
@@ -7225,16 +7182,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>23330051920065</v>
+        <v>23330051920052</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
         <v>30</v>
@@ -7245,7 +7202,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>23330051920067</v>
+        <v>23330051920052</v>
       </c>
       <c r="B4" t="s">
         <v>44</v>
@@ -7254,10 +7211,10 @@
         <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7265,16 +7222,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>23330051920072</v>
+        <v>23330051920065</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
         <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
         <v>30</v>
@@ -7285,21 +7242,61 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>23330051920246</v>
+        <v>23330051920067</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
         <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
         <v>30</v>
       </c>
       <c r="F6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>23330051920072</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>23330051920246</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8">
         <v>5</v>
       </c>
     </row>
@@ -7341,13 +7338,13 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7361,13 +7358,13 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7378,16 +7375,16 @@
         <v>21330051920082</v>
       </c>
       <c r="B4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E4" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7398,16 +7395,16 @@
         <v>21330051920089</v>
       </c>
       <c r="B5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C5" t="s">
         <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7418,16 +7415,16 @@
         <v>21330051920092</v>
       </c>
       <c r="B6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7438,16 +7435,16 @@
         <v>21330051920093</v>
       </c>
       <c r="B7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7458,16 +7455,16 @@
         <v>21330051920097</v>
       </c>
       <c r="B8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C8" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7478,16 +7475,16 @@
         <v>21330051920099</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7498,16 +7495,16 @@
         <v>21330051920100</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E10" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7518,16 +7515,16 @@
         <v>21330051920101</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -7541,13 +7538,13 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -7561,13 +7558,13 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E13" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -7578,16 +7575,16 @@
         <v>21330051920103</v>
       </c>
       <c r="B14" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E14" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -7598,16 +7595,16 @@
         <v>21330051920107</v>
       </c>
       <c r="B15" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D15" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E15" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -7618,16 +7615,16 @@
         <v>21330051920107</v>
       </c>
       <c r="B16" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D16" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E16" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -7641,13 +7638,13 @@
         <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D17" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E17" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -7658,16 +7655,16 @@
         <v>21330051920305</v>
       </c>
       <c r="B18" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C18" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D18" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E18" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -7678,16 +7675,16 @@
         <v>21330051920305</v>
       </c>
       <c r="B19" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C19" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D19" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E19" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -7728,16 +7725,16 @@
         <v>19330051920241</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7748,16 +7745,16 @@
         <v>21330051920111</v>
       </c>
       <c r="B3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7768,13 +7765,13 @@
         <v>21330051920111</v>
       </c>
       <c r="B4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E4" t="s">
         <v>251</v>
@@ -7788,16 +7785,16 @@
         <v>21330051920120</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7808,16 +7805,16 @@
         <v>21330051920123</v>
       </c>
       <c r="B6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E6" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7828,16 +7825,16 @@
         <v>21330051920125</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7848,16 +7845,16 @@
         <v>21330051920125</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E8" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7868,7 +7865,7 @@
         <v>21330051920126</v>
       </c>
       <c r="B9" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C9" t="s">
         <v>33</v>
@@ -7877,7 +7874,7 @@
         <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7888,7 +7885,7 @@
         <v>21330051920126</v>
       </c>
       <c r="B10" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C10" t="s">
         <v>33</v>
@@ -7897,7 +7894,7 @@
         <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7908,16 +7905,16 @@
         <v>21330051920132</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D11" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -7958,16 +7955,16 @@
         <v>21330051920031</v>
       </c>
       <c r="B2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7978,16 +7975,16 @@
         <v>21330051920031</v>
       </c>
       <c r="B3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E3" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7998,16 +7995,16 @@
         <v>21330051920035</v>
       </c>
       <c r="B4" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8018,16 +8015,16 @@
         <v>21330051920036</v>
       </c>
       <c r="B5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8038,16 +8035,16 @@
         <v>21330051920046</v>
       </c>
       <c r="B6" t="s">
-        <v>141</v>
+        <v>366</v>
       </c>
       <c r="C6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D6" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E6" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -8058,16 +8055,16 @@
         <v>21330051920048</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D7" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E7" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -8078,16 +8075,16 @@
         <v>21330051920057</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
         <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -8098,16 +8095,16 @@
         <v>21330051920057</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E9" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -8118,16 +8115,16 @@
         <v>21330051920062</v>
       </c>
       <c r="B10" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E10" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -8138,16 +8135,16 @@
         <v>21330051920063</v>
       </c>
       <c r="B11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C11" t="s">
         <v>123</v>
       </c>
-      <c r="C11" t="s">
-        <v>121</v>
-      </c>
       <c r="D11" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -8158,16 +8155,16 @@
         <v>21330051920063</v>
       </c>
       <c r="B12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" t="s">
         <v>123</v>
       </c>
-      <c r="C12" t="s">
-        <v>121</v>
-      </c>
       <c r="D12" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -8178,16 +8175,16 @@
         <v>21330051920065</v>
       </c>
       <c r="B13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C13" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E13" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -8201,13 +8198,13 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D14" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E14" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -8221,13 +8218,13 @@
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D15" t="s">
+        <v>492</v>
+      </c>
+      <c r="E15" t="s">
         <v>493</v>
-      </c>
-      <c r="E15" t="s">
-        <v>494</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -8271,13 +8268,13 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8291,13 +8288,13 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8308,16 +8305,16 @@
         <v>21330051920148</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8358,13 +8355,13 @@
         <v>23330051920077</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
         <v>30</v>
@@ -8378,13 +8375,13 @@
         <v>23330051920079</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
         <v>30</v>
@@ -8398,13 +8395,13 @@
         <v>23330051920081</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
         <v>29</v>
@@ -8418,13 +8415,13 @@
         <v>23330051920082</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
         <v>30</v>
@@ -8438,13 +8435,13 @@
         <v>23330051920083</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
         <v>30</v>
@@ -8458,13 +8455,13 @@
         <v>23330051920084</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
         <v>30</v>
@@ -8478,13 +8475,13 @@
         <v>23330051920086</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
         <v>30</v>
@@ -8501,10 +8498,10 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
         <v>30</v>
@@ -8521,10 +8518,10 @@
         <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E10" t="s">
         <v>30</v>
@@ -8541,10 +8538,10 @@
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E11" t="s">
         <v>29</v>
@@ -8558,13 +8555,13 @@
         <v>23330051920104</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E12" t="s">
         <v>30</v>
@@ -8578,13 +8575,13 @@
         <v>23330051920105</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D13" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
         <v>30</v>
@@ -8598,13 +8595,13 @@
         <v>23330051920105</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E14" t="s">
         <v>29</v>
@@ -8618,13 +8615,13 @@
         <v>23330051920112</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s">
         <v>30</v>
@@ -8668,16 +8665,16 @@
         <v>23330051920118</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
         <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8688,16 +8685,16 @@
         <v>23330051920118</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
         <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8708,13 +8705,13 @@
         <v>23330051920121</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E4" t="s">
         <v>30</v>
@@ -8728,13 +8725,13 @@
         <v>23330051920123</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
         <v>42</v>
@@ -8748,13 +8745,13 @@
         <v>23330051920123</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
         <v>30</v>
@@ -8771,10 +8768,10 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
         <v>30</v>
@@ -8788,13 +8785,13 @@
         <v>23330051920133</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
         <v>30</v>
@@ -8814,7 +8811,7 @@
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E9" t="s">
         <v>30</v>
@@ -8828,13 +8825,13 @@
         <v>23330051920139</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
         <v>29</v>
@@ -8848,13 +8845,13 @@
         <v>23330051920139</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E11" t="s">
         <v>30</v>
@@ -8871,10 +8868,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E12" t="s">
         <v>30</v>
@@ -8888,13 +8885,13 @@
         <v>23330051920142</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E13" t="s">
         <v>30</v>
@@ -8908,13 +8905,13 @@
         <v>23330051920144</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E14" t="s">
         <v>30</v>
@@ -8928,13 +8925,13 @@
         <v>23330051920145</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E15" t="s">
         <v>30</v>
@@ -8951,10 +8948,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E16" t="s">
         <v>30</v>
@@ -8971,10 +8968,10 @@
         <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E17" t="s">
         <v>30</v>
@@ -8988,13 +8985,13 @@
         <v>23330051920255</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E18" t="s">
         <v>30</v>
@@ -9008,13 +9005,13 @@
         <v>23330051920315</v>
       </c>
       <c r="B19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E19" t="s">
         <v>30</v>
@@ -9058,13 +9055,13 @@
         <v>23330051920154</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E2" t="s">
         <v>29</v>
@@ -9078,13 +9075,13 @@
         <v>23330051920154</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E3" t="s">
         <v>30</v>
@@ -9098,13 +9095,13 @@
         <v>23330051920155</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E4" t="s">
         <v>30</v>
@@ -9118,13 +9115,13 @@
         <v>23330051920155</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E5" t="s">
         <v>29</v>
@@ -9144,7 +9141,7 @@
         <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E6" t="s">
         <v>30</v>
@@ -9164,7 +9161,7 @@
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E7" t="s">
         <v>30</v>
@@ -9181,13 +9178,13 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -9201,10 +9198,10 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E9" t="s">
         <v>42</v>
@@ -9218,13 +9215,13 @@
         <v>23330051920165</v>
       </c>
       <c r="B10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E10" t="s">
         <v>30</v>
@@ -9238,13 +9235,13 @@
         <v>23330051920166</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E11" t="s">
         <v>30</v>
@@ -9258,13 +9255,13 @@
         <v>23330051920166</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E12" t="s">
         <v>29</v>
@@ -9278,13 +9275,13 @@
         <v>23330051920167</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C13" t="s">
         <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E13" t="s">
         <v>30</v>
@@ -9298,13 +9295,13 @@
         <v>23330051920169</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D14" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E14" t="s">
         <v>30</v>
@@ -9318,13 +9315,13 @@
         <v>23330051920169</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E15" t="s">
         <v>29</v>
@@ -9338,13 +9335,13 @@
         <v>23330051920170</v>
       </c>
       <c r="B16" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D16" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E16" t="s">
         <v>30</v>
@@ -9358,13 +9355,13 @@
         <v>23330051920171</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E17" t="s">
         <v>30</v>
@@ -9378,16 +9375,16 @@
         <v>23330051920171</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -9398,16 +9395,16 @@
         <v>23330051920174</v>
       </c>
       <c r="B19" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C19" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D19" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E19" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -9418,13 +9415,13 @@
         <v>23330051920354</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D20" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E20" t="s">
         <v>30</v>
@@ -9468,16 +9465,16 @@
         <v>22330051920006</v>
       </c>
       <c r="B2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -9488,16 +9485,16 @@
         <v>22330051920010</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -9511,13 +9508,13 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -9528,16 +9525,16 @@
         <v>22330051920015</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -9545,19 +9542,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920018</v>
+        <v>22330051920017</v>
       </c>
       <c r="B6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -9568,16 +9565,16 @@
         <v>22330051920173</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E7" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -9621,13 +9618,13 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E2" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -9641,13 +9638,13 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E3" t="s">
         <v>156</v>
-      </c>
-      <c r="D3" t="s">
-        <v>158</v>
-      </c>
-      <c r="E3" t="s">
-        <v>163</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -9658,16 +9655,16 @@
         <v>22330051920108</v>
       </c>
       <c r="B4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
         <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -9678,16 +9675,16 @@
         <v>22330051920108</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
         <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -9698,16 +9695,16 @@
         <v>22330051920114</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -9718,16 +9715,16 @@
         <v>22330051920116</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -9738,16 +9735,16 @@
         <v>22330051920122</v>
       </c>
       <c r="B8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C8" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E8" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -9788,16 +9785,16 @@
         <v>22330051920150</v>
       </c>
       <c r="B2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -9808,16 +9805,16 @@
         <v>22330051920153</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -9828,16 +9825,16 @@
         <v>22330051920157</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>169</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -9851,13 +9848,13 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -9868,16 +9865,16 @@
         <v>22330051920426</v>
       </c>
       <c r="B6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F6">
         <v>5</v>

--- a/Rescatables20231.xlsx
+++ b/Rescatables20231.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="502">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -1248,7 +1248,10 @@
     <t>MANTIENE LOS MOTORES DE CA Y CC</t>
   </si>
   <si>
-    <t>DECTOR</t>
+    <t>ZAVALA</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
   </si>
   <si>
     <t>ESCOBAR</t>
@@ -1257,13 +1260,22 @@
     <t>MENA</t>
   </si>
   <si>
+    <t>DELGADO</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
     <t>TETLACTLE</t>
   </si>
   <si>
     <t>ANGELES</t>
   </si>
   <si>
-    <t>KEVIN ALEXIS</t>
+    <t>AXEL GAEL</t>
+  </si>
+  <si>
+    <t>FERNANDA MARGARITA</t>
   </si>
   <si>
     <t>LUZ ALONDRA</t>
@@ -2964,7 +2976,7 @@
         <v>229</v>
       </c>
       <c r="E9" t="s">
-        <v>156</v>
+        <v>231</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2984,7 +2996,7 @@
         <v>229</v>
       </c>
       <c r="E10" t="s">
-        <v>231</v>
+        <v>156</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4604,7 +4616,7 @@
         <v>41</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4624,7 +4636,7 @@
         <v>41</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6158,10 +6170,10 @@
         <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E2" t="s">
         <v>231</v>
@@ -6178,10 +6190,10 @@
         <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D3" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E3" t="s">
         <v>166</v>
@@ -6192,19 +6204,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920236</v>
+        <v>22330051920176</v>
       </c>
       <c r="B4" t="s">
         <v>400</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>404</v>
       </c>
       <c r="D4" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E4" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6212,19 +6224,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920236</v>
+        <v>22330051920233</v>
       </c>
       <c r="B5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>405</v>
       </c>
       <c r="D5" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="E5" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6235,13 +6247,13 @@
         <v>22330051920237</v>
       </c>
       <c r="B6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E6" t="s">
         <v>165</v>
@@ -6261,7 +6273,7 @@
         <v>348</v>
       </c>
       <c r="D7" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E7" t="s">
         <v>156</v>
@@ -6281,7 +6293,7 @@
         <v>348</v>
       </c>
       <c r="D8" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E8" t="s">
         <v>167</v>
@@ -6298,10 +6310,10 @@
         <v>157</v>
       </c>
       <c r="C9" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D9" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="E9" t="s">
         <v>165</v>
@@ -6321,7 +6333,7 @@
         <v>280</v>
       </c>
       <c r="D10" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E10" t="s">
         <v>165</v>
@@ -6341,7 +6353,7 @@
         <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="E11" t="s">
         <v>231</v>
@@ -6361,7 +6373,7 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="E12" t="s">
         <v>167</v>
@@ -6381,7 +6393,7 @@
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E13" t="s">
         <v>156</v>
@@ -6431,7 +6443,7 @@
         <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E2" t="s">
         <v>156</v>
@@ -6451,7 +6463,7 @@
         <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E3" t="s">
         <v>167</v>
@@ -6471,7 +6483,7 @@
         <v>321</v>
       </c>
       <c r="D4" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E4" t="s">
         <v>165</v>
@@ -6491,7 +6503,7 @@
         <v>321</v>
       </c>
       <c r="D5" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E5" t="s">
         <v>167</v>
@@ -6528,10 +6540,10 @@
         <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="D7" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="E7" t="s">
         <v>156</v>
@@ -6551,7 +6563,7 @@
         <v>183</v>
       </c>
       <c r="D8" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E8" t="s">
         <v>156</v>
@@ -6571,7 +6583,7 @@
         <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E9" t="s">
         <v>165</v>
@@ -6591,7 +6603,7 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E10" t="s">
         <v>167</v>
@@ -6641,10 +6653,10 @@
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6661,10 +6673,10 @@
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E3" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6675,13 +6687,13 @@
         <v>21330051920002</v>
       </c>
       <c r="B4" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C4" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D4" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="E4" t="s">
         <v>165</v>
@@ -6701,7 +6713,7 @@
         <v>232</v>
       </c>
       <c r="D5" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E5" t="s">
         <v>156</v>
@@ -6718,10 +6730,10 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="D6" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E6" t="s">
         <v>156</v>
@@ -6738,10 +6750,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="D7" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E7" t="s">
         <v>167</v>
@@ -6758,7 +6770,7 @@
         <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="D8" t="s">
         <v>80</v>
@@ -6778,7 +6790,7 @@
         <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="D9" t="s">
         <v>80</v>
@@ -6825,13 +6837,13 @@
         <v>22330051920298</v>
       </c>
       <c r="B2" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C2" t="s">
         <v>271</v>
       </c>
       <c r="D2" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E2" t="s">
         <v>167</v>
@@ -6851,7 +6863,7 @@
         <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E3" t="s">
         <v>156</v>
@@ -6871,10 +6883,10 @@
         <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="E4" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6918,10 +6930,10 @@
         <v>144</v>
       </c>
       <c r="C2" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="D2" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E2" t="s">
         <v>249</v>
@@ -6941,7 +6953,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="E3" t="s">
         <v>252</v>
@@ -6955,13 +6967,13 @@
         <v>20330051920366</v>
       </c>
       <c r="B4" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E4" t="s">
         <v>269</v>
@@ -6975,13 +6987,13 @@
         <v>20330051920366</v>
       </c>
       <c r="B5" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E5" t="s">
         <v>252</v>
@@ -6995,13 +7007,13 @@
         <v>20330051920367</v>
       </c>
       <c r="B6" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="E6" t="s">
         <v>252</v>
@@ -7021,7 +7033,7 @@
         <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E7" t="s">
         <v>249</v>
@@ -7041,7 +7053,7 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="E8" t="s">
         <v>250</v>
@@ -7061,10 +7073,10 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="E9" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7081,7 +7093,7 @@
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E10" t="s">
         <v>250</v>
@@ -7095,13 +7107,13 @@
         <v>21330051920023</v>
       </c>
       <c r="B11" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E11" t="s">
         <v>269</v>
@@ -7115,13 +7127,13 @@
         <v>21330051920023</v>
       </c>
       <c r="B12" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E12" t="s">
         <v>250</v>
@@ -7194,7 +7206,7 @@
         <v>54</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7214,7 +7226,7 @@
         <v>54</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7338,7 +7350,7 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="D2" t="s">
         <v>87</v>
@@ -7378,10 +7390,10 @@
         <v>144</v>
       </c>
       <c r="C4" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="D4" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E4" t="s">
         <v>269</v>
@@ -7401,7 +7413,7 @@
         <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E5" t="s">
         <v>249</v>
@@ -7415,13 +7427,13 @@
         <v>21330051920092</v>
       </c>
       <c r="B6" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C6" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="D6" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="E6" t="s">
         <v>249</v>
@@ -7435,13 +7447,13 @@
         <v>21330051920093</v>
       </c>
       <c r="B7" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E7" t="s">
         <v>249</v>
@@ -7458,10 +7470,10 @@
         <v>217</v>
       </c>
       <c r="C8" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D8" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="E8" t="s">
         <v>249</v>
@@ -7481,7 +7493,7 @@
         <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E9" t="s">
         <v>249</v>
@@ -7501,7 +7513,7 @@
         <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="E10" t="s">
         <v>249</v>
@@ -7521,7 +7533,7 @@
         <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="E11" t="s">
         <v>249</v>
@@ -7541,7 +7553,7 @@
         <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="E12" t="s">
         <v>249</v>
@@ -7561,7 +7573,7 @@
         <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="E13" t="s">
         <v>251</v>
@@ -7575,13 +7587,13 @@
         <v>21330051920103</v>
       </c>
       <c r="B14" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C14" t="s">
         <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="E14" t="s">
         <v>249</v>
@@ -7595,13 +7607,13 @@
         <v>21330051920107</v>
       </c>
       <c r="B15" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C15" t="s">
         <v>171</v>
       </c>
       <c r="D15" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E15" t="s">
         <v>269</v>
@@ -7615,13 +7627,13 @@
         <v>21330051920107</v>
       </c>
       <c r="B16" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C16" t="s">
         <v>171</v>
       </c>
       <c r="D16" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E16" t="s">
         <v>249</v>
@@ -7638,10 +7650,10 @@
         <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="D17" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="E17" t="s">
         <v>249</v>
@@ -7655,13 +7667,13 @@
         <v>21330051920305</v>
       </c>
       <c r="B18" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C18" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D18" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="E18" t="s">
         <v>249</v>
@@ -7675,13 +7687,13 @@
         <v>21330051920305</v>
       </c>
       <c r="B19" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C19" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D19" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="E19" t="s">
         <v>251</v>
@@ -7697,7 +7709,7 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7731,10 +7743,10 @@
         <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="E2" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7751,7 +7763,7 @@
         <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="E3" t="s">
         <v>249</v>
@@ -7771,7 +7783,7 @@
         <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="E4" t="s">
         <v>251</v>
@@ -7782,19 +7794,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920120</v>
+        <v>21330051920114</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>280</v>
       </c>
       <c r="D5" t="s">
-        <v>475</v>
+        <v>245</v>
       </c>
       <c r="E5" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7802,19 +7814,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920123</v>
+        <v>21330051920120</v>
       </c>
       <c r="B6" t="s">
-        <v>469</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>471</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>260</v>
+        <v>479</v>
       </c>
       <c r="E6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7822,19 +7834,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920125</v>
+        <v>21330051920123</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>473</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>475</v>
       </c>
       <c r="D7" t="s">
-        <v>476</v>
+        <v>260</v>
       </c>
       <c r="E7" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7851,10 +7863,10 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E8" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7862,16 +7874,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920126</v>
+        <v>21330051920125</v>
       </c>
       <c r="B9" t="s">
-        <v>470</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>480</v>
       </c>
       <c r="E9" t="s">
         <v>251</v>
@@ -7885,7 +7897,7 @@
         <v>21330051920126</v>
       </c>
       <c r="B10" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C10" t="s">
         <v>33</v>
@@ -7894,7 +7906,7 @@
         <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7902,21 +7914,41 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
+        <v>21330051920126</v>
+      </c>
+      <c r="B11" t="s">
+        <v>474</v>
+      </c>
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s">
+        <v>269</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
         <v>21330051920132</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" t="s">
         <v>50</v>
       </c>
-      <c r="C11" t="s">
-        <v>472</v>
-      </c>
-      <c r="D11" t="s">
-        <v>477</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="C12" t="s">
+        <v>476</v>
+      </c>
+      <c r="D12" t="s">
+        <v>481</v>
+      </c>
+      <c r="E12" t="s">
         <v>251</v>
       </c>
-      <c r="F11">
+      <c r="F12">
         <v>5</v>
       </c>
     </row>
@@ -7961,7 +7993,7 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="E2" t="s">
         <v>249</v>
@@ -7981,10 +8013,10 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="E3" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8001,7 +8033,7 @@
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E4" t="s">
         <v>251</v>
@@ -8015,13 +8047,13 @@
         <v>21330051920036</v>
       </c>
       <c r="B5" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="E5" t="s">
         <v>251</v>
@@ -8038,10 +8070,10 @@
         <v>366</v>
       </c>
       <c r="C6" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="D6" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E6" t="s">
         <v>251</v>
@@ -8061,7 +8093,7 @@
         <v>170</v>
       </c>
       <c r="D7" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="E7" t="s">
         <v>251</v>
@@ -8081,10 +8113,10 @@
         <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="E8" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -8101,7 +8133,7 @@
         <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="E9" t="s">
         <v>251</v>
@@ -8115,13 +8147,13 @@
         <v>21330051920062</v>
       </c>
       <c r="B10" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C10" t="s">
         <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="E10" t="s">
         <v>251</v>
@@ -8141,7 +8173,7 @@
         <v>123</v>
       </c>
       <c r="D11" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="E11" t="s">
         <v>251</v>
@@ -8161,7 +8193,7 @@
         <v>123</v>
       </c>
       <c r="D12" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="E12" t="s">
         <v>249</v>
@@ -8178,7 +8210,7 @@
         <v>183</v>
       </c>
       <c r="C13" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="D13" t="s">
         <v>79</v>
@@ -8198,13 +8230,13 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="D14" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="E14" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -8218,13 +8250,13 @@
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="D15" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="E15" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -8268,10 +8300,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D2" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="E2" t="s">
         <v>251</v>
@@ -8288,10 +8320,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D3" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="E3" t="s">
         <v>249</v>
@@ -8308,10 +8340,10 @@
         <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="D4" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E4" t="s">
         <v>249</v>

--- a/Rescatables20231.xlsx
+++ b/Rescatables20231.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="488">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -666,15 +666,9 @@
     <t>JENKINS</t>
   </si>
   <si>
-    <t>MELCHOR</t>
-  </si>
-  <si>
     <t>ZEPEDA</t>
   </si>
   <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
     <t>CARLOS YAEL</t>
   </si>
   <si>
@@ -690,438 +684,405 @@
     <t>ABIEL NEFTALI</t>
   </si>
   <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
     <t>ARTHUR RICHARD</t>
   </si>
   <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>PIÑA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>ODALIS SOFIA</t>
+  </si>
+  <si>
+    <t>KARENT LILIANA</t>
+  </si>
+  <si>
+    <t>ABIGAIL ANTONIA</t>
+  </si>
+  <si>
+    <t>ZURI GABRIELA</t>
+  </si>
+  <si>
+    <t>LUISA MARIA</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
+    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS BACTERIOLÓGICAS</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>MAYO</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>NERI</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>AYLIN MELISSA</t>
+  </si>
+  <si>
     <t>ALDAHIR</t>
   </si>
   <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>PIÑA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>ODALIS SOFIA</t>
-  </si>
-  <si>
-    <t>KARENT LILIANA</t>
-  </si>
-  <si>
-    <t>ABIGAIL ANTONIA</t>
-  </si>
-  <si>
-    <t>ZURI GABRIELA</t>
-  </si>
-  <si>
-    <t>LUISA MARIA</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
-  </si>
-  <si>
-    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS BACTERIOLÓGICAS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>LOYO</t>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>LUIS OMAR</t>
+  </si>
+  <si>
+    <t>CHARBEL</t>
+  </si>
+  <si>
+    <t>CANDIDO</t>
+  </si>
+  <si>
+    <t>CIENCIA, TECNOLOGÍA, SOCIEDAD Y VALORES</t>
+  </si>
+  <si>
+    <t>FÍSICA II</t>
+  </si>
+  <si>
+    <t>DISEÑA Y MANTIENE LOS SISTEMAS DE ILUMINACIÓN</t>
+  </si>
+  <si>
+    <t>VENEGAS</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>AMECA</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>EZEQUIEL</t>
+  </si>
+  <si>
+    <t>ABAD</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>INGLÉS V</t>
+  </si>
+  <si>
+    <t>CÁLCULO INTEGRAL</t>
+  </si>
+  <si>
+    <t>TEHUINTLE</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
+    <t>LIZBETH JOSELYN</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>GETSEMANI GUADALUPE</t>
+  </si>
+  <si>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
   </si>
   <si>
     <t>LORENZO</t>
   </si>
   <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>MAYO</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>NERI</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>AYLIN MELISSA</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
+    <t>ALEMAN</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>CHRISTIAN YAIR</t>
+  </si>
+  <si>
+    <t>JORGE GUILLERMO</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>GREGORIO</t>
+  </si>
+  <si>
+    <t>IMPLEMENTA Y MANTIENE LOS SISTEMAS DE ENERGÍA RENOVABLE</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>VILLASEÑOR</t>
+  </si>
+  <si>
+    <t>MONGE</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>NAHOMY</t>
+  </si>
+  <si>
+    <t>JOSE RAFAEL</t>
+  </si>
+  <si>
+    <t>DIANA CRISTINA</t>
+  </si>
+  <si>
+    <t>MONICA AIME</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
+  </si>
+  <si>
+    <t>KARINA YOSELIN</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>BUSTOS</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>DAMIAN</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>AUTRAN</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>JOSE EMILIANO</t>
+  </si>
+  <si>
+    <t>JESUS JAREF</t>
+  </si>
+  <si>
+    <t>NATANAHEL</t>
+  </si>
+  <si>
+    <t>AXEL AARON</t>
+  </si>
+  <si>
+    <t>LUIS FABIAN</t>
+  </si>
+  <si>
+    <t>ALEX URIEL</t>
+  </si>
+  <si>
+    <t>SABDY</t>
+  </si>
+  <si>
+    <t>Pensamiento matemático I</t>
+  </si>
+  <si>
+    <t>CALVA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
+    <t>FERRER</t>
+  </si>
+  <si>
+    <t>MONTERROSAS</t>
+  </si>
+  <si>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>YAMILETH</t>
+  </si>
+  <si>
+    <t>INGRID ISABEL</t>
+  </si>
+  <si>
+    <t>VANESA</t>
+  </si>
+  <si>
+    <t>VALERY MIRANDA</t>
+  </si>
+  <si>
+    <t>LUZ YESENIA</t>
+  </si>
+  <si>
+    <t>MIGUEL ENRIQUE</t>
+  </si>
+  <si>
+    <t>ANEL</t>
+  </si>
+  <si>
+    <t>VICTORIA VIANNEY</t>
+  </si>
+  <si>
+    <t>ANGEL ABRAHAM</t>
+  </si>
+  <si>
+    <t>GISELA GUADALUPE</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>Inglés I</t>
+  </si>
+  <si>
+    <t>ALMANZA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CUAPIO</t>
+  </si>
+  <si>
+    <t>DORANTES</t>
+  </si>
+  <si>
+    <t>GILES</t>
+  </si>
+  <si>
+    <t>LAGUNA</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>MACUIXTLE</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>FIGUEROA</t>
+  </si>
+  <si>
+    <t>NATH</t>
+  </si>
+  <si>
+    <t>MONDRAGON</t>
+  </si>
+  <si>
+    <t>VANESA BETHSABE</t>
+  </si>
+  <si>
+    <t>RAMSES</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
   </si>
   <si>
     <t>ROBERTO</t>
   </si>
   <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>LUIS OMAR</t>
-  </si>
-  <si>
-    <t>CHARBEL</t>
-  </si>
-  <si>
-    <t>CANDIDO</t>
-  </si>
-  <si>
-    <t>CÁLCULO INTEGRAL</t>
-  </si>
-  <si>
-    <t>CIENCIA, TECNOLOGÍA, SOCIEDAD Y VALORES</t>
-  </si>
-  <si>
-    <t>FÍSICA II</t>
-  </si>
-  <si>
-    <t>DISEÑA Y MANTIENE LOS SISTEMAS DE ILUMINACIÓN</t>
-  </si>
-  <si>
-    <t>ARGÜELLO</t>
-  </si>
-  <si>
-    <t>VENEGAS</t>
-  </si>
-  <si>
-    <t>NARANJO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>AMECA</t>
-  </si>
-  <si>
-    <t>ESTEFANIA</t>
-  </si>
-  <si>
-    <t>ATZIN HEFZIBA</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>EZEQUIEL</t>
-  </si>
-  <si>
-    <t>ABAD</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>INGLÉS V</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>LIZBETH JOSELYN</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>GETSEMANI GUADALUPE</t>
-  </si>
-  <si>
-    <t>NUBE</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>ALEMAN</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>CUICAHUA</t>
-  </si>
-  <si>
-    <t>CHRISTIAN YAIR</t>
-  </si>
-  <si>
-    <t>JORGE GUILLERMO</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>DIEGO HUMBERTO</t>
-  </si>
-  <si>
-    <t>ZURIEL ELIHU</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>DARINKA</t>
-  </si>
-  <si>
-    <t>IMPLEMENTA Y MANTIENE LOS SISTEMAS DE ENERGÍA RENOVABLE</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>NAHOMY</t>
-  </si>
-  <si>
-    <t>JOSE RAFAEL</t>
-  </si>
-  <si>
-    <t>YAMILET MONSERRAT</t>
-  </si>
-  <si>
-    <t>DIANA CRISTINA</t>
-  </si>
-  <si>
-    <t>ANA LAURA</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>IVANNA DANIELA</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>BUSTOS</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>AUTRAN</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>JOSE EMILIANO</t>
-  </si>
-  <si>
-    <t>JESUS JAREF</t>
-  </si>
-  <si>
-    <t>NATANAHEL</t>
-  </si>
-  <si>
-    <t>AXEL AARON</t>
-  </si>
-  <si>
-    <t>LUIS FABIAN</t>
-  </si>
-  <si>
-    <t>ALEX URIEL</t>
-  </si>
-  <si>
-    <t>SABDY</t>
-  </si>
-  <si>
-    <t>Pensamiento matemático I</t>
-  </si>
-  <si>
-    <t>CALVA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
-    <t>FERRER</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>YAMILETH</t>
-  </si>
-  <si>
-    <t>INGRID ISABEL</t>
-  </si>
-  <si>
-    <t>VANESA</t>
-  </si>
-  <si>
-    <t>VALERY MIRANDA</t>
-  </si>
-  <si>
-    <t>LUZ YESENIA</t>
-  </si>
-  <si>
-    <t>MIGUEL ENRIQUE</t>
-  </si>
-  <si>
-    <t>ANEL</t>
-  </si>
-  <si>
-    <t>VICTORIA VIANNEY</t>
-  </si>
-  <si>
-    <t>ANGEL ABRAHAM</t>
-  </si>
-  <si>
-    <t>GISELA GUADALUPE</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>Inglés I</t>
-  </si>
-  <si>
-    <t>ALMANZA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CUAPIO</t>
-  </si>
-  <si>
-    <t>DORANTES</t>
-  </si>
-  <si>
-    <t>GILES</t>
-  </si>
-  <si>
-    <t>LAGUNA</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MACUIXTLE</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>FIGUEROA</t>
-  </si>
-  <si>
-    <t>NATH</t>
-  </si>
-  <si>
-    <t>MONDRAGON</t>
-  </si>
-  <si>
-    <t>VANESA BETHSABE</t>
-  </si>
-  <si>
-    <t>RAMSES</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
     <t>MARIANA</t>
   </si>
   <si>
@@ -1165,9 +1126,6 @@
   </si>
   <si>
     <t>AARON</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
   </si>
   <si>
     <t>ANA ISABEL</t>
@@ -2549,7 +2507,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2583,7 +2541,7 @@
         <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E2" t="s">
         <v>155</v>
@@ -2603,7 +2561,7 @@
         <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E3" t="s">
         <v>167</v>
@@ -2620,10 +2578,10 @@
         <v>202</v>
       </c>
       <c r="C4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E4" t="s">
         <v>155</v>
@@ -2643,7 +2601,7 @@
         <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E5" t="s">
         <v>167</v>
@@ -2663,7 +2621,7 @@
         <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E6" t="s">
         <v>156</v>
@@ -2683,7 +2641,7 @@
         <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E7" t="s">
         <v>155</v>
@@ -2703,7 +2661,7 @@
         <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E8" t="s">
         <v>155</v>
@@ -2714,16 +2672,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920049</v>
+        <v>22330051920189</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>205</v>
       </c>
       <c r="C9" t="s">
-        <v>208</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E9" t="s">
         <v>155</v>
@@ -2743,52 +2701,12 @@
         <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920189</v>
-      </c>
-      <c r="B11" t="s">
-        <v>205</v>
-      </c>
-      <c r="C11" t="s">
-        <v>103</v>
-      </c>
-      <c r="D11" t="s">
-        <v>215</v>
-      </c>
-      <c r="E11" t="s">
-        <v>156</v>
-      </c>
-      <c r="F11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920191</v>
-      </c>
-      <c r="B12" t="s">
-        <v>206</v>
-      </c>
-      <c r="C12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" t="s">
-        <v>216</v>
-      </c>
-      <c r="E12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F12">
         <v>5</v>
       </c>
     </row>
@@ -2827,16 +2745,16 @@
         <v>22330051920110</v>
       </c>
       <c r="B2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2850,13 +2768,13 @@
         <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2870,10 +2788,10 @@
         <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D4" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E4" t="s">
         <v>166</v>
@@ -2890,13 +2808,13 @@
         <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D5" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E5" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2913,10 +2831,10 @@
         <v>77</v>
       </c>
       <c r="D6" t="s">
+        <v>223</v>
+      </c>
+      <c r="E6" t="s">
         <v>227</v>
-      </c>
-      <c r="E6" t="s">
-        <v>231</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2933,7 +2851,7 @@
         <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E7" t="s">
         <v>166</v>
@@ -2950,10 +2868,10 @@
         <v>49</v>
       </c>
       <c r="C8" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D8" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E8" t="s">
         <v>166</v>
@@ -2967,16 +2885,16 @@
         <v>22330051920352</v>
       </c>
       <c r="B9" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2987,13 +2905,13 @@
         <v>22330051920352</v>
       </c>
       <c r="B10" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E10" t="s">
         <v>156</v>
@@ -3010,10 +2928,10 @@
         <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D11" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E11" t="s">
         <v>166</v>
@@ -3029,7 +2947,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3063,10 +2981,10 @@
         <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E2" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3083,10 +3001,10 @@
         <v>49</v>
       </c>
       <c r="D3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E3" t="s">
         <v>242</v>
-      </c>
-      <c r="E3" t="s">
-        <v>250</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3103,10 +3021,10 @@
         <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="E4" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3123,10 +3041,10 @@
         <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="E5" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3137,7 +3055,7 @@
         <v>21330051920153</v>
       </c>
       <c r="B6" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C6" t="s">
         <v>123</v>
@@ -3146,7 +3064,7 @@
         <v>151</v>
       </c>
       <c r="E6" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3154,19 +3072,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920164</v>
+        <v>21330051920166</v>
       </c>
       <c r="B7" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>232</v>
       </c>
       <c r="D7" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="E7" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3174,19 +3092,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920165</v>
+        <v>21330051920167</v>
       </c>
       <c r="B8" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C8" t="s">
+        <v>233</v>
+      </c>
+      <c r="D8" t="s">
         <v>238</v>
       </c>
-      <c r="D8" t="s">
-        <v>244</v>
-      </c>
       <c r="E8" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3194,19 +3112,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920166</v>
+        <v>21330051920167</v>
       </c>
       <c r="B9" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C9" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="D9" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="E9" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3214,19 +3132,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920167</v>
+        <v>21330051920169</v>
       </c>
       <c r="B10" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C10" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D10" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="E10" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3234,19 +3152,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920167</v>
+        <v>21330051920169</v>
       </c>
       <c r="B11" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C11" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D11" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="E11" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3254,19 +3172,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920169</v>
+        <v>21330051920176</v>
       </c>
       <c r="B12" t="s">
-        <v>237</v>
+        <v>185</v>
       </c>
       <c r="C12" t="s">
-        <v>241</v>
+        <v>124</v>
       </c>
       <c r="D12" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="E12" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3274,61 +3192,21 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920169</v>
+        <v>21330051920176</v>
       </c>
       <c r="B13" t="s">
-        <v>237</v>
+        <v>185</v>
       </c>
       <c r="C13" t="s">
+        <v>124</v>
+      </c>
+      <c r="D13" t="s">
+        <v>240</v>
+      </c>
+      <c r="E13" t="s">
         <v>241</v>
       </c>
-      <c r="D13" t="s">
-        <v>247</v>
-      </c>
-      <c r="E13" t="s">
-        <v>250</v>
-      </c>
       <c r="F13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920176</v>
-      </c>
-      <c r="B14" t="s">
-        <v>185</v>
-      </c>
-      <c r="C14" t="s">
-        <v>124</v>
-      </c>
-      <c r="D14" t="s">
-        <v>248</v>
-      </c>
-      <c r="E14" t="s">
-        <v>249</v>
-      </c>
-      <c r="F14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920176</v>
-      </c>
-      <c r="B15" t="s">
-        <v>185</v>
-      </c>
-      <c r="C15" t="s">
-        <v>124</v>
-      </c>
-      <c r="D15" t="s">
-        <v>248</v>
-      </c>
-      <c r="E15" t="s">
-        <v>250</v>
-      </c>
-      <c r="F15">
         <v>5</v>
       </c>
     </row>
@@ -3339,7 +3217,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3364,19 +3242,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920081</v>
+        <v>21330051920257</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>169</v>
+        <v>245</v>
       </c>
       <c r="D2" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="E2" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3384,61 +3262,21 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920253</v>
+        <v>21330051920287</v>
       </c>
       <c r="B3" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="C3" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="D3" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="E3" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920257</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>256</v>
-      </c>
-      <c r="D4" t="s">
-        <v>260</v>
-      </c>
-      <c r="E4" t="s">
-        <v>251</v>
-      </c>
-      <c r="F4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920287</v>
-      </c>
-      <c r="B5" t="s">
-        <v>254</v>
-      </c>
-      <c r="C5" t="s">
-        <v>257</v>
-      </c>
-      <c r="D5" t="s">
-        <v>261</v>
-      </c>
-      <c r="E5" t="s">
-        <v>251</v>
-      </c>
-      <c r="F5">
         <v>5</v>
       </c>
     </row>
@@ -3477,16 +3315,16 @@
         <v>21330051920331</v>
       </c>
       <c r="B2" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="C2" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="D2" t="s">
         <v>112</v>
       </c>
       <c r="E2" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3500,13 +3338,13 @@
         <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="D3" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="E3" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3517,16 +3355,16 @@
         <v>21330051920353</v>
       </c>
       <c r="B4" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="C4" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="D4" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="E4" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3537,16 +3375,16 @@
         <v>21330051920353</v>
       </c>
       <c r="B5" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="C5" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="E5" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3587,16 +3425,16 @@
         <v>21330051920222</v>
       </c>
       <c r="B2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C2" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="E2" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3616,7 +3454,7 @@
         <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3627,16 +3465,16 @@
         <v>21330051920235</v>
       </c>
       <c r="B4" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C4" t="s">
         <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E4" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3647,16 +3485,16 @@
         <v>21330051920249</v>
       </c>
       <c r="B5" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="C5" t="s">
         <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="E5" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3667,16 +3505,16 @@
         <v>21330051920250</v>
       </c>
       <c r="B6" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C6" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="D6" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="E6" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3689,7 +3527,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3717,16 +3555,16 @@
         <v>20330051920100</v>
       </c>
       <c r="B2" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="C2" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="D2" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="E2" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3737,16 +3575,16 @@
         <v>20330051920100</v>
       </c>
       <c r="B3" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="C3" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="D3" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="E3" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3763,10 +3601,10 @@
         <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E4" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3774,19 +3612,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920190</v>
+        <v>21330051920201</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>266</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>269</v>
       </c>
       <c r="D5" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="E5" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3794,19 +3632,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920201</v>
+        <v>21330051920213</v>
       </c>
       <c r="B6" t="s">
-        <v>278</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="D6" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="E6" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3814,19 +3652,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920205</v>
+        <v>21330051920213</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>270</v>
       </c>
       <c r="D7" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="E7" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3834,19 +3672,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920208</v>
+        <v>21330051920386</v>
       </c>
       <c r="B8" t="s">
-        <v>238</v>
+        <v>267</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="E8" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3854,61 +3692,21 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920213</v>
+        <v>21330051920386</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>267</v>
       </c>
       <c r="C9" t="s">
-        <v>281</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="E9" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="F9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920213</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" t="s">
-        <v>281</v>
-      </c>
-      <c r="D10" t="s">
-        <v>288</v>
-      </c>
-      <c r="E10" t="s">
-        <v>251</v>
-      </c>
-      <c r="F10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920214</v>
-      </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" t="s">
-        <v>282</v>
-      </c>
-      <c r="D11" t="s">
-        <v>289</v>
-      </c>
-      <c r="E11" t="s">
-        <v>249</v>
-      </c>
-      <c r="F11">
         <v>5</v>
       </c>
     </row>
@@ -3950,13 +3748,13 @@
         <v>96</v>
       </c>
       <c r="C2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D2" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="E2" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3973,10 +3771,10 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="E3" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3993,10 +3791,10 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="E4" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4016,7 +3814,7 @@
         <v>163</v>
       </c>
       <c r="E5" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4024,19 +3822,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920302</v>
+        <v>21330051920307</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="D6" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="E6" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4044,19 +3842,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920307</v>
+        <v>21330051920311</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>266</v>
       </c>
       <c r="C7" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="D7" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="E7" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4064,19 +3862,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920316</v>
+        <v>21330051920311</v>
       </c>
       <c r="B8" t="s">
-        <v>291</v>
+        <v>266</v>
       </c>
       <c r="C8" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>287</v>
       </c>
       <c r="E8" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4084,19 +3882,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920321</v>
+        <v>21330051920316</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>277</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>282</v>
       </c>
       <c r="D9" t="s">
-        <v>301</v>
+        <v>27</v>
       </c>
       <c r="E9" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4113,10 +3911,10 @@
         <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="E10" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4124,19 +3922,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920323</v>
+        <v>21330051920328</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>278</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>283</v>
       </c>
       <c r="D11" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="E11" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -4144,19 +3942,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920326</v>
+        <v>21330051920328</v>
       </c>
       <c r="B12" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="C12" t="s">
-        <v>10</v>
+        <v>283</v>
       </c>
       <c r="D12" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="E12" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -4167,16 +3965,16 @@
         <v>21330051920337</v>
       </c>
       <c r="B13" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="C13" t="s">
         <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="E13" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -4217,13 +4015,13 @@
         <v>23330051920180</v>
       </c>
       <c r="B2" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="C2" t="s">
         <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="E2" t="s">
         <v>42</v>
@@ -4237,13 +4035,13 @@
         <v>23330051920180</v>
       </c>
       <c r="B3" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="E3" t="s">
         <v>30</v>
@@ -4260,10 +4058,10 @@
         <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="D4" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="E4" t="s">
         <v>30</v>
@@ -4280,10 +4078,10 @@
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="D5" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="E5" t="s">
         <v>42</v>
@@ -4300,10 +4098,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="D6" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="E6" t="s">
         <v>142</v>
@@ -4320,10 +4118,10 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="D7" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="E7" t="s">
         <v>30</v>
@@ -4340,13 +4138,13 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="D8" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="E8" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4360,10 +4158,10 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="D9" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="E9" t="s">
         <v>142</v>
@@ -4377,10 +4175,10 @@
         <v>23330051920199</v>
       </c>
       <c r="B10" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="C10" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="D10" t="s">
         <v>150</v>
@@ -4397,10 +4195,10 @@
         <v>23330051920199</v>
       </c>
       <c r="B11" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="C11" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="D11" t="s">
         <v>150</v>
@@ -4423,7 +4221,7 @@
         <v>144</v>
       </c>
       <c r="D12" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="E12" t="s">
         <v>42</v>
@@ -4443,7 +4241,7 @@
         <v>144</v>
       </c>
       <c r="D13" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="E13" t="s">
         <v>30</v>
@@ -4457,13 +4255,13 @@
         <v>23330051920212</v>
       </c>
       <c r="B14" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="C14" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="D14" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="E14" t="s">
         <v>30</v>
@@ -4477,16 +4275,16 @@
         <v>23330051920212</v>
       </c>
       <c r="B15" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="C15" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="D15" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="E15" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -4500,10 +4298,10 @@
         <v>170</v>
       </c>
       <c r="C16" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D16" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="E16" t="s">
         <v>30</v>
@@ -4677,13 +4475,13 @@
         <v>23330051920215</v>
       </c>
       <c r="B2" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="C2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="D2" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="E2" t="s">
         <v>31</v>
@@ -4697,13 +4495,13 @@
         <v>23330051920215</v>
       </c>
       <c r="B3" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="C3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="D3" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="E3" t="s">
         <v>42</v>
@@ -4720,10 +4518,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="D4" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="E4" t="s">
         <v>31</v>
@@ -4740,13 +4538,13 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="D5" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="E5" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4757,16 +4555,16 @@
         <v>23330051920227</v>
       </c>
       <c r="B6" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="C6" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="D6" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="E6" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4780,10 +4578,10 @@
         <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="D7" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="E7" t="s">
         <v>42</v>
@@ -4797,13 +4595,13 @@
         <v>23330051920242</v>
       </c>
       <c r="B8" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C8" t="s">
         <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="E8" t="s">
         <v>30</v>
@@ -4817,13 +4615,13 @@
         <v>23330051920244</v>
       </c>
       <c r="B9" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="E9" t="s">
         <v>42</v>
@@ -4837,13 +4635,13 @@
         <v>23330051920254</v>
       </c>
       <c r="B10" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="E10" t="s">
         <v>42</v>
@@ -4857,13 +4655,13 @@
         <v>23330051920254</v>
       </c>
       <c r="B11" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="E11" t="s">
         <v>31</v>
@@ -4897,13 +4695,13 @@
         <v>23330051920275</v>
       </c>
       <c r="B13" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="C13" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="D13" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="E13" t="s">
         <v>31</v>
@@ -4917,13 +4715,13 @@
         <v>23330051920275</v>
       </c>
       <c r="B14" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="C14" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="D14" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="E14" t="s">
         <v>30</v>
@@ -4943,7 +4741,7 @@
         <v>19</v>
       </c>
       <c r="D15" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="E15" t="s">
         <v>42</v>
@@ -4957,16 +4755,16 @@
         <v>23330051920280</v>
       </c>
       <c r="B16" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="C16" t="s">
         <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="E16" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -4980,13 +4778,13 @@
         <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D17" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="E17" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -5000,13 +4798,13 @@
         <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D18" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="E18" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -5023,7 +4821,7 @@
         <v>19</v>
       </c>
       <c r="D19" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="E19" t="s">
         <v>42</v>
@@ -5067,16 +4865,16 @@
         <v>23330051920218</v>
       </c>
       <c r="B2" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="E2" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5087,16 +4885,16 @@
         <v>23330051920220</v>
       </c>
       <c r="B3" t="s">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="C3" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="D3" t="s">
         <v>87</v>
       </c>
       <c r="E3" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5107,16 +4905,16 @@
         <v>23330051920220</v>
       </c>
       <c r="B4" t="s">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="C4" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="D4" t="s">
         <v>87</v>
       </c>
       <c r="E4" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5133,10 +4931,10 @@
         <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="E5" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5147,16 +4945,16 @@
         <v>23330051920222</v>
       </c>
       <c r="B6" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="C6" t="s">
         <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="E6" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5167,13 +4965,13 @@
         <v>23330051920222</v>
       </c>
       <c r="B7" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="C7" t="s">
         <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="E7" t="s">
         <v>30</v>
@@ -5187,16 +4985,16 @@
         <v>23330051920224</v>
       </c>
       <c r="B8" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="C8" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="D8" t="s">
-        <v>244</v>
+        <v>344</v>
       </c>
       <c r="E8" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5210,10 +5008,10 @@
         <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="D9" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="E9" t="s">
         <v>30</v>
@@ -5230,13 +5028,13 @@
         <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="D10" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="E10" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -5253,10 +5051,10 @@
         <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="E11" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -5267,16 +5065,16 @@
         <v>23330051920231</v>
       </c>
       <c r="B12" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="C12" t="s">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="D12" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="E12" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -5287,16 +5085,16 @@
         <v>23330051920243</v>
       </c>
       <c r="B13" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="C13" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="D13" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="E13" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -5307,13 +5105,13 @@
         <v>23330051920251</v>
       </c>
       <c r="B14" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="E14" t="s">
         <v>31</v>
@@ -5327,16 +5125,16 @@
         <v>23330051920251</v>
       </c>
       <c r="B15" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="C15" t="s">
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="E15" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -5347,16 +5145,16 @@
         <v>23330051920253</v>
       </c>
       <c r="B16" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="C16" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="D16" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="E16" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -5370,13 +5168,13 @@
         <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="D17" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="E17" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -5417,13 +5215,13 @@
         <v>23330051920299</v>
       </c>
       <c r="B2" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="C2" t="s">
         <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="E2" t="s">
         <v>142</v>
@@ -5437,13 +5235,13 @@
         <v>23330051920299</v>
       </c>
       <c r="B3" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="E3" t="s">
         <v>30</v>
@@ -5457,13 +5255,13 @@
         <v>23330051920310</v>
       </c>
       <c r="B4" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="C4" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="D4" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="E4" t="s">
         <v>142</v>
@@ -5477,13 +5275,13 @@
         <v>23330051920310</v>
       </c>
       <c r="B5" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="C5" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="D5" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="E5" t="s">
         <v>42</v>
@@ -5497,13 +5295,13 @@
         <v>23330051920311</v>
       </c>
       <c r="B6" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C6" t="s">
         <v>103</v>
       </c>
       <c r="D6" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="E6" t="s">
         <v>142</v>
@@ -5517,16 +5315,16 @@
         <v>23330051920311</v>
       </c>
       <c r="B7" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C7" t="s">
         <v>103</v>
       </c>
       <c r="D7" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="E7" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5546,7 +5344,7 @@
         <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5563,10 +5361,10 @@
         <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="E9" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5597,16 +5395,16 @@
         <v>23330051920356</v>
       </c>
       <c r="B11" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="C11" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="D11" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="E11" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -5623,7 +5421,7 @@
         <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="E12" t="s">
         <v>142</v>
@@ -5643,7 +5441,7 @@
         <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="E13" t="s">
         <v>42</v>
@@ -5687,13 +5485,13 @@
         <v>23330051920302</v>
       </c>
       <c r="B2" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>373</v>
+        <v>278</v>
       </c>
       <c r="D2" t="s">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="E2" t="s">
         <v>29</v>
@@ -5707,13 +5505,13 @@
         <v>23330051920302</v>
       </c>
       <c r="B3" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="C3" t="s">
-        <v>373</v>
+        <v>278</v>
       </c>
       <c r="D3" t="s">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="E3" t="s">
         <v>42</v>
@@ -5733,7 +5531,7 @@
         <v>122</v>
       </c>
       <c r="D4" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="E4" t="s">
         <v>42</v>
@@ -5753,10 +5551,10 @@
         <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="E5" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5800,13 +5598,13 @@
         <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="D2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E2" t="s">
         <v>384</v>
-      </c>
-      <c r="E2" t="s">
-        <v>398</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5820,13 +5618,13 @@
         <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="D3" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="E3" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5837,13 +5635,13 @@
         <v>21330051920007</v>
       </c>
       <c r="B4" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="C4" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="D4" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="E4" t="s">
         <v>165</v>
@@ -5860,10 +5658,10 @@
         <v>144</v>
       </c>
       <c r="C5" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D5" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="E5" t="s">
         <v>165</v>
@@ -5883,7 +5681,7 @@
         <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="E6" t="s">
         <v>165</v>
@@ -5900,13 +5698,13 @@
         <v>170</v>
       </c>
       <c r="C7" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D7" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="E7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5920,13 +5718,13 @@
         <v>170</v>
       </c>
       <c r="C8" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D8" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="E8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5937,13 +5735,13 @@
         <v>22330051920192</v>
       </c>
       <c r="B9" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="E9" t="s">
         <v>165</v>
@@ -5963,7 +5761,7 @@
         <v>144</v>
       </c>
       <c r="D10" t="s">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="E10" t="s">
         <v>165</v>
@@ -5983,7 +5781,7 @@
         <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>391</v>
+        <v>377</v>
       </c>
       <c r="E11" t="s">
         <v>165</v>
@@ -6003,7 +5801,7 @@
         <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="E12" t="s">
         <v>165</v>
@@ -6020,10 +5818,10 @@
         <v>185</v>
       </c>
       <c r="C13" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="D13" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="E13" t="s">
         <v>165</v>
@@ -6037,13 +5835,13 @@
         <v>22330051920359</v>
       </c>
       <c r="B14" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="C14" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="D14" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="E14" t="s">
         <v>167</v>
@@ -6057,13 +5855,13 @@
         <v>22330051920363</v>
       </c>
       <c r="B15" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="C15" t="s">
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="E15" t="s">
         <v>167</v>
@@ -6080,13 +5878,13 @@
         <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="D16" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="E16" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -6100,13 +5898,13 @@
         <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="D17" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="E17" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -6123,7 +5921,7 @@
         <v>186</v>
       </c>
       <c r="D18" t="s">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="E18" t="s">
         <v>165</v>
@@ -6170,13 +5968,13 @@
         <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="D2" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
       <c r="E2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6190,10 +5988,10 @@
         <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="D3" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
       <c r="E3" t="s">
         <v>166</v>
@@ -6207,13 +6005,13 @@
         <v>22330051920176</v>
       </c>
       <c r="B4" t="s">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="C4" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="D4" t="s">
-        <v>408</v>
+        <v>394</v>
       </c>
       <c r="E4" t="s">
         <v>156</v>
@@ -6227,13 +6025,13 @@
         <v>22330051920233</v>
       </c>
       <c r="B5" t="s">
-        <v>401</v>
+        <v>387</v>
       </c>
       <c r="C5" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="D5" t="s">
-        <v>409</v>
+        <v>395</v>
       </c>
       <c r="E5" t="s">
         <v>156</v>
@@ -6247,13 +6045,13 @@
         <v>22330051920237</v>
       </c>
       <c r="B6" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="E6" t="s">
         <v>165</v>
@@ -6270,10 +6068,10 @@
         <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="D7" t="s">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="E7" t="s">
         <v>156</v>
@@ -6290,10 +6088,10 @@
         <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="D8" t="s">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="E8" t="s">
         <v>167</v>
@@ -6310,10 +6108,10 @@
         <v>157</v>
       </c>
       <c r="C9" t="s">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="D9" t="s">
-        <v>412</v>
+        <v>398</v>
       </c>
       <c r="E9" t="s">
         <v>165</v>
@@ -6330,10 +6128,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="D10" t="s">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="E10" t="s">
         <v>165</v>
@@ -6353,10 +6151,10 @@
         <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="E11" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6373,7 +6171,7 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="E12" t="s">
         <v>167</v>
@@ -6393,7 +6191,7 @@
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="E13" t="s">
         <v>156</v>
@@ -6443,7 +6241,7 @@
         <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="E2" t="s">
         <v>156</v>
@@ -6463,7 +6261,7 @@
         <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="E3" t="s">
         <v>167</v>
@@ -6477,13 +6275,13 @@
         <v>22330051920273</v>
       </c>
       <c r="B4" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="C4" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="D4" t="s">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="E4" t="s">
         <v>165</v>
@@ -6497,13 +6295,13 @@
         <v>22330051920273</v>
       </c>
       <c r="B5" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="C5" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="D5" t="s">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="E5" t="s">
         <v>167</v>
@@ -6520,10 +6318,10 @@
         <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D6" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="E6" t="s">
         <v>156</v>
@@ -6540,10 +6338,10 @@
         <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>417</v>
+        <v>403</v>
       </c>
       <c r="D7" t="s">
-        <v>420</v>
+        <v>406</v>
       </c>
       <c r="E7" t="s">
         <v>156</v>
@@ -6557,13 +6355,13 @@
         <v>22330051920286</v>
       </c>
       <c r="B8" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C8" t="s">
         <v>183</v>
       </c>
       <c r="D8" t="s">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="E8" t="s">
         <v>156</v>
@@ -6583,7 +6381,7 @@
         <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="E9" t="s">
         <v>165</v>
@@ -6603,7 +6401,7 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="E10" t="s">
         <v>167</v>
@@ -6653,10 +6451,10 @@
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="E2" t="s">
-        <v>430</v>
+        <v>416</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6673,10 +6471,10 @@
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="E3" t="s">
-        <v>431</v>
+        <v>417</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6687,13 +6485,13 @@
         <v>21330051920002</v>
       </c>
       <c r="B4" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
       <c r="C4" t="s">
-        <v>423</v>
+        <v>409</v>
       </c>
       <c r="D4" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="E4" t="s">
         <v>165</v>
@@ -6710,10 +6508,10 @@
         <v>186</v>
       </c>
       <c r="C5" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D5" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="E5" t="s">
         <v>156</v>
@@ -6730,10 +6528,10 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="D6" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="E6" t="s">
         <v>156</v>
@@ -6750,10 +6548,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="D7" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="E7" t="s">
         <v>167</v>
@@ -6770,7 +6568,7 @@
         <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="D8" t="s">
         <v>80</v>
@@ -6790,7 +6588,7 @@
         <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="D9" t="s">
         <v>80</v>
@@ -6837,13 +6635,13 @@
         <v>22330051920298</v>
       </c>
       <c r="B2" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
       <c r="C2" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="E2" t="s">
         <v>167</v>
@@ -6863,7 +6661,7 @@
         <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="E3" t="s">
         <v>156</v>
@@ -6883,10 +6681,10 @@
         <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>435</v>
+        <v>421</v>
       </c>
       <c r="E4" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6930,13 +6728,13 @@
         <v>144</v>
       </c>
       <c r="C2" t="s">
-        <v>439</v>
+        <v>425</v>
       </c>
       <c r="D2" t="s">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="E2" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6953,10 +6751,10 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>441</v>
+        <v>427</v>
       </c>
       <c r="E3" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6967,16 +6765,16 @@
         <v>20330051920366</v>
       </c>
       <c r="B4" t="s">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="E4" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6987,16 +6785,16 @@
         <v>20330051920366</v>
       </c>
       <c r="B5" t="s">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="E5" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7007,16 +6805,16 @@
         <v>20330051920367</v>
       </c>
       <c r="B6" t="s">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="E6" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7033,10 +6831,10 @@
         <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="E7" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7053,10 +6851,10 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="E8" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7073,10 +6871,10 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="E9" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7093,10 +6891,10 @@
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>446</v>
+        <v>432</v>
       </c>
       <c r="E10" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7107,16 +6905,16 @@
         <v>21330051920023</v>
       </c>
       <c r="B11" t="s">
-        <v>438</v>
+        <v>424</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="E11" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -7127,16 +6925,16 @@
         <v>21330051920023</v>
       </c>
       <c r="B12" t="s">
-        <v>438</v>
+        <v>424</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="E12" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -7350,13 +7148,13 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="D2" t="s">
         <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7376,7 +7174,7 @@
         <v>87</v>
       </c>
       <c r="E3" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7390,13 +7188,13 @@
         <v>144</v>
       </c>
       <c r="C4" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="D4" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="E4" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7407,16 +7205,16 @@
         <v>21330051920089</v>
       </c>
       <c r="B5" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="C5" t="s">
         <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="E5" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7427,16 +7225,16 @@
         <v>21330051920092</v>
       </c>
       <c r="B6" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="C6" t="s">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="D6" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="E6" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7447,16 +7245,16 @@
         <v>21330051920093</v>
       </c>
       <c r="B7" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="E7" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7467,16 +7265,16 @@
         <v>21330051920097</v>
       </c>
       <c r="B8" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C8" t="s">
-        <v>457</v>
+        <v>443</v>
       </c>
       <c r="D8" t="s">
-        <v>464</v>
+        <v>450</v>
       </c>
       <c r="E8" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7493,10 +7291,10 @@
         <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>465</v>
+        <v>451</v>
       </c>
       <c r="E9" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7513,10 +7311,10 @@
         <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>466</v>
+        <v>452</v>
       </c>
       <c r="E10" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7533,10 +7331,10 @@
         <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="E11" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -7553,10 +7351,10 @@
         <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>468</v>
+        <v>454</v>
       </c>
       <c r="E12" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -7573,10 +7371,10 @@
         <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>468</v>
+        <v>454</v>
       </c>
       <c r="E13" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -7587,16 +7385,16 @@
         <v>21330051920103</v>
       </c>
       <c r="B14" t="s">
-        <v>451</v>
+        <v>437</v>
       </c>
       <c r="C14" t="s">
         <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>469</v>
+        <v>455</v>
       </c>
       <c r="E14" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -7607,16 +7405,16 @@
         <v>21330051920107</v>
       </c>
       <c r="B15" t="s">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="C15" t="s">
         <v>171</v>
       </c>
       <c r="D15" t="s">
-        <v>470</v>
+        <v>456</v>
       </c>
       <c r="E15" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -7627,16 +7425,16 @@
         <v>21330051920107</v>
       </c>
       <c r="B16" t="s">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="C16" t="s">
         <v>171</v>
       </c>
       <c r="D16" t="s">
-        <v>470</v>
+        <v>456</v>
       </c>
       <c r="E16" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -7650,13 +7448,13 @@
         <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="D17" t="s">
-        <v>471</v>
+        <v>457</v>
       </c>
       <c r="E17" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -7667,16 +7465,16 @@
         <v>21330051920305</v>
       </c>
       <c r="B18" t="s">
-        <v>453</v>
+        <v>439</v>
       </c>
       <c r="C18" t="s">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="D18" t="s">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="E18" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -7687,16 +7485,16 @@
         <v>21330051920305</v>
       </c>
       <c r="B19" t="s">
-        <v>453</v>
+        <v>439</v>
       </c>
       <c r="C19" t="s">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="D19" t="s">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="E19" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -7743,10 +7541,10 @@
         <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>477</v>
+        <v>463</v>
       </c>
       <c r="E2" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7757,16 +7555,16 @@
         <v>21330051920111</v>
       </c>
       <c r="B3" t="s">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="C3" t="s">
         <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="E3" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7777,16 +7575,16 @@
         <v>21330051920111</v>
       </c>
       <c r="B4" t="s">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="C4" t="s">
         <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="E4" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7800,13 +7598,13 @@
         <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="D5" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E5" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7823,10 +7621,10 @@
         <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="E6" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7837,16 +7635,16 @@
         <v>21330051920123</v>
       </c>
       <c r="B7" t="s">
-        <v>473</v>
+        <v>459</v>
       </c>
       <c r="C7" t="s">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="D7" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="E7" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7863,10 +7661,10 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="E8" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7883,10 +7681,10 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="E9" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7897,7 +7695,7 @@
         <v>21330051920126</v>
       </c>
       <c r="B10" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="C10" t="s">
         <v>33</v>
@@ -7906,7 +7704,7 @@
         <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7917,7 +7715,7 @@
         <v>21330051920126</v>
       </c>
       <c r="B11" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="C11" t="s">
         <v>33</v>
@@ -7926,7 +7724,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -7940,13 +7738,13 @@
         <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="D12" t="s">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="E12" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -7987,16 +7785,16 @@
         <v>21330051920031</v>
       </c>
       <c r="B2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>488</v>
+        <v>474</v>
       </c>
       <c r="E2" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8007,16 +7805,16 @@
         <v>21330051920031</v>
       </c>
       <c r="B3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>488</v>
+        <v>474</v>
       </c>
       <c r="E3" t="s">
-        <v>497</v>
+        <v>483</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8027,16 +7825,16 @@
         <v>21330051920035</v>
       </c>
       <c r="B4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>489</v>
+        <v>475</v>
       </c>
       <c r="E4" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8047,16 +7845,16 @@
         <v>21330051920036</v>
       </c>
       <c r="B5" t="s">
-        <v>483</v>
+        <v>469</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>490</v>
+        <v>476</v>
       </c>
       <c r="E5" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8067,16 +7865,16 @@
         <v>21330051920046</v>
       </c>
       <c r="B6" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="C6" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="D6" t="s">
-        <v>491</v>
+        <v>477</v>
       </c>
       <c r="E6" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -8093,10 +7891,10 @@
         <v>170</v>
       </c>
       <c r="D7" t="s">
-        <v>492</v>
+        <v>478</v>
       </c>
       <c r="E7" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -8113,10 +7911,10 @@
         <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>493</v>
+        <v>479</v>
       </c>
       <c r="E8" t="s">
-        <v>497</v>
+        <v>483</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -8133,10 +7931,10 @@
         <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>493</v>
+        <v>479</v>
       </c>
       <c r="E9" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -8147,16 +7945,16 @@
         <v>21330051920062</v>
       </c>
       <c r="B10" t="s">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="C10" t="s">
         <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>494</v>
+        <v>480</v>
       </c>
       <c r="E10" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -8173,10 +7971,10 @@
         <v>123</v>
       </c>
       <c r="D11" t="s">
-        <v>495</v>
+        <v>481</v>
       </c>
       <c r="E11" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -8193,10 +7991,10 @@
         <v>123</v>
       </c>
       <c r="D12" t="s">
-        <v>495</v>
+        <v>481</v>
       </c>
       <c r="E12" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -8210,13 +8008,13 @@
         <v>183</v>
       </c>
       <c r="C13" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="D13" t="s">
         <v>79</v>
       </c>
       <c r="E13" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -8230,13 +8028,13 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>487</v>
+        <v>473</v>
       </c>
       <c r="D14" t="s">
-        <v>496</v>
+        <v>482</v>
       </c>
       <c r="E14" t="s">
-        <v>498</v>
+        <v>484</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -8250,13 +8048,13 @@
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>487</v>
+        <v>473</v>
       </c>
       <c r="D15" t="s">
-        <v>496</v>
+        <v>482</v>
       </c>
       <c r="E15" t="s">
-        <v>497</v>
+        <v>483</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -8300,13 +8098,13 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="D2" t="s">
-        <v>500</v>
+        <v>486</v>
       </c>
       <c r="E2" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8320,13 +8118,13 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="D3" t="s">
-        <v>500</v>
+        <v>486</v>
       </c>
       <c r="E3" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8340,13 +8138,13 @@
         <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>499</v>
+        <v>485</v>
       </c>
       <c r="D4" t="s">
-        <v>501</v>
+        <v>487</v>
       </c>
       <c r="E4" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F4">
         <v>5</v>

--- a/Rescatables20231.xlsx
+++ b/Rescatables20231.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="362">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -651,72 +651,93 @@
     <t>CHICO</t>
   </si>
   <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t>NARVAEZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
     <t>DAMIAN</t>
   </si>
   <si>
     <t>COCOTLE</t>
   </si>
   <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
     <t>AUTRAN</t>
   </si>
   <si>
     <t>CARRERA</t>
   </si>
   <si>
+    <t>LIBRADO</t>
+  </si>
+  <si>
+    <t>JESUS JAREF</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>JULIO CESAR</t>
+  </si>
+  <si>
+    <t>NATANAHEL</t>
+  </si>
+  <si>
+    <t>AXEL AARON</t>
+  </si>
+  <si>
+    <t>KEVYN DANIEL</t>
+  </si>
+  <si>
+    <t>LAZARO</t>
+  </si>
+  <si>
+    <t>LUIS FABIAN</t>
+  </si>
+  <si>
+    <t>ROBBIE ALONSO</t>
+  </si>
+  <si>
+    <t>ARMANDO GABRIEL</t>
+  </si>
+  <si>
+    <t>Pensamiento matemático I</t>
+  </si>
+  <si>
+    <t>Ciencias sociales I</t>
+  </si>
+  <si>
+    <t>Inglés I</t>
+  </si>
+  <si>
+    <t>CALVA</t>
+  </si>
+  <si>
+    <t>FUENTES</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
     <t>VILLA</t>
   </si>
   <si>
-    <t>JESUS JAREF</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>NATANAHEL</t>
-  </si>
-  <si>
-    <t>AXEL AARON</t>
-  </si>
-  <si>
-    <t>KEVYN DANIEL</t>
-  </si>
-  <si>
-    <t>LUIS FABIAN</t>
-  </si>
-  <si>
-    <t>ROBBIE ALONSO</t>
-  </si>
-  <si>
-    <t>ALEX URIEL</t>
-  </si>
-  <si>
-    <t>Ciencias sociales I</t>
-  </si>
-  <si>
-    <t>Pensamiento matemático I</t>
-  </si>
-  <si>
-    <t>Lengua y comunicación I</t>
-  </si>
-  <si>
-    <t>CALVA</t>
-  </si>
-  <si>
-    <t>FUENTES</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
     <t>CANDELARIO</t>
   </si>
   <si>
@@ -750,9 +771,6 @@
     <t>VANESSA</t>
   </si>
   <si>
-    <t>Inglés I</t>
-  </si>
-  <si>
     <t>ALMANZA</t>
   </si>
   <si>
@@ -858,9 +876,6 @@
     <t>FERNANDA YAMILET</t>
   </si>
   <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
     <t>AVILA</t>
   </si>
   <si>
@@ -870,24 +885,24 @@
     <t>CORTES</t>
   </si>
   <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
     <t>PERALTA</t>
   </si>
   <si>
+    <t>CASANOVA</t>
+  </si>
+  <si>
     <t>GARZA</t>
   </si>
   <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
     <t>PABLO</t>
   </si>
   <si>
     <t>GALINDO</t>
   </si>
   <si>
-    <t>JURISEL</t>
-  </si>
-  <si>
     <t>MARIANA JANET</t>
   </si>
   <si>
@@ -900,12 +915,21 @@
     <t>MICHEL LEONEL</t>
   </si>
   <si>
+    <t>JUSTIN GIOVANNI</t>
+  </si>
+  <si>
     <t>JESHUA</t>
   </si>
   <si>
+    <t>HUGO ANTONIO</t>
+  </si>
+  <si>
     <t>IVETTE</t>
   </si>
   <si>
+    <t>LUCIA</t>
+  </si>
+  <si>
     <t>JENNYFER ARIANA</t>
   </si>
   <si>
@@ -915,15 +939,27 @@
     <t>MARCELINO</t>
   </si>
   <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
     <t>MARIEL</t>
   </si>
   <si>
     <t>GIANCARLO</t>
   </si>
   <si>
+    <t>NOHEMI ANGELICA</t>
+  </si>
+  <si>
     <t>ESTEBAN</t>
   </si>
   <si>
+    <t>SERGIO JOSUE</t>
+  </si>
+  <si>
     <t>YAMILET</t>
   </si>
   <si>
@@ -1032,13 +1068,13 @@
     <t>GAMALIEL</t>
   </si>
   <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
     <t>NAJERA</t>
   </si>
   <si>
-    <t>NAZARIO</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
+    <t>RAFAEL</t>
   </si>
   <si>
     <t>DULIAM</t>
@@ -1050,43 +1086,22 @@
     <t>ISAAC</t>
   </si>
   <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
     <t>ARIEL</t>
   </si>
   <si>
-    <t>VICTOR ISRAEL</t>
-  </si>
-  <si>
     <t>REALIZA MANTENIMIENTO A LAS INSTALACIONES ELÉCTRICAS RESIDENCIALES, COMERCIALES E INDUSTRIALES</t>
   </si>
   <si>
     <t>ESPIRITU</t>
   </si>
   <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>NEGRETE</t>
-  </si>
-  <si>
     <t>ABIGAIL</t>
   </si>
   <si>
     <t>EVELYN JOHANA</t>
   </si>
   <si>
-    <t>VANESSA AMAIRANY</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
+    <t>MIROSLAVA</t>
   </si>
   <si>
     <t>MARIA JOSE</t>
@@ -1095,51 +1110,18 @@
     <t>MARIA TERESA</t>
   </si>
   <si>
-    <t>MARIA MICHELLE</t>
-  </si>
-  <si>
     <t>INGLÉS V</t>
   </si>
   <si>
     <t>ZABDIEL</t>
   </si>
   <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
     <t>ROMANOS</t>
   </si>
   <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
     <t>TEZOCO</t>
   </si>
   <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>GABRIELA ELIZABET</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>MIA ARANZA</t>
-  </si>
-  <si>
-    <t>MICHEL</t>
-  </si>
-  <si>
-    <t>INGRID CRISTEL</t>
-  </si>
-  <si>
-    <t>HANIA ZARETH</t>
-  </si>
-  <si>
     <t>SUPERVISA EL CUMPLIMIENTO DE LAS MEDIDAS DE HIGIENE Y SEGURIDAD EN LA ORGANIZACIÓN</t>
   </si>
   <si>
@@ -1147,9 +1129,6 @@
   </si>
   <si>
     <t>MILKA SARAY</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
   </si>
   <si>
     <t>RONALDO</t>
@@ -2630,7 +2609,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2661,10 +2640,10 @@
         <v>174</v>
       </c>
       <c r="C2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E2" t="s">
         <v>35</v>
@@ -2684,10 +2663,10 @@
         <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2704,10 +2683,10 @@
         <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E4" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2724,10 +2703,10 @@
         <v>113</v>
       </c>
       <c r="D5" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="E5" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2735,19 +2714,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>23330051920184</v>
+        <v>23330051920185</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>205</v>
       </c>
       <c r="D6" t="s">
-        <v>208</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2755,19 +2734,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>23330051920185</v>
+        <v>23330051920188</v>
       </c>
       <c r="B7" t="s">
-        <v>127</v>
+        <v>201</v>
       </c>
       <c r="C7" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>213</v>
       </c>
       <c r="E7" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2775,19 +2754,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>23330051920189</v>
+        <v>23330051920188</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>201</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>206</v>
       </c>
       <c r="D8" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E8" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2795,19 +2774,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>23330051920190</v>
+        <v>23330051920189</v>
       </c>
       <c r="B9" t="s">
         <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>203</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E9" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2821,13 +2800,13 @@
         <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D10" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="E10" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2835,19 +2814,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>23330051920192</v>
+        <v>23330051920190</v>
       </c>
       <c r="B11" t="s">
-        <v>152</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D11" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>221</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2855,16 +2834,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>23330051920203</v>
+        <v>23330051920192</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>152</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>208</v>
       </c>
       <c r="D12" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E12" t="s">
         <v>35</v>
@@ -2875,19 +2854,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>23330051920204</v>
+        <v>23330051920202</v>
       </c>
       <c r="B13" t="s">
+        <v>202</v>
+      </c>
+      <c r="C13" t="s">
         <v>65</v>
       </c>
-      <c r="C13" t="s">
-        <v>48</v>
-      </c>
       <c r="D13" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E13" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -2895,19 +2874,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>23330051920212</v>
+        <v>23330051920202</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>202</v>
       </c>
       <c r="C14" t="s">
-        <v>205</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E14" t="s">
-        <v>35</v>
+        <v>222</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -2915,21 +2894,81 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>23330051920212</v>
+        <v>23330051920203</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>205</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E15" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
       <c r="F15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>23330051920204</v>
+      </c>
+      <c r="B16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" t="s">
+        <v>219</v>
+      </c>
+      <c r="E16" t="s">
+        <v>222</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>23330051920324</v>
+      </c>
+      <c r="B17" t="s">
+        <v>203</v>
+      </c>
+      <c r="C17" t="s">
+        <v>209</v>
+      </c>
+      <c r="D17" t="s">
+        <v>220</v>
+      </c>
+      <c r="E17" t="s">
+        <v>222</v>
+      </c>
+      <c r="F17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>23330051920324</v>
+      </c>
+      <c r="B18" t="s">
+        <v>203</v>
+      </c>
+      <c r="C18" t="s">
+        <v>209</v>
+      </c>
+      <c r="D18" t="s">
+        <v>220</v>
+      </c>
+      <c r="E18" t="s">
+        <v>223</v>
+      </c>
+      <c r="F18">
         <v>5</v>
       </c>
     </row>
@@ -3158,13 +3197,13 @@
         <v>23330051920215</v>
       </c>
       <c r="B2" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C2" t="s">
         <v>175</v>
       </c>
       <c r="D2" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E2" t="s">
         <v>35</v>
@@ -3178,16 +3217,16 @@
         <v>23330051920216</v>
       </c>
       <c r="B3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D3" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="E3" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3198,16 +3237,16 @@
         <v>23330051920216</v>
       </c>
       <c r="B4" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C4" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D4" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="E4" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3221,13 +3260,13 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D5" t="s">
         <v>126</v>
       </c>
       <c r="E5" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3241,13 +3280,13 @@
         <v>191</v>
       </c>
       <c r="C6" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="D6" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="E6" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3258,16 +3297,16 @@
         <v>23330051920248</v>
       </c>
       <c r="B7" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C7" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D7" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="E7" t="s">
-        <v>234</v>
+        <v>35</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3278,16 +3317,16 @@
         <v>23330051920248</v>
       </c>
       <c r="B8" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C8" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D8" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>223</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3304,10 +3343,10 @@
         <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="E9" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3324,7 +3363,7 @@
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="E10" t="s">
         <v>35</v>
@@ -3341,13 +3380,13 @@
         <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D11" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="E11" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3358,16 +3397,16 @@
         <v>23330051920277</v>
       </c>
       <c r="B12" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C12" t="s">
         <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="E12" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3378,16 +3417,16 @@
         <v>23330051920277</v>
       </c>
       <c r="B13" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C13" t="s">
         <v>109</v>
       </c>
       <c r="D13" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="E13" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -3398,16 +3437,16 @@
         <v>23330051920280</v>
       </c>
       <c r="B14" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C14" t="s">
         <v>64</v>
       </c>
       <c r="D14" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E14" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -3424,10 +3463,10 @@
         <v>39</v>
       </c>
       <c r="D15" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="E15" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -3444,10 +3483,10 @@
         <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="E16" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -3488,16 +3527,16 @@
         <v>23330051920218</v>
       </c>
       <c r="B2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E2" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3508,16 +3547,16 @@
         <v>23330051920220</v>
       </c>
       <c r="B3" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C3" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D3" t="s">
         <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3528,16 +3567,16 @@
         <v>23330051920220</v>
       </c>
       <c r="B4" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C4" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D4" t="s">
         <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3554,10 +3593,10 @@
         <v>174</v>
       </c>
       <c r="D5" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E5" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3568,16 +3607,16 @@
         <v>23330051920222</v>
       </c>
       <c r="B6" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E6" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3588,16 +3627,16 @@
         <v>23330051920224</v>
       </c>
       <c r="B7" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="C7" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="D7" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="E7" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3614,10 +3653,10 @@
         <v>192</v>
       </c>
       <c r="D8" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>223</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3634,10 +3673,10 @@
         <v>192</v>
       </c>
       <c r="D9" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="E9" t="s">
-        <v>234</v>
+        <v>35</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3651,13 +3690,13 @@
         <v>152</v>
       </c>
       <c r="C10" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="D10" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="E10" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3674,10 +3713,10 @@
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="E11" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3691,13 +3730,13 @@
         <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="D12" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E12" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3711,13 +3750,13 @@
         <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="D13" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E13" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -3734,10 +3773,10 @@
         <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E14" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -3754,10 +3793,10 @@
         <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E15" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -3771,13 +3810,13 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="D16" t="s">
         <v>52</v>
       </c>
       <c r="E16" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -3791,13 +3830,13 @@
         <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="D17" t="s">
         <v>52</v>
       </c>
       <c r="E17" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -3808,16 +3847,16 @@
         <v>23330051920243</v>
       </c>
       <c r="B18" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="C18" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="D18" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="E18" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -3828,13 +3867,13 @@
         <v>23330051920249</v>
       </c>
       <c r="B19" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="C19" t="s">
         <v>45</v>
       </c>
       <c r="D19" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E19" t="s">
         <v>35</v>
@@ -3848,16 +3887,16 @@
         <v>23330051920251</v>
       </c>
       <c r="B20" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C20" t="s">
         <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E20" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -3868,16 +3907,16 @@
         <v>23330051920253</v>
       </c>
       <c r="B21" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="C21" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="D21" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="E21" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -3891,10 +3930,10 @@
         <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="D22" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E22" t="s">
         <v>35</v>
@@ -3908,16 +3947,16 @@
         <v>23330051920264</v>
       </c>
       <c r="B23" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="C23" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="D23" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="E23" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F23">
         <v>5</v>
@@ -3928,16 +3967,16 @@
         <v>23330051920264</v>
       </c>
       <c r="B24" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="C24" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="D24" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="E24" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -3951,13 +3990,13 @@
         <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D25" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="E25" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -3974,10 +4013,10 @@
         <v>20</v>
       </c>
       <c r="D26" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="E26" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F26">
         <v>5</v>
@@ -3994,10 +4033,10 @@
         <v>20</v>
       </c>
       <c r="D27" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="E27" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F27">
         <v>5</v>
@@ -4014,10 +4053,10 @@
         <v>150</v>
       </c>
       <c r="D28" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E28" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F28">
         <v>5</v>
@@ -4034,10 +4073,10 @@
         <v>150</v>
       </c>
       <c r="D29" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E29" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F29">
         <v>5</v>
@@ -4050,7 +4089,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4075,19 +4114,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>23330051920281</v>
+        <v>23330051920282</v>
       </c>
       <c r="B2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C2" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="D2" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E2" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4098,16 +4137,16 @@
         <v>23330051920282</v>
       </c>
       <c r="B3" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C3" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="D3" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="E3" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4115,19 +4154,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>23330051920282</v>
+        <v>23330051920284</v>
       </c>
       <c r="B4" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="C4" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="D4" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="E4" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4135,19 +4174,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>23330051920284</v>
+        <v>23330051920285</v>
       </c>
       <c r="B5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C5" t="s">
-        <v>278</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="E5" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4155,19 +4194,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>23330051920284</v>
+        <v>23330051920285</v>
       </c>
       <c r="B6" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C6" t="s">
-        <v>278</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="E6" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4175,19 +4214,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>23330051920285</v>
+        <v>23330051920299</v>
       </c>
       <c r="B7" t="s">
-        <v>273</v>
+        <v>134</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="E7" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4195,19 +4234,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>23330051920285</v>
+        <v>23330051920308</v>
       </c>
       <c r="B8" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="E8" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4215,19 +4254,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>23330051920299</v>
+        <v>23330051920308</v>
       </c>
       <c r="B9" t="s">
-        <v>134</v>
+        <v>279</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="E9" t="s">
-        <v>215</v>
+        <v>35</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4238,16 +4277,16 @@
         <v>23330051920310</v>
       </c>
       <c r="B10" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="C10" t="s">
         <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="E10" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4255,19 +4294,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>23330051920336</v>
+        <v>23330051920311</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>175</v>
       </c>
       <c r="C11" t="s">
-        <v>251</v>
+        <v>152</v>
       </c>
       <c r="D11" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="E11" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -4275,16 +4314,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>23330051920348</v>
+        <v>23330051920311</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>175</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>152</v>
       </c>
       <c r="D12" t="s">
-        <v>131</v>
+        <v>291</v>
       </c>
       <c r="E12" t="s">
         <v>35</v>
@@ -4295,19 +4334,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>23330051920356</v>
+        <v>23330051920336</v>
       </c>
       <c r="B13" t="s">
-        <v>275</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="D13" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E13" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -4315,21 +4354,101 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
+        <v>23330051920347</v>
+      </c>
+      <c r="B14" t="s">
+        <v>281</v>
+      </c>
+      <c r="C14" t="s">
+        <v>174</v>
+      </c>
+      <c r="D14" t="s">
+        <v>293</v>
+      </c>
+      <c r="E14" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>23330051920347</v>
+      </c>
+      <c r="B15" t="s">
+        <v>281</v>
+      </c>
+      <c r="C15" t="s">
+        <v>174</v>
+      </c>
+      <c r="D15" t="s">
+        <v>293</v>
+      </c>
+      <c r="E15" t="s">
+        <v>221</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>23330051920348</v>
+      </c>
+      <c r="B16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" t="s">
+        <v>131</v>
+      </c>
+      <c r="E16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>23330051920356</v>
+      </c>
+      <c r="B17" t="s">
+        <v>282</v>
+      </c>
+      <c r="C17" t="s">
+        <v>252</v>
+      </c>
+      <c r="D17" t="s">
+        <v>294</v>
+      </c>
+      <c r="E17" t="s">
+        <v>221</v>
+      </c>
+      <c r="F17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
         <v>23330051920363</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B18" t="s">
         <v>151</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C18" t="s">
         <v>90</v>
       </c>
-      <c r="D14" t="s">
-        <v>287</v>
-      </c>
-      <c r="E14" t="s">
-        <v>215</v>
-      </c>
-      <c r="F14">
+      <c r="D18" t="s">
+        <v>295</v>
+      </c>
+      <c r="E18" t="s">
+        <v>222</v>
+      </c>
+      <c r="F18">
         <v>5</v>
       </c>
     </row>
@@ -4340,7 +4459,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4371,13 +4490,13 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="D2" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="E2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4388,16 +4507,16 @@
         <v>23330051920300</v>
       </c>
       <c r="B3" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="C3" t="s">
         <v>111</v>
       </c>
       <c r="D3" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="E3" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4405,19 +4524,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>23330051920300</v>
+        <v>23330051920303</v>
       </c>
       <c r="B4" t="s">
-        <v>288</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
+        <v>297</v>
       </c>
       <c r="D4" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="E4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4434,10 +4553,10 @@
         <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="E5" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4445,19 +4564,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>23330051920342</v>
+        <v>23330051920332</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>298</v>
       </c>
       <c r="D6" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="E6" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4465,21 +4584,61 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
+        <v>23330051920332</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D7" t="s">
+        <v>303</v>
+      </c>
+      <c r="E7" t="s">
+        <v>222</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
         <v>23330051920342</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>20</v>
       </c>
-      <c r="D7" t="s">
-        <v>292</v>
-      </c>
-      <c r="E7" t="s">
-        <v>234</v>
-      </c>
-      <c r="F7">
+      <c r="D8" t="s">
+        <v>304</v>
+      </c>
+      <c r="E8" t="s">
+        <v>221</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>23330051920342</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>304</v>
+      </c>
+      <c r="E9" t="s">
+        <v>223</v>
+      </c>
+      <c r="F9">
         <v>5</v>
       </c>
     </row>
@@ -4524,7 +4683,7 @@
         <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="E2" t="s">
         <v>133</v>
@@ -4541,10 +4700,10 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="D3" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="E3" t="s">
         <v>133</v>
@@ -4558,13 +4717,13 @@
         <v>22330051920363</v>
       </c>
       <c r="B4" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="E4" t="s">
         <v>133</v>
@@ -4581,10 +4740,10 @@
         <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="D5" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="E5" t="s">
         <v>133</v>
@@ -4601,10 +4760,10 @@
         <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="D6" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="E6" t="s">
         <v>133</v>
@@ -4651,10 +4810,10 @@
         <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="D2" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="E2" t="s">
         <v>171</v>
@@ -4671,10 +4830,10 @@
         <v>48</v>
       </c>
       <c r="C3" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="D3" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="E3" t="s">
         <v>143</v>
@@ -4688,13 +4847,13 @@
         <v>22330051920233</v>
       </c>
       <c r="B4" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="C4" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D4" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="E4" t="s">
         <v>142</v>
@@ -4708,13 +4867,13 @@
         <v>22330051920236</v>
       </c>
       <c r="B5" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="C5" t="s">
         <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="E5" t="s">
         <v>141</v>
@@ -4728,13 +4887,13 @@
         <v>22330051920236</v>
       </c>
       <c r="B6" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="C6" t="s">
         <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="E6" t="s">
         <v>133</v>
@@ -4748,13 +4907,13 @@
         <v>22330051920256</v>
       </c>
       <c r="B7" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="C7" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="D7" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="E7" t="s">
         <v>141</v>
@@ -4774,7 +4933,7 @@
         <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="E8" t="s">
         <v>141</v>
@@ -4821,10 +4980,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="D2" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="E2" t="s">
         <v>142</v>
@@ -4841,10 +5000,10 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="D3" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="E3" t="s">
         <v>133</v>
@@ -4861,10 +5020,10 @@
         <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="D4" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="E4" t="s">
         <v>142</v>
@@ -4881,10 +5040,10 @@
         <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="D5" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="E5" t="s">
         <v>142</v>
@@ -4898,13 +5057,13 @@
         <v>22330051920286</v>
       </c>
       <c r="B6" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C6" t="s">
         <v>147</v>
       </c>
       <c r="D6" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="E6" t="s">
         <v>142</v>
@@ -4924,7 +5083,7 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="E7" t="s">
         <v>133</v>
@@ -4968,13 +5127,13 @@
         <v>21330051920002</v>
       </c>
       <c r="B2" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C2" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="D2" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="E2" t="s">
         <v>133</v>
@@ -4988,13 +5147,13 @@
         <v>22330051920222</v>
       </c>
       <c r="B3" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="C3" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="D3" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="E3" t="s">
         <v>141</v>
@@ -5014,7 +5173,7 @@
         <v>149</v>
       </c>
       <c r="D4" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="E4" t="s">
         <v>133</v>
@@ -5061,10 +5220,10 @@
         <v>137</v>
       </c>
       <c r="C2" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="D2" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="E2" t="s">
         <v>142</v>
@@ -5084,7 +5243,7 @@
         <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="E3" t="s">
         <v>142</v>
@@ -5100,7 +5259,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5125,19 +5284,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920018</v>
+        <v>20330051920049</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>340</v>
       </c>
       <c r="C2" t="s">
-        <v>329</v>
+        <v>129</v>
       </c>
       <c r="D2" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="E2" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5154,7 +5313,7 @@
         <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="E3" t="s">
         <v>199</v>
@@ -5168,16 +5327,16 @@
         <v>20330051920366</v>
       </c>
       <c r="B4" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="C4" t="s">
         <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="E4" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5185,16 +5344,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920367</v>
+        <v>20330051920366</v>
       </c>
       <c r="B5" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="C5" t="s">
         <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="E5" t="s">
         <v>199</v>
@@ -5205,19 +5364,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920003</v>
+        <v>20330051920367</v>
       </c>
       <c r="B6" t="s">
-        <v>181</v>
+        <v>341</v>
       </c>
       <c r="C6" t="s">
-        <v>288</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="E6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5225,16 +5384,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920012</v>
+        <v>20330051920367</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>341</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="E7" t="s">
         <v>180</v>
@@ -5254,32 +5413,12 @@
         <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="E8" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="F8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920015</v>
-      </c>
-      <c r="B9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" t="s">
-        <v>336</v>
-      </c>
-      <c r="E9" t="s">
-        <v>180</v>
-      </c>
-      <c r="F9">
         <v>5</v>
       </c>
     </row>
@@ -5500,7 +5639,7 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5534,10 +5673,10 @@
         <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="E2" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5545,16 +5684,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920071</v>
+        <v>21330051920075</v>
       </c>
       <c r="B3" t="s">
-        <v>150</v>
+        <v>348</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="E3" t="s">
         <v>197</v>
@@ -5565,16 +5704,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920075</v>
+        <v>21330051920078</v>
       </c>
       <c r="B4" t="s">
-        <v>338</v>
+        <v>152</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="E4" t="s">
         <v>197</v>
@@ -5585,19 +5724,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920077</v>
+        <v>21330051920078</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>152</v>
       </c>
       <c r="C5" t="s">
-        <v>340</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>351</v>
       </c>
       <c r="E5" t="s">
-        <v>179</v>
+        <v>354</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5625,19 +5764,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920082</v>
+        <v>21330051920109</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>226</v>
       </c>
       <c r="C7" t="s">
-        <v>341</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="E7" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5645,121 +5784,21 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920082</v>
+        <v>21330051920260</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>341</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="E8" t="s">
-        <v>197</v>
+        <v>354</v>
       </c>
       <c r="F8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920102</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>127</v>
-      </c>
-      <c r="D9" t="s">
-        <v>346</v>
-      </c>
-      <c r="E9" t="s">
-        <v>179</v>
-      </c>
-      <c r="F9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920109</v>
-      </c>
-      <c r="B10" t="s">
-        <v>220</v>
-      </c>
-      <c r="C10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" t="s">
-        <v>347</v>
-      </c>
-      <c r="E10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920109</v>
-      </c>
-      <c r="B11" t="s">
-        <v>220</v>
-      </c>
-      <c r="C11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" t="s">
-        <v>347</v>
-      </c>
-      <c r="E11" t="s">
-        <v>350</v>
-      </c>
-      <c r="F11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920260</v>
-      </c>
-      <c r="B12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" t="s">
-        <v>348</v>
-      </c>
-      <c r="E12" t="s">
-        <v>350</v>
-      </c>
-      <c r="F12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920305</v>
-      </c>
-      <c r="B13" t="s">
-        <v>339</v>
-      </c>
-      <c r="C13" t="s">
-        <v>342</v>
-      </c>
-      <c r="D13" t="s">
-        <v>349</v>
-      </c>
-      <c r="E13" t="s">
-        <v>179</v>
-      </c>
-      <c r="F13">
         <v>5</v>
       </c>
     </row>
@@ -5804,10 +5843,10 @@
         <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5820,7 +5859,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5845,161 +5884,21 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920035</v>
+        <v>21330051920059</v>
       </c>
       <c r="B2" t="s">
-        <v>294</v>
+        <v>356</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>357</v>
       </c>
       <c r="D2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E2" t="s">
         <v>358</v>
       </c>
-      <c r="E2" t="s">
-        <v>179</v>
-      </c>
       <c r="F2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920036</v>
-      </c>
-      <c r="B3" t="s">
-        <v>352</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>359</v>
-      </c>
-      <c r="E3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920046</v>
-      </c>
-      <c r="B4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C4" t="s">
-        <v>355</v>
-      </c>
-      <c r="D4" t="s">
-        <v>360</v>
-      </c>
-      <c r="E4" t="s">
-        <v>179</v>
-      </c>
-      <c r="F4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920048</v>
-      </c>
-      <c r="B5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>361</v>
-      </c>
-      <c r="E5" t="s">
-        <v>179</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920057</v>
-      </c>
-      <c r="B6" t="s">
-        <v>151</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" t="s">
-        <v>362</v>
-      </c>
-      <c r="E6" t="s">
-        <v>179</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920059</v>
-      </c>
-      <c r="B7" t="s">
-        <v>353</v>
-      </c>
-      <c r="C7" t="s">
-        <v>356</v>
-      </c>
-      <c r="D7" t="s">
-        <v>155</v>
-      </c>
-      <c r="E7" t="s">
-        <v>364</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920065</v>
-      </c>
-      <c r="B8" t="s">
-        <v>147</v>
-      </c>
-      <c r="C8" t="s">
-        <v>357</v>
-      </c>
-      <c r="D8" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" t="s">
-        <v>179</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920067</v>
-      </c>
-      <c r="B9" t="s">
-        <v>354</v>
-      </c>
-      <c r="C9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" t="s">
-        <v>363</v>
-      </c>
-      <c r="E9" t="s">
-        <v>179</v>
-      </c>
-      <c r="F9">
         <v>5</v>
       </c>
     </row>
@@ -6010,7 +5909,7 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6038,16 +5937,16 @@
         <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="C2" t="s">
         <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="E2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6055,19 +5954,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920135</v>
+        <v>21330051920140</v>
       </c>
       <c r="B3" t="s">
-        <v>325</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="E3" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6075,101 +5974,41 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920140</v>
+        <v>21330051920147</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="E4" t="s">
         <v>179</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920140</v>
+        <v>21330051920147</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="D5" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="E5" t="s">
         <v>197</v>
       </c>
       <c r="F5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920141</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>328</v>
-      </c>
-      <c r="D6" t="s">
-        <v>367</v>
-      </c>
-      <c r="E6" t="s">
-        <v>179</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920147</v>
-      </c>
-      <c r="B7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" t="s">
-        <v>368</v>
-      </c>
-      <c r="E7" t="s">
-        <v>179</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920147</v>
-      </c>
-      <c r="B8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D8" t="s">
-        <v>368</v>
-      </c>
-      <c r="E8" t="s">
-        <v>197</v>
-      </c>
-      <c r="F8">
         <v>5</v>
       </c>
     </row>

--- a/Rescatables20231.xlsx
+++ b/Rescatables20231.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="347">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -318,282 +318,276 @@
     <t>GUTIERREZ</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>MANZANO</t>
+  </si>
+  <si>
+    <t>DANIA LIZETH</t>
+  </si>
+  <si>
+    <t>ANGEL URIEL</t>
+  </si>
+  <si>
+    <t>ABREGO</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>LARRACILLA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>VELUETA</t>
+  </si>
+  <si>
+    <t>ZGAIP</t>
+  </si>
+  <si>
+    <t>VIVANCO</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>SULU ALAN</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>DORIAN ALEXANDER</t>
+  </si>
+  <si>
+    <t>HECTOR</t>
+  </si>
+  <si>
+    <t>JOSELYN</t>
+  </si>
+  <si>
+    <t>KEVIN IVAN</t>
+  </si>
+  <si>
+    <t>MONICA</t>
+  </si>
+  <si>
+    <t>VICTOR JESUS</t>
+  </si>
+  <si>
+    <t>JONATHAN ISAI</t>
+  </si>
+  <si>
+    <t>DANNAE ADALID</t>
+  </si>
+  <si>
+    <t>ADAIR DE JESUS</t>
+  </si>
+  <si>
+    <t>LUIS AARON</t>
+  </si>
+  <si>
+    <t>YAMILETH</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>JOAQUIN</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>BIOLOGÍA</t>
+  </si>
+  <si>
+    <t>ÉTICA</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>PRADO</t>
+  </si>
+  <si>
+    <t>LUGO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>ANETTE</t>
+  </si>
+  <si>
+    <t>ZAYRA</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>GEOMETRÍA ANALÍTICA</t>
+  </si>
+  <si>
+    <t>INGLÉS III</t>
+  </si>
+  <si>
+    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS PARASITOLÓGICAS</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>AYOHUA</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>JIMENA</t>
+  </si>
+  <si>
+    <t>MELANIE SOFIA</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>JESUS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>JENKINS</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>CARLOS YAEL</t>
+  </si>
+  <si>
+    <t>ROGGER JUSEFH</t>
+  </si>
+  <si>
+    <t>ARTHUR RICHARD</t>
+  </si>
+  <si>
+    <t>PIÑA</t>
+  </si>
+  <si>
+    <t>MEZA</t>
+  </si>
+  <si>
+    <t>ABIGAIL ANTONIA</t>
+  </si>
+  <si>
+    <t>ACSA FERNANDA</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS BACTERIOLÓGICAS</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>MAYO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>AYLIN MELISSA</t>
+  </si>
+  <si>
+    <t>ALDAHIR</t>
+  </si>
+  <si>
+    <t>LUIS OMAR</t>
+  </si>
+  <si>
+    <t>FÍSICA II</t>
+  </si>
+  <si>
+    <t>CIENCIA, TECNOLOGÍA, SOCIEDAD Y VALORES</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>MANZANO</t>
-  </si>
-  <si>
-    <t>DANIA LIZETH</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>ANGEL URIEL</t>
-  </si>
-  <si>
-    <t>ABREGO</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>LARRACILLA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>VELUETA</t>
-  </si>
-  <si>
-    <t>ZGAIP</t>
-  </si>
-  <si>
-    <t>VIVANCO</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>SULU ALAN</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>DORIAN ALEXANDER</t>
-  </si>
-  <si>
-    <t>HECTOR</t>
-  </si>
-  <si>
-    <t>JOSELYN</t>
-  </si>
-  <si>
-    <t>KEVIN IVAN</t>
-  </si>
-  <si>
-    <t>MONICA</t>
-  </si>
-  <si>
-    <t>VICTOR JESUS</t>
-  </si>
-  <si>
-    <t>JONATHAN ISAI</t>
-  </si>
-  <si>
-    <t>DANNAE ADALID</t>
-  </si>
-  <si>
-    <t>ADAIR DE JESUS</t>
-  </si>
-  <si>
-    <t>LUIS AARON</t>
-  </si>
-  <si>
-    <t>YAMILETH</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>JOAQUIN</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>BIOLOGÍA</t>
-  </si>
-  <si>
-    <t>ÉTICA</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>LUGO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>ANETTE</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>GEOMETRÍA ANALÍTICA</t>
-  </si>
-  <si>
-    <t>INGLÉS III</t>
-  </si>
-  <si>
-    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS PARASITOLÓGICAS</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>AYOHUA</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>JIMENA</t>
-  </si>
-  <si>
-    <t>MELANIE SOFIA</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>JESUS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
-    <t>JENKINS</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>CARLOS YAEL</t>
-  </si>
-  <si>
-    <t>ROGGER JUSEFH</t>
-  </si>
-  <si>
-    <t>ARTHUR RICHARD</t>
-  </si>
-  <si>
-    <t>PIÑA</t>
-  </si>
-  <si>
-    <t>MEZA</t>
-  </si>
-  <si>
-    <t>ABIGAIL ANTONIA</t>
-  </si>
-  <si>
-    <t>ACSA FERNANDA</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS BACTERIOLÓGICAS</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>MAYO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>AYLIN MELISSA</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>LUIS OMAR</t>
-  </si>
-  <si>
-    <t>FÍSICA II</t>
-  </si>
-  <si>
-    <t>CIENCIA, TECNOLOGÍA, SOCIEDAD Y VALORES</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
     <t>JOSELIN</t>
   </si>
   <si>
@@ -603,12 +597,6 @@
     <t>CONSTRUYE BASES DE DATOS PARA APLICACIONES WEB</t>
   </si>
   <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>KARINA</t>
-  </si>
-  <si>
     <t>NUBE</t>
   </si>
   <si>
@@ -657,9 +645,6 @@
     <t>NARVAEZ</t>
   </si>
   <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
     <t>DAMIAN</t>
   </si>
   <si>
@@ -675,7 +660,7 @@
     <t>CARRERA</t>
   </si>
   <si>
-    <t>LIBRADO</t>
+    <t>CIRUELO</t>
   </si>
   <si>
     <t>JESUS JAREF</t>
@@ -708,7 +693,7 @@
     <t>ROBBIE ALONSO</t>
   </si>
   <si>
-    <t>ARMANDO GABRIEL</t>
+    <t>SABDY</t>
   </si>
   <si>
     <t>Pensamiento matemático I</t>
@@ -717,69 +702,66 @@
     <t>Ciencias sociales I</t>
   </si>
   <si>
+    <t>CALVA</t>
+  </si>
+  <si>
+    <t>FUENTES</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>CANDELARIO</t>
+  </si>
+  <si>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>ANGEL JESUS</t>
+  </si>
+  <si>
+    <t>INGRID ISABEL</t>
+  </si>
+  <si>
+    <t>VIVIANA JOSELIN</t>
+  </si>
+  <si>
+    <t>XIMENA ISABEL</t>
+  </si>
+  <si>
+    <t>MIGUEL ENRIQUE</t>
+  </si>
+  <si>
+    <t>DANNA PAOLA</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>ANGEL ABRAHAM</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
     <t>Inglés I</t>
   </si>
   <si>
-    <t>CALVA</t>
-  </si>
-  <si>
-    <t>FUENTES</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>CANDELARIO</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>ANGEL JESUS</t>
-  </si>
-  <si>
-    <t>INGRID ISABEL</t>
-  </si>
-  <si>
-    <t>VIVIANA JOSELIN</t>
-  </si>
-  <si>
-    <t>XIMENA ISABEL</t>
-  </si>
-  <si>
-    <t>MIGUEL ENRIQUE</t>
-  </si>
-  <si>
-    <t>DANNA PAOLA</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>ANGEL ABRAHAM</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
     <t>ALMANZA</t>
   </si>
   <si>
     <t>BARRAGAN</t>
   </si>
   <si>
-    <t>CUAPIO</t>
-  </si>
-  <si>
     <t>DORANTES</t>
   </si>
   <si>
@@ -789,51 +771,39 @@
     <t>LUIS</t>
   </si>
   <si>
-    <t>MARQUEZ</t>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>MACUIXTLE</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>NATH</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
   </si>
   <si>
     <t>MENDEZ</t>
   </si>
   <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>MACUIXTLE</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>NATH</t>
-  </si>
-  <si>
-    <t>MONDRAGON</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
     <t>VANESA BETHSABE</t>
   </si>
   <si>
-    <t>RAMSES</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
     <t>ROBERTO</t>
   </si>
   <si>
@@ -843,9 +813,6 @@
     <t>MARIANA</t>
   </si>
   <si>
-    <t>JAIRO</t>
-  </si>
-  <si>
     <t>MIRIAM</t>
   </si>
   <si>
@@ -855,15 +822,12 @@
     <t>AARON ZACHARY</t>
   </si>
   <si>
+    <t>RAYMUNDO</t>
+  </si>
+  <si>
     <t>DIANA LAURA</t>
   </si>
   <si>
-    <t>DIEGO GREGORIO</t>
-  </si>
-  <si>
-    <t>ANGEL ADRIAN</t>
-  </si>
-  <si>
     <t>AIDE SCARLET</t>
   </si>
   <si>
@@ -966,9 +930,6 @@
     <t>TLAXCALA</t>
   </si>
   <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
     <t>PLIEGO</t>
   </si>
   <si>
@@ -987,22 +948,22 @@
     <t>JOSE ANTONIO</t>
   </si>
   <si>
+    <t>LLANOS</t>
+  </si>
+  <si>
     <t>BONILLA</t>
   </si>
   <si>
     <t>DECTOR</t>
   </si>
   <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
     <t>MENA</t>
   </si>
   <si>
     <t>IBAÑEZ</t>
   </si>
   <si>
-    <t>TETLACTLE</t>
+    <t>SERGIO</t>
   </si>
   <si>
     <t>ANGELES</t>
@@ -1014,9 +975,6 @@
     <t>KEVIN ALEXIS</t>
   </si>
   <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
     <t>AILYN</t>
   </si>
   <si>
@@ -1053,6 +1011,9 @@
     <t>ADRIAN</t>
   </si>
   <si>
+    <t>LILIANA</t>
+  </si>
+  <si>
     <t>EVELYN ROSALIA</t>
   </si>
   <si>
@@ -1077,19 +1038,13 @@
     <t>RAFAEL</t>
   </si>
   <si>
-    <t>DULIAM</t>
-  </si>
-  <si>
     <t>ELI ANTONIO</t>
   </si>
   <si>
     <t>ISAAC</t>
   </si>
   <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
-    <t>REALIZA MANTENIMIENTO A LAS INSTALACIONES ELÉCTRICAS RESIDENCIALES, COMERCIALES E INDUSTRIALES</t>
+    <t>LUIS ENRIQUE</t>
   </si>
   <si>
     <t>ESPIRITU</t>
@@ -1810,13 +1765,13 @@
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -1827,16 +1782,16 @@
         <v>22330051920068</v>
       </c>
       <c r="B3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -1850,13 +1805,13 @@
         <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -1870,13 +1825,13 @@
         <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -1887,16 +1842,16 @@
         <v>22330051920084</v>
       </c>
       <c r="B6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -1907,16 +1862,16 @@
         <v>22330051920084</v>
       </c>
       <c r="B7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D7" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E7" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -1930,13 +1885,13 @@
         <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D8" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E8" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -1947,16 +1902,16 @@
         <v>22330051920333</v>
       </c>
       <c r="B9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -1967,16 +1922,16 @@
         <v>22330051920334</v>
       </c>
       <c r="B10" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C10" t="s">
         <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E10" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2017,16 +1972,16 @@
         <v>22330051920034</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2040,13 +1995,13 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2057,16 +2012,16 @@
         <v>22330051920189</v>
       </c>
       <c r="B4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2110,13 +2065,13 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2130,13 +2085,13 @@
         <v>44</v>
       </c>
       <c r="C3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2147,16 +2102,16 @@
         <v>22330051920352</v>
       </c>
       <c r="B4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2197,16 +2152,16 @@
         <v>20330051920069</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C2" t="s">
         <v>64</v>
       </c>
       <c r="D2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E2" t="s">
         <v>176</v>
-      </c>
-      <c r="E2" t="s">
-        <v>179</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2217,16 +2172,16 @@
         <v>21330051920001</v>
       </c>
       <c r="B3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D3" t="s">
         <v>174</v>
       </c>
-      <c r="D3" t="s">
-        <v>177</v>
-      </c>
       <c r="E3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2237,16 +2192,16 @@
         <v>21330051920167</v>
       </c>
       <c r="B4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D4" t="s">
         <v>175</v>
       </c>
-      <c r="D4" t="s">
-        <v>178</v>
-      </c>
       <c r="E4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2289,7 +2244,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2317,16 +2272,16 @@
         <v>21330051920149</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>179</v>
       </c>
       <c r="D2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E2" t="s">
         <v>182</v>
-      </c>
-      <c r="E2" t="s">
-        <v>184</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2334,19 +2289,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920334</v>
+        <v>21330051920149</v>
       </c>
       <c r="B3" t="s">
-        <v>181</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="D3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2357,18 +2312,38 @@
         <v>21330051920334</v>
       </c>
       <c r="B4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D4" t="s">
         <v>181</v>
       </c>
-      <c r="C4" t="s">
-        <v>151</v>
-      </c>
-      <c r="D4" t="s">
-        <v>183</v>
-      </c>
       <c r="E4" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>21330051920334</v>
+      </c>
+      <c r="B5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E5" t="s">
+        <v>182</v>
+      </c>
+      <c r="F5">
         <v>5</v>
       </c>
     </row>
@@ -2379,7 +2354,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2399,26 +2374,6 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920221</v>
-      </c>
-      <c r="B2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C2" t="s">
-        <v>185</v>
-      </c>
-      <c r="D2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E2" t="s">
-        <v>179</v>
-      </c>
-      <c r="F2">
         <v>5</v>
       </c>
     </row>
@@ -2460,13 +2415,13 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D2" t="s">
         <v>189</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>193</v>
-      </c>
-      <c r="E2" t="s">
-        <v>197</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2477,16 +2432,16 @@
         <v>20330051920100</v>
       </c>
       <c r="B3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D3" t="s">
         <v>190</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>194</v>
-      </c>
-      <c r="E3" t="s">
-        <v>198</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2497,16 +2452,16 @@
         <v>20330051920100</v>
       </c>
       <c r="B4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D4" t="s">
         <v>190</v>
       </c>
-      <c r="D4" t="s">
-        <v>194</v>
-      </c>
       <c r="E4" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2520,13 +2475,13 @@
         <v>65</v>
       </c>
       <c r="C5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D5" t="s">
         <v>191</v>
       </c>
-      <c r="D5" t="s">
-        <v>195</v>
-      </c>
       <c r="E5" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2540,13 +2495,13 @@
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E6" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2557,16 +2512,16 @@
         <v>21330051920386</v>
       </c>
       <c r="B7" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C7" t="s">
         <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E7" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2609,7 +2564,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2637,13 +2592,13 @@
         <v>23330051920181</v>
       </c>
       <c r="B2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E2" t="s">
         <v>35</v>
@@ -2657,16 +2612,16 @@
         <v>23330051920183</v>
       </c>
       <c r="B3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C3" t="s">
         <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2677,16 +2632,16 @@
         <v>23330051920183</v>
       </c>
       <c r="B4" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C4" t="s">
         <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E4" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2700,13 +2655,13 @@
         <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="E5" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2717,16 +2672,16 @@
         <v>23330051920185</v>
       </c>
       <c r="B6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C6" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2737,16 +2692,16 @@
         <v>23330051920188</v>
       </c>
       <c r="B7" t="s">
+        <v>197</v>
+      </c>
+      <c r="C7" t="s">
         <v>201</v>
       </c>
-      <c r="C7" t="s">
-        <v>206</v>
-      </c>
       <c r="D7" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="E7" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2757,16 +2712,16 @@
         <v>23330051920188</v>
       </c>
       <c r="B8" t="s">
+        <v>197</v>
+      </c>
+      <c r="C8" t="s">
         <v>201</v>
       </c>
-      <c r="C8" t="s">
-        <v>206</v>
-      </c>
       <c r="D8" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="E8" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2783,10 +2738,10 @@
         <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="E9" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2800,13 +2755,13 @@
         <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D10" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E10" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2820,13 +2775,13 @@
         <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D11" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E11" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2837,13 +2792,13 @@
         <v>23330051920192</v>
       </c>
       <c r="B12" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C12" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D12" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="E12" t="s">
         <v>35</v>
@@ -2857,16 +2812,16 @@
         <v>23330051920202</v>
       </c>
       <c r="B13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C13" t="s">
         <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -2877,16 +2832,16 @@
         <v>23330051920202</v>
       </c>
       <c r="B14" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C14" t="s">
         <v>65</v>
       </c>
       <c r="D14" t="s">
+        <v>212</v>
+      </c>
+      <c r="E14" t="s">
         <v>217</v>
-      </c>
-      <c r="E14" t="s">
-        <v>222</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -2903,7 +2858,7 @@
         <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E15" t="s">
         <v>35</v>
@@ -2923,10 +2878,10 @@
         <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E16" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -2934,41 +2889,21 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>23330051920324</v>
+        <v>23330051920329</v>
       </c>
       <c r="B17" t="s">
-        <v>203</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D17" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E17" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="F17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>23330051920324</v>
-      </c>
-      <c r="B18" t="s">
-        <v>203</v>
-      </c>
-      <c r="C18" t="s">
-        <v>209</v>
-      </c>
-      <c r="D18" t="s">
-        <v>220</v>
-      </c>
-      <c r="E18" t="s">
-        <v>223</v>
-      </c>
-      <c r="F18">
         <v>5</v>
       </c>
     </row>
@@ -3197,13 +3132,13 @@
         <v>23330051920215</v>
       </c>
       <c r="B2" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D2" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="E2" t="s">
         <v>35</v>
@@ -3217,16 +3152,16 @@
         <v>23330051920216</v>
       </c>
       <c r="B3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="E3" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3237,16 +3172,16 @@
         <v>23330051920216</v>
       </c>
       <c r="B4" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C4" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D4" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="E4" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3260,13 +3195,13 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E5" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3277,16 +3212,16 @@
         <v>23330051920227</v>
       </c>
       <c r="B6" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C6" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D6" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="E6" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3297,13 +3232,13 @@
         <v>23330051920248</v>
       </c>
       <c r="B7" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C7" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D7" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="E7" t="s">
         <v>35</v>
@@ -3317,16 +3252,16 @@
         <v>23330051920248</v>
       </c>
       <c r="B8" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C8" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D8" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="E8" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3340,13 +3275,13 @@
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>179</v>
       </c>
       <c r="D9" t="s">
+        <v>229</v>
+      </c>
+      <c r="E9" t="s">
         <v>235</v>
-      </c>
-      <c r="E9" t="s">
-        <v>223</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3357,13 +3292,13 @@
         <v>23330051920254</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E10" t="s">
         <v>35</v>
@@ -3377,16 +3312,16 @@
         <v>23330051920256</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>179</v>
       </c>
       <c r="C11" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="D11" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E11" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3397,16 +3332,16 @@
         <v>23330051920277</v>
       </c>
       <c r="B12" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E12" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3417,16 +3352,16 @@
         <v>23330051920277</v>
       </c>
       <c r="B13" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D13" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -3437,16 +3372,16 @@
         <v>23330051920280</v>
       </c>
       <c r="B14" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C14" t="s">
         <v>64</v>
       </c>
       <c r="D14" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="E14" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -3457,16 +3392,16 @@
         <v>23330051920357</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>179</v>
       </c>
       <c r="C15" t="s">
         <v>39</v>
       </c>
       <c r="D15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E15" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -3477,16 +3412,16 @@
         <v>23330051920357</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>179</v>
       </c>
       <c r="C16" t="s">
         <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E16" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -3499,7 +3434,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3527,16 +3462,16 @@
         <v>23330051920218</v>
       </c>
       <c r="B2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="E2" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3547,16 +3482,16 @@
         <v>23330051920220</v>
       </c>
       <c r="B3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C3" t="s">
         <v>242</v>
-      </c>
-      <c r="C3" t="s">
-        <v>250</v>
       </c>
       <c r="D3" t="s">
         <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3567,16 +3502,16 @@
         <v>23330051920220</v>
       </c>
       <c r="B4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C4" t="s">
         <v>242</v>
-      </c>
-      <c r="C4" t="s">
-        <v>250</v>
       </c>
       <c r="D4" t="s">
         <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3584,19 +3519,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>23330051920221</v>
+        <v>23330051920224</v>
       </c>
       <c r="B5" t="s">
-        <v>127</v>
+        <v>238</v>
       </c>
       <c r="C5" t="s">
-        <v>174</v>
+        <v>243</v>
       </c>
       <c r="D5" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="E5" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3604,19 +3539,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>23330051920222</v>
+        <v>23330051920228</v>
       </c>
       <c r="B6" t="s">
-        <v>243</v>
+        <v>149</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>188</v>
       </c>
       <c r="D6" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="E6" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3624,19 +3559,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>23330051920224</v>
+        <v>23330051920228</v>
       </c>
       <c r="B7" t="s">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="C7" t="s">
-        <v>251</v>
+        <v>188</v>
       </c>
       <c r="D7" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="E7" t="s">
-        <v>223</v>
+        <v>35</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3644,19 +3579,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>23330051920228</v>
+        <v>23330051920229</v>
       </c>
       <c r="B8" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C8" t="s">
-        <v>192</v>
+        <v>244</v>
       </c>
       <c r="D8" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="E8" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3664,19 +3599,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>23330051920228</v>
+        <v>23330051920233</v>
       </c>
       <c r="B9" t="s">
-        <v>152</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>192</v>
+        <v>245</v>
       </c>
       <c r="D9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3684,19 +3619,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>23330051920229</v>
+        <v>23330051920233</v>
       </c>
       <c r="B10" t="s">
-        <v>152</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="D10" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="E10" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3704,19 +3639,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>23330051920230</v>
+        <v>23330051920234</v>
       </c>
       <c r="B11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="E11" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3724,19 +3659,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>23330051920233</v>
+        <v>23330051920236</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D12" t="s">
-        <v>266</v>
+        <v>52</v>
       </c>
       <c r="E12" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3744,19 +3679,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>23330051920233</v>
+        <v>23330051920243</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>239</v>
       </c>
       <c r="C13" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D13" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="E13" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -3764,19 +3699,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>23330051920234</v>
+        <v>23330051920247</v>
       </c>
       <c r="B14" t="s">
-        <v>154</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>244</v>
       </c>
       <c r="D14" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="E14" t="s">
-        <v>221</v>
+        <v>35</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -3784,19 +3719,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>23330051920234</v>
+        <v>23330051920247</v>
       </c>
       <c r="B15" t="s">
-        <v>154</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>244</v>
       </c>
       <c r="D15" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="E15" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -3804,19 +3739,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>23330051920236</v>
+        <v>23330051920249</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>240</v>
       </c>
       <c r="C16" t="s">
-        <v>254</v>
+        <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>52</v>
+        <v>259</v>
       </c>
       <c r="E16" t="s">
-        <v>223</v>
+        <v>35</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -3824,19 +3759,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>23330051920236</v>
+        <v>23330051920258</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="D17" t="s">
-        <v>52</v>
+        <v>260</v>
       </c>
       <c r="E17" t="s">
-        <v>221</v>
+        <v>35</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -3844,19 +3779,19 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>23330051920243</v>
+        <v>23330051920264</v>
       </c>
       <c r="B18" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C18" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="D18" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="E18" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -3864,19 +3799,19 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>23330051920249</v>
+        <v>23330051920264</v>
       </c>
       <c r="B19" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C19" t="s">
-        <v>45</v>
+        <v>249</v>
       </c>
       <c r="D19" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="E19" t="s">
-        <v>35</v>
+        <v>216</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -3884,19 +3819,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>23330051920251</v>
+        <v>23330051920265</v>
       </c>
       <c r="B20" t="s">
-        <v>247</v>
+        <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
+        <v>250</v>
       </c>
       <c r="D20" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E20" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -3904,19 +3839,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>23330051920253</v>
+        <v>23330051920271</v>
       </c>
       <c r="B21" t="s">
-        <v>248</v>
+        <v>110</v>
       </c>
       <c r="C21" t="s">
-        <v>256</v>
+        <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="E21" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -3924,19 +3859,19 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>23330051920258</v>
+        <v>23330051920271</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="C22" t="s">
-        <v>257</v>
+        <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="E22" t="s">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="F22">
         <v>5</v>
@@ -3944,141 +3879,21 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>23330051920264</v>
+        <v>23330051920335</v>
       </c>
       <c r="B23" t="s">
-        <v>249</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>258</v>
+        <v>147</v>
       </c>
       <c r="D23" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="E23" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>23330051920264</v>
-      </c>
-      <c r="B24" t="s">
-        <v>249</v>
-      </c>
-      <c r="C24" t="s">
-        <v>258</v>
-      </c>
-      <c r="D24" t="s">
-        <v>273</v>
-      </c>
-      <c r="E24" t="s">
-        <v>221</v>
-      </c>
-      <c r="F24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>23330051920265</v>
-      </c>
-      <c r="B25" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" t="s">
-        <v>248</v>
-      </c>
-      <c r="D25" t="s">
-        <v>274</v>
-      </c>
-      <c r="E25" t="s">
-        <v>223</v>
-      </c>
-      <c r="F25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>23330051920271</v>
-      </c>
-      <c r="B26" t="s">
-        <v>113</v>
-      </c>
-      <c r="C26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D26" t="s">
-        <v>275</v>
-      </c>
-      <c r="E26" t="s">
-        <v>221</v>
-      </c>
-      <c r="F26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>23330051920271</v>
-      </c>
-      <c r="B27" t="s">
-        <v>113</v>
-      </c>
-      <c r="C27" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" t="s">
-        <v>275</v>
-      </c>
-      <c r="E27" t="s">
-        <v>223</v>
-      </c>
-      <c r="F27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>23330051920335</v>
-      </c>
-      <c r="B28" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" t="s">
-        <v>150</v>
-      </c>
-      <c r="D28" t="s">
-        <v>269</v>
-      </c>
-      <c r="E28" t="s">
-        <v>223</v>
-      </c>
-      <c r="F28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>23330051920335</v>
-      </c>
-      <c r="B29" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" t="s">
-        <v>150</v>
-      </c>
-      <c r="D29" t="s">
-        <v>269</v>
-      </c>
-      <c r="E29" t="s">
-        <v>221</v>
-      </c>
-      <c r="F29">
         <v>5</v>
       </c>
     </row>
@@ -4117,16 +3932,16 @@
         <v>23330051920282</v>
       </c>
       <c r="B2" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="C2" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="D2" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="E2" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4137,16 +3952,16 @@
         <v>23330051920282</v>
       </c>
       <c r="B3" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="C3" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="D3" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="E3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4157,16 +3972,16 @@
         <v>23330051920284</v>
       </c>
       <c r="B4" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="C4" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="D4" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="E4" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4177,16 +3992,16 @@
         <v>23330051920285</v>
       </c>
       <c r="B5" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="C5" t="s">
         <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="E5" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4197,16 +4012,16 @@
         <v>23330051920285</v>
       </c>
       <c r="B6" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="C6" t="s">
         <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="E6" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4217,16 +4032,16 @@
         <v>23330051920299</v>
       </c>
       <c r="B7" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="E7" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4237,16 +4052,16 @@
         <v>23330051920308</v>
       </c>
       <c r="B8" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="E8" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4257,13 +4072,13 @@
         <v>23330051920308</v>
       </c>
       <c r="B9" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="E9" t="s">
         <v>35</v>
@@ -4277,16 +4092,16 @@
         <v>23330051920310</v>
       </c>
       <c r="B10" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="E10" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4297,16 +4112,16 @@
         <v>23330051920311</v>
       </c>
       <c r="B11" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C11" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D11" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="E11" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -4317,13 +4132,13 @@
         <v>23330051920311</v>
       </c>
       <c r="B12" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C12" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D12" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="E12" t="s">
         <v>35</v>
@@ -4337,16 +4152,16 @@
         <v>23330051920336</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>179</v>
       </c>
       <c r="C13" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="D13" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="E13" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -4357,13 +4172,13 @@
         <v>23330051920347</v>
       </c>
       <c r="B14" t="s">
+        <v>269</v>
+      </c>
+      <c r="C14" t="s">
+        <v>171</v>
+      </c>
+      <c r="D14" t="s">
         <v>281</v>
-      </c>
-      <c r="C14" t="s">
-        <v>174</v>
-      </c>
-      <c r="D14" t="s">
-        <v>293</v>
       </c>
       <c r="E14" t="s">
         <v>33</v>
@@ -4377,16 +4192,16 @@
         <v>23330051920347</v>
       </c>
       <c r="B15" t="s">
+        <v>269</v>
+      </c>
+      <c r="C15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D15" t="s">
         <v>281</v>
       </c>
-      <c r="C15" t="s">
-        <v>174</v>
-      </c>
-      <c r="D15" t="s">
-        <v>293</v>
-      </c>
       <c r="E15" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -4403,7 +4218,7 @@
         <v>64</v>
       </c>
       <c r="D16" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E16" t="s">
         <v>35</v>
@@ -4417,16 +4232,16 @@
         <v>23330051920356</v>
       </c>
       <c r="B17" t="s">
+        <v>270</v>
+      </c>
+      <c r="C17" t="s">
+        <v>244</v>
+      </c>
+      <c r="D17" t="s">
         <v>282</v>
       </c>
-      <c r="C17" t="s">
-        <v>252</v>
-      </c>
-      <c r="D17" t="s">
-        <v>294</v>
-      </c>
       <c r="E17" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -4437,16 +4252,16 @@
         <v>23330051920363</v>
       </c>
       <c r="B18" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>179</v>
       </c>
       <c r="D18" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="E18" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -4490,13 +4305,13 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D2" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="E2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4507,16 +4322,16 @@
         <v>23330051920300</v>
       </c>
       <c r="B3" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="C3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="E3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4530,13 +4345,13 @@
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="D4" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="E4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4550,13 +4365,13 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>179</v>
       </c>
       <c r="D5" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="E5" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4570,13 +4385,13 @@
         <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D6" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="E6" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4590,13 +4405,13 @@
         <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D7" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="E7" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4613,10 +4428,10 @@
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="E8" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4633,10 +4448,10 @@
         <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="E9" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4683,10 +4498,10 @@
         <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="E2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4700,13 +4515,13 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>306</v>
+        <v>204</v>
       </c>
       <c r="D3" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="E3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4717,16 +4532,16 @@
         <v>22330051920363</v>
       </c>
       <c r="B4" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="E4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4737,16 +4552,16 @@
         <v>22330051920378</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>179</v>
       </c>
       <c r="C5" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="D5" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="E5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4760,13 +4575,13 @@
         <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="D6" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="E6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4779,7 +4594,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4804,19 +4619,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920105</v>
+        <v>21330051420317</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>300</v>
       </c>
       <c r="C2" t="s">
-        <v>316</v>
+        <v>244</v>
       </c>
       <c r="D2" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="E2" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4824,19 +4639,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920105</v>
+        <v>21330051420317</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>300</v>
       </c>
       <c r="C3" t="s">
-        <v>316</v>
+        <v>244</v>
       </c>
       <c r="D3" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="E3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4844,19 +4659,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920233</v>
+        <v>21330051920105</v>
       </c>
       <c r="B4" t="s">
-        <v>313</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="D4" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="E4" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4864,19 +4679,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920236</v>
+        <v>21330051920105</v>
       </c>
       <c r="B5" t="s">
-        <v>314</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>303</v>
       </c>
       <c r="D5" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="E5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4884,19 +4699,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920236</v>
+        <v>22330051920233</v>
       </c>
       <c r="B6" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>304</v>
       </c>
       <c r="D6" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="E6" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4904,19 +4719,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920256</v>
+        <v>22330051920236</v>
       </c>
       <c r="B7" t="s">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="C7" t="s">
-        <v>318</v>
+        <v>179</v>
       </c>
       <c r="D7" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="E7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4924,21 +4739,41 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
+        <v>22330051920236</v>
+      </c>
+      <c r="B8" t="s">
+        <v>302</v>
+      </c>
+      <c r="C8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D8" t="s">
+        <v>308</v>
+      </c>
+      <c r="E8" t="s">
+        <v>130</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
         <v>22330051920366</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>41</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>61</v>
       </c>
-      <c r="D8" t="s">
-        <v>323</v>
-      </c>
-      <c r="E8" t="s">
-        <v>141</v>
-      </c>
-      <c r="F8">
+      <c r="D9" t="s">
+        <v>309</v>
+      </c>
+      <c r="E9" t="s">
+        <v>138</v>
+      </c>
+      <c r="F9">
         <v>5</v>
       </c>
     </row>
@@ -4980,13 +4815,13 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="D2" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="E2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5000,13 +4835,13 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="D3" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="E3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5017,16 +4852,16 @@
         <v>22330051920276</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D4" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="E4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5040,13 +4875,13 @@
         <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="D5" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="E5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5057,16 +4892,16 @@
         <v>22330051920286</v>
       </c>
       <c r="B6" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D6" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="E6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5083,10 +4918,10 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="E7" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5099,7 +4934,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5127,16 +4962,16 @@
         <v>21330051920002</v>
       </c>
       <c r="B2" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="C2" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="D2" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="E2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5144,19 +4979,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>22330051920222</v>
+        <v>22330051920213</v>
       </c>
       <c r="B3" t="s">
-        <v>331</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>333</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="E3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5164,21 +4999,61 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
+        <v>22330051920213</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>22330051920222</v>
+      </c>
+      <c r="B5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C5" t="s">
+        <v>319</v>
+      </c>
+      <c r="D5" t="s">
+        <v>322</v>
+      </c>
+      <c r="E5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
         <v>22330051920374</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B6" t="s">
         <v>46</v>
       </c>
-      <c r="C4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D4" t="s">
-        <v>336</v>
-      </c>
-      <c r="E4" t="s">
-        <v>133</v>
-      </c>
-      <c r="F4">
+      <c r="C6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" t="s">
+        <v>323</v>
+      </c>
+      <c r="E6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F6">
         <v>5</v>
       </c>
     </row>
@@ -5217,16 +5092,16 @@
         <v>22330051920291</v>
       </c>
       <c r="B2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C2" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="D2" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="E2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5240,13 +5115,13 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>179</v>
       </c>
       <c r="D3" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="E3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5259,7 +5134,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5287,16 +5162,16 @@
         <v>20330051920049</v>
       </c>
       <c r="B2" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="C2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D2" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="E2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5304,19 +5179,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920078</v>
+        <v>20330051920366</v>
       </c>
       <c r="B3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C3" t="s">
         <v>39</v>
       </c>
-      <c r="C3" t="s">
-        <v>61</v>
-      </c>
       <c r="D3" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="E3" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5327,16 +5202,16 @@
         <v>20330051920366</v>
       </c>
       <c r="B4" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="C4" t="s">
         <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="E4" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5344,19 +5219,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920366</v>
+        <v>20330051920367</v>
       </c>
       <c r="B5" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="C5" t="s">
         <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="E5" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5367,16 +5242,16 @@
         <v>20330051920367</v>
       </c>
       <c r="B6" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="C6" t="s">
         <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="E6" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5384,41 +5259,21 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920367</v>
+        <v>21330051920195</v>
       </c>
       <c r="B7" t="s">
-        <v>341</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>179</v>
       </c>
       <c r="D7" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="E7" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920012</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" t="s">
-        <v>346</v>
-      </c>
-      <c r="E8" t="s">
-        <v>347</v>
-      </c>
-      <c r="F8">
         <v>5</v>
       </c>
     </row>
@@ -5667,16 +5522,16 @@
         <v>21330051920071</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C2" t="s">
         <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="E2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5687,16 +5542,16 @@
         <v>21330051920075</v>
       </c>
       <c r="B3" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="E3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5707,16 +5562,16 @@
         <v>21330051920078</v>
       </c>
       <c r="B4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C4" t="s">
         <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="E4" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5727,16 +5582,16 @@
         <v>21330051920078</v>
       </c>
       <c r="B5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C5" t="s">
         <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="E5" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5756,7 +5611,7 @@
         <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5767,16 +5622,16 @@
         <v>21330051920109</v>
       </c>
       <c r="B7" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C7" t="s">
         <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="E7" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5793,10 +5648,10 @@
         <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="E8" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5809,7 +5664,7 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5837,18 +5692,58 @@
         <v>21330051920125</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>179</v>
       </c>
       <c r="C2" t="s">
         <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="E2" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="F2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>21330051920126</v>
+      </c>
+      <c r="B3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" t="s">
+        <v>339</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>21330051920126</v>
+      </c>
+      <c r="B4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F4">
         <v>5</v>
       </c>
     </row>
@@ -5887,16 +5782,16 @@
         <v>21330051920059</v>
       </c>
       <c r="B2" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="C2" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E2" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5937,16 +5832,16 @@
         <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="C2" t="s">
         <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="E2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5963,10 +5858,10 @@
         <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="E3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5977,16 +5872,16 @@
         <v>21330051920147</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D4" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="E4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5997,16 +5892,16 @@
         <v>21330051920147</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D5" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="E5" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6209,7 +6104,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6240,10 +6135,10 @@
         <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
         <v>33</v>
@@ -6254,41 +6149,21 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>23330051920139</v>
+        <v>23330051920315</v>
       </c>
       <c r="B3" t="s">
         <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
         <v>33</v>
       </c>
       <c r="F3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>23330051920315</v>
-      </c>
-      <c r="B4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D4" t="s">
-        <v>97</v>
-      </c>
-      <c r="E4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4">
         <v>5</v>
       </c>
     </row>
@@ -6327,13 +6202,13 @@
         <v>23330051920151</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E2" t="s">
         <v>35</v>
@@ -6353,7 +6228,7 @@
         <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E3" t="s">
         <v>33</v>
@@ -6373,7 +6248,7 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E4" t="s">
         <v>33</v>
@@ -6390,10 +6265,10 @@
         <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E5" t="s">
         <v>35</v>
@@ -6407,13 +6282,13 @@
         <v>23330051920161</v>
       </c>
       <c r="B6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E6" t="s">
         <v>33</v>
@@ -6427,16 +6302,16 @@
         <v>23330051920162</v>
       </c>
       <c r="B7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
         <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6447,16 +6322,16 @@
         <v>23330051920162</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C8" t="s">
         <v>58</v>
       </c>
       <c r="D8" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6467,13 +6342,13 @@
         <v>23330051920164</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E9" t="s">
         <v>35</v>
@@ -6487,13 +6362,13 @@
         <v>23330051920169</v>
       </c>
       <c r="B10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E10" t="s">
         <v>33</v>
@@ -6513,7 +6388,7 @@
         <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E11" t="s">
         <v>33</v>
@@ -6527,13 +6402,13 @@
         <v>23330051920175</v>
       </c>
       <c r="B12" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E12" t="s">
         <v>33</v>
@@ -6547,13 +6422,13 @@
         <v>23330051920175</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E13" t="s">
         <v>35</v>
@@ -6567,13 +6442,13 @@
         <v>23330051920176</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D14" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E14" t="s">
         <v>35</v>
@@ -6587,13 +6462,13 @@
         <v>23330051920313</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E15" t="s">
         <v>33</v>
@@ -6607,13 +6482,13 @@
         <v>23330051920313</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E16" t="s">
         <v>35</v>
@@ -6627,13 +6502,13 @@
         <v>23330051920316</v>
       </c>
       <c r="B17" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C17" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D17" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E17" t="s">
         <v>34</v>
@@ -6677,16 +6552,16 @@
         <v>20330051920059</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6697,16 +6572,16 @@
         <v>20330051920059</v>
       </c>
       <c r="B3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" t="s">
         <v>130</v>
-      </c>
-      <c r="E3" t="s">
-        <v>133</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6717,16 +6592,16 @@
         <v>22330051920010</v>
       </c>
       <c r="B4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" t="s">
         <v>129</v>
-      </c>
-      <c r="D4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E4" t="s">
-        <v>132</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6770,13 +6645,13 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2" t="s">
         <v>135</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>138</v>
-      </c>
-      <c r="E2" t="s">
-        <v>141</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6790,13 +6665,13 @@
         <v>64</v>
       </c>
       <c r="C3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" t="s">
         <v>136</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>139</v>
-      </c>
-      <c r="E3" t="s">
-        <v>142</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6810,13 +6685,13 @@
         <v>64</v>
       </c>
       <c r="C4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" t="s">
         <v>136</v>
       </c>
-      <c r="D4" t="s">
-        <v>139</v>
-      </c>
       <c r="E4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6827,16 +6702,16 @@
         <v>22330051920105</v>
       </c>
       <c r="B5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5" t="s">
         <v>134</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>137</v>
       </c>
-      <c r="D5" t="s">
-        <v>140</v>
-      </c>
       <c r="E5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6847,16 +6722,16 @@
         <v>22330051920105</v>
       </c>
       <c r="B6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" t="s">
         <v>134</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>137</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>140</v>
-      </c>
-      <c r="E6" t="s">
-        <v>143</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6903,10 +6778,10 @@
         <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6917,16 +6792,16 @@
         <v>22330051920386</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F3">
         <v>5</v>

--- a/Rescatables20231.xlsx
+++ b/Rescatables20231.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="335">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -702,352 +702,313 @@
     <t>Ciencias sociales I</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
     <t>CALVA</t>
   </si>
   <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
     <t>FUENTES</t>
   </si>
   <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>CLAUDIA RUBI</t>
+  </si>
+  <si>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>ANGEL JESUS</t>
+  </si>
+  <si>
+    <t>NURIA BELEN</t>
+  </si>
+  <si>
+    <t>VALERY MIRANDA</t>
+  </si>
+  <si>
+    <t>VIVIANA JOSELIN</t>
+  </si>
+  <si>
+    <t>MIGUEL ENRIQUE</t>
+  </si>
+  <si>
+    <t>ANGEL ABRAHAM</t>
+  </si>
+  <si>
+    <t>GISELA GUADALUPE</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>Lengua y comunicación I</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>MACUIXTLE</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>REGINA DAYTRI</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>MIRIAM</t>
+  </si>
+  <si>
+    <t>MARYSOL</t>
+  </si>
+  <si>
+    <t>ESTEFANIA</t>
+  </si>
+  <si>
+    <t>RAYMUNDO</t>
+  </si>
+  <si>
+    <t>DIANA LAURA</t>
+  </si>
+  <si>
+    <t>AIDE SCARLET</t>
+  </si>
+  <si>
+    <t>KARINA MONSERRATH</t>
+  </si>
+  <si>
+    <t>KARINA</t>
+  </si>
+  <si>
+    <t>FERNANDA YAMILET</t>
+  </si>
+  <si>
+    <t>AVILA</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>CASANOVA</t>
+  </si>
+  <si>
+    <t>GARZA</t>
+  </si>
+  <si>
+    <t>PABLO</t>
+  </si>
+  <si>
+    <t>MARIANA JANET</t>
+  </si>
+  <si>
+    <t>DANIEL DE JESUS</t>
+  </si>
+  <si>
+    <t>MICHEL LEONEL</t>
+  </si>
+  <si>
+    <t>JUSTIN GIOVANNI</t>
+  </si>
+  <si>
+    <t>JESHUA</t>
+  </si>
+  <si>
+    <t>HUGO ANTONIO</t>
+  </si>
+  <si>
+    <t>LUCIA</t>
+  </si>
+  <si>
+    <t>JENNYFER ARIANA</t>
+  </si>
+  <si>
+    <t>AARON</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>NOHEMI ANGELICA</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>SERGIO JOSUE</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>LAGUNA</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>OSMAR</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>LLANOS</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>DECTOR</t>
+  </si>
+  <si>
+    <t>MENA</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>SERGIO</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>FERNANDA MARGARITA</t>
+  </si>
+  <si>
+    <t>KEVIN ALEXIS</t>
+  </si>
+  <si>
+    <t>AILYN</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>HECTOR MISAEL</t>
+  </si>
+  <si>
+    <t>JONATAN GILBERTO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>LILIANA</t>
+  </si>
+  <si>
+    <t>EVELYN ROSALIA</t>
+  </si>
+  <si>
+    <t>KARLA YARITZY</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>ELI ANTONIO</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>CANDELARIO</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>ANGEL JESUS</t>
-  </si>
-  <si>
-    <t>INGRID ISABEL</t>
-  </si>
-  <si>
-    <t>VIVIANA JOSELIN</t>
-  </si>
-  <si>
-    <t>XIMENA ISABEL</t>
-  </si>
-  <si>
-    <t>MIGUEL ENRIQUE</t>
-  </si>
-  <si>
-    <t>DANNA PAOLA</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>ANGEL ABRAHAM</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>Inglés I</t>
-  </si>
-  <si>
-    <t>ALMANZA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>DORANTES</t>
-  </si>
-  <si>
-    <t>LAGUNA</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>MACUIXTLE</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>NATH</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
     <t>MENDEZ</t>
   </si>
   <si>
-    <t>VANESA BETHSABE</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>REGINA DAYTRI</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>MIRIAM</t>
-  </si>
-  <si>
-    <t>ALEX TADEO</t>
-  </si>
-  <si>
-    <t>AARON ZACHARY</t>
-  </si>
-  <si>
-    <t>RAYMUNDO</t>
-  </si>
-  <si>
-    <t>DIANA LAURA</t>
-  </si>
-  <si>
-    <t>AIDE SCARLET</t>
-  </si>
-  <si>
-    <t>KARINA MONSERRATH</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>FERNANDA YAMILET</t>
-  </si>
-  <si>
-    <t>AVILA</t>
-  </si>
-  <si>
-    <t>BERTELY</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>CASANOVA</t>
-  </si>
-  <si>
-    <t>GARZA</t>
-  </si>
-  <si>
-    <t>PABLO</t>
-  </si>
-  <si>
-    <t>GALINDO</t>
-  </si>
-  <si>
-    <t>MARIANA JANET</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>DANIEL DE JESUS</t>
-  </si>
-  <si>
-    <t>MICHEL LEONEL</t>
-  </si>
-  <si>
-    <t>JUSTIN GIOVANNI</t>
-  </si>
-  <si>
-    <t>JESHUA</t>
-  </si>
-  <si>
-    <t>HUGO ANTONIO</t>
-  </si>
-  <si>
-    <t>IVETTE</t>
-  </si>
-  <si>
-    <t>LUCIA</t>
-  </si>
-  <si>
-    <t>JENNYFER ARIANA</t>
-  </si>
-  <si>
-    <t>AARON</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>GIANCARLO</t>
-  </si>
-  <si>
-    <t>NOHEMI ANGELICA</t>
-  </si>
-  <si>
-    <t>ESTEBAN</t>
-  </si>
-  <si>
-    <t>SERGIO JOSUE</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
-    <t>OSMAR</t>
-  </si>
-  <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>LLANOS</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
-    <t>MENA</t>
-  </si>
-  <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>SERGIO</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>FERNANDA MARGARITA</t>
-  </si>
-  <si>
-    <t>KEVIN ALEXIS</t>
-  </si>
-  <si>
-    <t>AILYN</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>ERIK</t>
-  </si>
-  <si>
-    <t>OSCAR</t>
-  </si>
-  <si>
-    <t>ABRAHAM</t>
-  </si>
-  <si>
-    <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>LILIANA</t>
-  </si>
-  <si>
-    <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
-    <t>KARLA YARITZY</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>EFRAIN DE JESUS</t>
-  </si>
-  <si>
-    <t>GAMALIEL</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>ELI ANTONIO</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
+    <t>REYLI</t>
   </si>
   <si>
     <t>ABIGAIL</t>
@@ -1056,7 +1017,10 @@
     <t>EVELYN JOHANA</t>
   </si>
   <si>
-    <t>MIROSLAVA</t>
+    <t>YARED</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
   </si>
   <si>
     <t>MARIA JOSE</t>
@@ -2821,7 +2785,7 @@
         <v>212</v>
       </c>
       <c r="E13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -2841,7 +2805,7 @@
         <v>212</v>
       </c>
       <c r="E14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -3104,7 +3068,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3129,19 +3093,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>23330051920215</v>
+        <v>23330051920214</v>
       </c>
       <c r="B2" t="s">
         <v>218</v>
       </c>
       <c r="C2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D2" t="s">
         <v>225</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>216</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3149,16 +3113,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>23330051920216</v>
+        <v>23330051920214</v>
       </c>
       <c r="B3" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="C3" t="s">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="D3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E3" t="s">
         <v>235</v>
@@ -3169,19 +3133,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>23330051920216</v>
+        <v>23330051920215</v>
       </c>
       <c r="B4" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="C4" t="s">
-        <v>203</v>
+        <v>172</v>
       </c>
       <c r="D4" t="s">
         <v>226</v>
       </c>
       <c r="E4" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3189,16 +3153,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>23330051920226</v>
+        <v>23330051920216</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>203</v>
       </c>
       <c r="C5" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="D5" t="s">
-        <v>123</v>
+        <v>227</v>
       </c>
       <c r="E5" t="s">
         <v>216</v>
@@ -3209,16 +3173,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>23330051920227</v>
+        <v>23330051920226</v>
       </c>
       <c r="B6" t="s">
-        <v>187</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
         <v>223</v>
       </c>
       <c r="D6" t="s">
-        <v>227</v>
+        <v>123</v>
       </c>
       <c r="E6" t="s">
         <v>216</v>
@@ -3229,13 +3193,13 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>23330051920248</v>
+        <v>23330051920239</v>
       </c>
       <c r="B7" t="s">
-        <v>219</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>199</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
         <v>228</v>
@@ -3249,19 +3213,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>23330051920248</v>
+        <v>23330051920239</v>
       </c>
       <c r="B8" t="s">
-        <v>219</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>199</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
         <v>228</v>
       </c>
       <c r="E8" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3269,19 +3233,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>23330051920252</v>
+        <v>23330051920242</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>220</v>
       </c>
       <c r="C9" t="s">
-        <v>179</v>
+        <v>224</v>
       </c>
       <c r="D9" t="s">
         <v>229</v>
       </c>
       <c r="E9" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3289,13 +3253,13 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>23330051920254</v>
+        <v>23330051920248</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>221</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>199</v>
       </c>
       <c r="D10" t="s">
         <v>230</v>
@@ -3309,13 +3273,13 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>23330051920256</v>
+        <v>23330051920254</v>
       </c>
       <c r="B11" t="s">
-        <v>179</v>
+        <v>110</v>
       </c>
       <c r="C11" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
         <v>231</v>
@@ -3329,19 +3293,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>23330051920277</v>
+        <v>23330051920254</v>
       </c>
       <c r="B12" t="s">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E12" t="s">
-        <v>235</v>
+        <v>35</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3349,13 +3313,13 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>23330051920277</v>
+        <v>23330051920280</v>
       </c>
       <c r="B13" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C13" t="s">
-        <v>106</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
         <v>232</v>
@@ -3369,19 +3333,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>23330051920280</v>
+        <v>23330051920328</v>
       </c>
       <c r="B14" t="s">
-        <v>221</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>204</v>
       </c>
       <c r="D14" t="s">
         <v>233</v>
       </c>
       <c r="E14" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -3401,29 +3365,9 @@
         <v>234</v>
       </c>
       <c r="E15" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="F15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>23330051920357</v>
-      </c>
-      <c r="B16" t="s">
-        <v>179</v>
-      </c>
-      <c r="C16" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" t="s">
-        <v>234</v>
-      </c>
-      <c r="E16" t="s">
-        <v>216</v>
-      </c>
-      <c r="F16">
         <v>5</v>
       </c>
     </row>
@@ -3434,7 +3378,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3459,19 +3403,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>23330051920218</v>
+        <v>23330051920220</v>
       </c>
       <c r="B2" t="s">
         <v>236</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>240</v>
       </c>
       <c r="D2" t="s">
-        <v>251</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3479,19 +3423,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>23330051920220</v>
+        <v>23330051920228</v>
       </c>
       <c r="B3" t="s">
-        <v>237</v>
+        <v>149</v>
       </c>
       <c r="C3" t="s">
-        <v>242</v>
+        <v>188</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>245</v>
       </c>
       <c r="E3" t="s">
-        <v>235</v>
+        <v>35</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3499,16 +3443,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>23330051920220</v>
+        <v>23330051920229</v>
       </c>
       <c r="B4" t="s">
-        <v>237</v>
+        <v>149</v>
       </c>
       <c r="C4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>246</v>
       </c>
       <c r="E4" t="s">
         <v>216</v>
@@ -3519,19 +3463,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>23330051920224</v>
+        <v>23330051920233</v>
       </c>
       <c r="B5" t="s">
-        <v>238</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D5" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E5" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3539,19 +3483,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>23330051920228</v>
+        <v>23330051920241</v>
       </c>
       <c r="B6" t="s">
-        <v>149</v>
+        <v>237</v>
       </c>
       <c r="C6" t="s">
-        <v>188</v>
+        <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E6" t="s">
-        <v>235</v>
+        <v>35</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3559,19 +3503,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>23330051920228</v>
+        <v>23330051920241</v>
       </c>
       <c r="B7" t="s">
-        <v>149</v>
+        <v>237</v>
       </c>
       <c r="C7" t="s">
-        <v>188</v>
+        <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>216</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3579,16 +3523,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>23330051920229</v>
+        <v>23330051920245</v>
       </c>
       <c r="B8" t="s">
-        <v>149</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>244</v>
+        <v>197</v>
       </c>
       <c r="D8" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E8" t="s">
         <v>216</v>
@@ -3599,19 +3543,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>23330051920233</v>
+        <v>23330051920245</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>245</v>
+        <v>197</v>
       </c>
       <c r="D9" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E9" t="s">
-        <v>235</v>
+        <v>35</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3619,19 +3563,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>23330051920233</v>
+        <v>23330051920247</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D10" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E10" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3639,19 +3583,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>23330051920234</v>
+        <v>23330051920249</v>
       </c>
       <c r="B11" t="s">
-        <v>151</v>
+        <v>238</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E11" t="s">
-        <v>235</v>
+        <v>35</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3659,19 +3603,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>23330051920236</v>
+        <v>23330051920258</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>252</v>
       </c>
       <c r="E12" t="s">
-        <v>235</v>
+        <v>35</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3679,19 +3623,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>23330051920243</v>
+        <v>23330051920264</v>
       </c>
       <c r="B13" t="s">
         <v>239</v>
       </c>
       <c r="C13" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D13" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="E13" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -3699,16 +3643,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>23330051920247</v>
+        <v>23330051920267</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="C14" t="s">
-        <v>244</v>
+        <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E14" t="s">
         <v>35</v>
@@ -3719,19 +3663,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>23330051920247</v>
+        <v>23330051920267</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="C15" t="s">
-        <v>244</v>
+        <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E15" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -3739,161 +3683,21 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>23330051920249</v>
+        <v>23330051920271</v>
       </c>
       <c r="B16" t="s">
-        <v>240</v>
+        <v>110</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E16" t="s">
-        <v>35</v>
+        <v>216</v>
       </c>
       <c r="F16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>23330051920258</v>
-      </c>
-      <c r="B17" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" t="s">
-        <v>248</v>
-      </c>
-      <c r="D17" t="s">
-        <v>260</v>
-      </c>
-      <c r="E17" t="s">
-        <v>35</v>
-      </c>
-      <c r="F17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>23330051920264</v>
-      </c>
-      <c r="B18" t="s">
-        <v>241</v>
-      </c>
-      <c r="C18" t="s">
-        <v>249</v>
-      </c>
-      <c r="D18" t="s">
-        <v>261</v>
-      </c>
-      <c r="E18" t="s">
-        <v>235</v>
-      </c>
-      <c r="F18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>23330051920264</v>
-      </c>
-      <c r="B19" t="s">
-        <v>241</v>
-      </c>
-      <c r="C19" t="s">
-        <v>249</v>
-      </c>
-      <c r="D19" t="s">
-        <v>261</v>
-      </c>
-      <c r="E19" t="s">
-        <v>216</v>
-      </c>
-      <c r="F19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>23330051920265</v>
-      </c>
-      <c r="B20" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" t="s">
-        <v>250</v>
-      </c>
-      <c r="D20" t="s">
-        <v>262</v>
-      </c>
-      <c r="E20" t="s">
-        <v>235</v>
-      </c>
-      <c r="F20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>23330051920271</v>
-      </c>
-      <c r="B21" t="s">
-        <v>110</v>
-      </c>
-      <c r="C21" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" t="s">
-        <v>263</v>
-      </c>
-      <c r="E21" t="s">
-        <v>216</v>
-      </c>
-      <c r="F21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>23330051920271</v>
-      </c>
-      <c r="B22" t="s">
-        <v>110</v>
-      </c>
-      <c r="C22" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" t="s">
-        <v>263</v>
-      </c>
-      <c r="E22" t="s">
-        <v>235</v>
-      </c>
-      <c r="F22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>23330051920335</v>
-      </c>
-      <c r="B23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" t="s">
-        <v>147</v>
-      </c>
-      <c r="D23" t="s">
-        <v>259</v>
-      </c>
-      <c r="E23" t="s">
-        <v>235</v>
-      </c>
-      <c r="F23">
         <v>5</v>
       </c>
     </row>
@@ -3904,7 +3708,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3932,16 +3736,16 @@
         <v>23330051920282</v>
       </c>
       <c r="B2" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="C2" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="D2" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="E2" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3949,16 +3753,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>23330051920282</v>
+        <v>23330051920285</v>
       </c>
       <c r="B3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" t="s">
         <v>264</v>
-      </c>
-      <c r="C3" t="s">
-        <v>271</v>
-      </c>
-      <c r="D3" t="s">
-        <v>273</v>
       </c>
       <c r="E3" t="s">
         <v>217</v>
@@ -3969,19 +3773,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>23330051920284</v>
+        <v>23330051920299</v>
       </c>
       <c r="B4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
         <v>265</v>
       </c>
-      <c r="C4" t="s">
-        <v>272</v>
-      </c>
-      <c r="D4" t="s">
-        <v>274</v>
-      </c>
       <c r="E4" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3989,19 +3793,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>23330051920285</v>
+        <v>23330051920308</v>
       </c>
       <c r="B5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
         <v>266</v>
       </c>
-      <c r="C5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" t="s">
-        <v>275</v>
-      </c>
       <c r="E5" t="s">
-        <v>217</v>
+        <v>35</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4009,19 +3813,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>23330051920285</v>
+        <v>23330051920310</v>
       </c>
       <c r="B6" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="E6" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4029,19 +3833,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>23330051920299</v>
+        <v>23330051920311</v>
       </c>
       <c r="B7" t="s">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="D7" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="E7" t="s">
-        <v>217</v>
+        <v>35</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4049,19 +3853,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>23330051920308</v>
+        <v>23330051920347</v>
       </c>
       <c r="B8" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>171</v>
       </c>
       <c r="D8" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="E8" t="s">
-        <v>235</v>
+        <v>33</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4069,19 +3873,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>23330051920308</v>
+        <v>23330051920347</v>
       </c>
       <c r="B9" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>171</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>216</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4089,19 +3893,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>23330051920310</v>
+        <v>23330051920348</v>
       </c>
       <c r="B10" t="s">
-        <v>268</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>278</v>
+        <v>128</v>
       </c>
       <c r="E10" t="s">
-        <v>217</v>
+        <v>35</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4109,19 +3913,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>23330051920311</v>
+        <v>23330051920356</v>
       </c>
       <c r="B11" t="s">
-        <v>172</v>
+        <v>261</v>
       </c>
       <c r="C11" t="s">
-        <v>149</v>
+        <v>241</v>
       </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="E11" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -4129,141 +3933,21 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>23330051920311</v>
+        <v>23330051920363</v>
       </c>
       <c r="B12" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="C12" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="D12" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="F12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>23330051920336</v>
-      </c>
-      <c r="B13" t="s">
-        <v>179</v>
-      </c>
-      <c r="C13" t="s">
-        <v>248</v>
-      </c>
-      <c r="D13" t="s">
-        <v>280</v>
-      </c>
-      <c r="E13" t="s">
-        <v>235</v>
-      </c>
-      <c r="F13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>23330051920347</v>
-      </c>
-      <c r="B14" t="s">
-        <v>269</v>
-      </c>
-      <c r="C14" t="s">
-        <v>171</v>
-      </c>
-      <c r="D14" t="s">
-        <v>281</v>
-      </c>
-      <c r="E14" t="s">
-        <v>33</v>
-      </c>
-      <c r="F14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>23330051920347</v>
-      </c>
-      <c r="B15" t="s">
-        <v>269</v>
-      </c>
-      <c r="C15" t="s">
-        <v>171</v>
-      </c>
-      <c r="D15" t="s">
-        <v>281</v>
-      </c>
-      <c r="E15" t="s">
-        <v>216</v>
-      </c>
-      <c r="F15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>23330051920348</v>
-      </c>
-      <c r="B16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" t="s">
-        <v>128</v>
-      </c>
-      <c r="E16" t="s">
-        <v>35</v>
-      </c>
-      <c r="F16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>23330051920356</v>
-      </c>
-      <c r="B17" t="s">
-        <v>270</v>
-      </c>
-      <c r="C17" t="s">
-        <v>244</v>
-      </c>
-      <c r="D17" t="s">
-        <v>282</v>
-      </c>
-      <c r="E17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>23330051920363</v>
-      </c>
-      <c r="B18" t="s">
-        <v>148</v>
-      </c>
-      <c r="C18" t="s">
-        <v>179</v>
-      </c>
-      <c r="D18" t="s">
-        <v>283</v>
-      </c>
-      <c r="E18" t="s">
-        <v>217</v>
-      </c>
-      <c r="F18">
         <v>5</v>
       </c>
     </row>
@@ -4274,7 +3958,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4305,10 +3989,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D2" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="E2" t="s">
         <v>216</v>
@@ -4319,19 +4003,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>23330051920300</v>
+        <v>23330051920303</v>
       </c>
       <c r="B3" t="s">
-        <v>284</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>272</v>
       </c>
       <c r="D3" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="E3" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4339,19 +4023,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>23330051920303</v>
+        <v>23330051920319</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>147</v>
       </c>
       <c r="C4" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="D4" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="E4" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4359,19 +4043,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>23330051920305</v>
+        <v>23330051920319</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>147</v>
       </c>
       <c r="C5" t="s">
-        <v>179</v>
+        <v>273</v>
       </c>
       <c r="D5" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="E5" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4385,10 +4069,10 @@
         <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="D6" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="E6" t="s">
         <v>217</v>
@@ -4399,61 +4083,21 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>23330051920332</v>
+        <v>23330051920342</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>286</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="E7" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="F7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>23330051920342</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" t="s">
-        <v>292</v>
-      </c>
-      <c r="E8" t="s">
-        <v>235</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>23330051920342</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" t="s">
-        <v>292</v>
-      </c>
-      <c r="E9" t="s">
-        <v>216</v>
-      </c>
-      <c r="F9">
         <v>5</v>
       </c>
     </row>
@@ -4498,7 +4142,7 @@
         <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="E2" t="s">
         <v>130</v>
@@ -4518,7 +4162,7 @@
         <v>204</v>
       </c>
       <c r="D3" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="E3" t="s">
         <v>130</v>
@@ -4532,13 +4176,13 @@
         <v>22330051920363</v>
       </c>
       <c r="B4" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="E4" t="s">
         <v>130</v>
@@ -4555,10 +4199,10 @@
         <v>179</v>
       </c>
       <c r="C5" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="D5" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="E5" t="s">
         <v>130</v>
@@ -4575,10 +4219,10 @@
         <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>239</v>
+        <v>282</v>
       </c>
       <c r="D6" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="E6" t="s">
         <v>130</v>
@@ -4622,13 +4266,13 @@
         <v>21330051420317</v>
       </c>
       <c r="B2" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="C2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D2" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="E2" t="s">
         <v>138</v>
@@ -4642,13 +4286,13 @@
         <v>21330051420317</v>
       </c>
       <c r="B3" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="C3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D3" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="E3" t="s">
         <v>139</v>
@@ -4665,10 +4309,10 @@
         <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="D4" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="E4" t="s">
         <v>168</v>
@@ -4685,10 +4329,10 @@
         <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="D5" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="E5" t="s">
         <v>140</v>
@@ -4702,13 +4346,13 @@
         <v>22330051920233</v>
       </c>
       <c r="B6" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="C6" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="D6" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="E6" t="s">
         <v>139</v>
@@ -4722,13 +4366,13 @@
         <v>22330051920236</v>
       </c>
       <c r="B7" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="C7" t="s">
         <v>179</v>
       </c>
       <c r="D7" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="E7" t="s">
         <v>138</v>
@@ -4742,13 +4386,13 @@
         <v>22330051920236</v>
       </c>
       <c r="B8" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="C8" t="s">
         <v>179</v>
       </c>
       <c r="D8" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="E8" t="s">
         <v>130</v>
@@ -4768,7 +4412,7 @@
         <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="E9" t="s">
         <v>138</v>
@@ -4784,7 +4428,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4815,13 +4459,13 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="D2" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="E2" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4829,19 +4473,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920396</v>
+        <v>22330051920279</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="D3" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="E3" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4849,19 +4493,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920276</v>
+        <v>22330051920279</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>220</v>
+        <v>299</v>
       </c>
       <c r="D4" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="E4" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4869,61 +4513,21 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920277</v>
+        <v>22330051920405</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>311</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="E5" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="F5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920286</v>
-      </c>
-      <c r="B6" t="s">
-        <v>220</v>
-      </c>
-      <c r="C6" t="s">
-        <v>144</v>
-      </c>
-      <c r="D6" t="s">
-        <v>315</v>
-      </c>
-      <c r="E6" t="s">
-        <v>139</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920405</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" t="s">
-        <v>316</v>
-      </c>
-      <c r="E7" t="s">
-        <v>130</v>
-      </c>
-      <c r="F7">
         <v>5</v>
       </c>
     </row>
@@ -4962,13 +4566,13 @@
         <v>21330051920002</v>
       </c>
       <c r="B2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D2" t="s">
         <v>306</v>
-      </c>
-      <c r="C2" t="s">
-        <v>318</v>
-      </c>
-      <c r="D2" t="s">
-        <v>320</v>
       </c>
       <c r="E2" t="s">
         <v>130</v>
@@ -4988,7 +4592,7 @@
         <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="E3" t="s">
         <v>138</v>
@@ -5008,7 +4612,7 @@
         <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="E4" t="s">
         <v>130</v>
@@ -5022,13 +4626,13 @@
         <v>22330051920222</v>
       </c>
       <c r="B5" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="C5" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="D5" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="E5" t="s">
         <v>138</v>
@@ -5048,7 +4652,7 @@
         <v>146</v>
       </c>
       <c r="D6" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="E6" t="s">
         <v>130</v>
@@ -5064,7 +4668,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5084,46 +4688,6 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920291</v>
-      </c>
-      <c r="B2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C2" t="s">
-        <v>324</v>
-      </c>
-      <c r="D2" t="s">
-        <v>325</v>
-      </c>
-      <c r="E2" t="s">
-        <v>139</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920305</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D3" t="s">
-        <v>326</v>
-      </c>
-      <c r="E3" t="s">
-        <v>139</v>
-      </c>
-      <c r="F3">
         <v>5</v>
       </c>
     </row>
@@ -5162,13 +4726,13 @@
         <v>20330051920049</v>
       </c>
       <c r="B2" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="C2" t="s">
         <v>126</v>
       </c>
       <c r="D2" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="E2" t="s">
         <v>177</v>
@@ -5182,13 +4746,13 @@
         <v>20330051920366</v>
       </c>
       <c r="B3" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="C3" t="s">
         <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="E3" t="s">
         <v>177</v>
@@ -5202,13 +4766,13 @@
         <v>20330051920366</v>
       </c>
       <c r="B4" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="C4" t="s">
         <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="E4" t="s">
         <v>195</v>
@@ -5222,13 +4786,13 @@
         <v>20330051920367</v>
       </c>
       <c r="B5" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="C5" t="s">
         <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="E5" t="s">
         <v>195</v>
@@ -5242,13 +4806,13 @@
         <v>20330051920367</v>
       </c>
       <c r="B6" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="C6" t="s">
         <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="E6" t="s">
         <v>177</v>
@@ -5268,7 +4832,7 @@
         <v>179</v>
       </c>
       <c r="D7" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="E7" t="s">
         <v>177</v>
@@ -5361,7 +4925,7 @@
         <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5381,7 +4945,7 @@
         <v>68</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5494,7 +5058,7 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5519,19 +5083,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920071</v>
+        <v>20330051920378</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>319</v>
       </c>
       <c r="D2" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="E2" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5539,16 +5103,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920075</v>
+        <v>21330051920071</v>
       </c>
       <c r="B3" t="s">
-        <v>333</v>
+        <v>147</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="E3" t="s">
         <v>193</v>
@@ -5559,16 +5123,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920078</v>
+        <v>21330051920075</v>
       </c>
       <c r="B4" t="s">
-        <v>149</v>
+        <v>316</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="E4" t="s">
         <v>193</v>
@@ -5579,19 +5143,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920078</v>
+        <v>21330051920076</v>
       </c>
       <c r="B5" t="s">
-        <v>149</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="E5" t="s">
-        <v>339</v>
+        <v>177</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5619,19 +5183,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920109</v>
+        <v>21330051920103</v>
       </c>
       <c r="B7" t="s">
-        <v>220</v>
+        <v>317</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>179</v>
       </c>
       <c r="D7" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="E7" t="s">
-        <v>339</v>
+        <v>177</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5639,21 +5203,81 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
+        <v>21330051920109</v>
+      </c>
+      <c r="B8" t="s">
+        <v>318</v>
+      </c>
+      <c r="C8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E8" t="s">
+        <v>177</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>21330051920109</v>
+      </c>
+      <c r="B9" t="s">
+        <v>318</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="s">
+        <v>325</v>
+      </c>
+      <c r="E9" t="s">
+        <v>327</v>
+      </c>
+      <c r="F9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
         <v>21330051920260</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B10" t="s">
         <v>20</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C10" t="s">
         <v>36</v>
       </c>
-      <c r="D8" t="s">
-        <v>338</v>
-      </c>
-      <c r="E8" t="s">
-        <v>339</v>
-      </c>
-      <c r="F8">
+      <c r="D10" t="s">
+        <v>326</v>
+      </c>
+      <c r="E10" t="s">
+        <v>177</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>21330051920260</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>326</v>
+      </c>
+      <c r="E11" t="s">
+        <v>327</v>
+      </c>
+      <c r="F11">
         <v>5</v>
       </c>
     </row>
@@ -5698,10 +5322,10 @@
         <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="E2" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5721,7 +5345,7 @@
         <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5782,16 +5406,16 @@
         <v>21330051920059</v>
       </c>
       <c r="B2" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="C2" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="D2" t="s">
         <v>152</v>
       </c>
       <c r="E2" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5832,13 +5456,13 @@
         <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
-        <v>324</v>
+        <v>218</v>
       </c>
       <c r="C2" t="s">
         <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="E2" t="s">
         <v>177</v>
@@ -5858,7 +5482,7 @@
         <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="E3" t="s">
         <v>193</v>
@@ -5878,7 +5502,7 @@
         <v>106</v>
       </c>
       <c r="D4" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="E4" t="s">
         <v>176</v>
@@ -5898,7 +5522,7 @@
         <v>106</v>
       </c>
       <c r="D5" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="E5" t="s">
         <v>193</v>

--- a/Rescatables20231.xlsx
+++ b/Rescatables20231.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="360">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -702,28 +702,70 @@
     <t>Ciencias sociales I</t>
   </si>
   <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
+    <t>CALVA</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>FUENTES</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>FERRER</t>
+  </si>
+  <si>
+    <t>SOSA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>CANDELARIO</t>
+  </si>
+  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
-    <t>CALVA</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>FUENTES</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>CLAUDIA RUBI</t>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>MONTERROSAS</t>
+  </si>
+  <si>
+    <t>DORIAN</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
   </si>
   <si>
     <t>LORENA</t>
@@ -732,16 +774,49 @@
     <t>ANGEL JESUS</t>
   </si>
   <si>
-    <t>NURIA BELEN</t>
+    <t>INGRID ISABEL</t>
+  </si>
+  <si>
+    <t>VANESA</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
   </si>
   <si>
     <t>VALERY MIRANDA</t>
   </si>
   <si>
+    <t>LUZ YESENIA</t>
+  </si>
+  <si>
     <t>VIVIANA JOSELIN</t>
   </si>
   <si>
-    <t>MIGUEL ENRIQUE</t>
+    <t>ANDREA</t>
+  </si>
+  <si>
+    <t>XIMENA ISABEL</t>
+  </si>
+  <si>
+    <t>DANNA PAOLA</t>
+  </si>
+  <si>
+    <t>BRISEIDA</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>SAMANTHA BETHANY</t>
+  </si>
+  <si>
+    <t>ANEL</t>
+  </si>
+  <si>
+    <t>VICTORIA VIANNEY</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
   </si>
   <si>
     <t>ANGEL ABRAHAM</t>
@@ -750,10 +825,16 @@
     <t>GISELA GUADALUPE</t>
   </si>
   <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>SILVANA</t>
+  </si>
+  <si>
     <t>VANESSA</t>
   </si>
   <si>
-    <t>Lengua y comunicación I</t>
+    <t>Recursos socioemocionales I</t>
   </si>
   <si>
     <t>BARRAGAN</t>
@@ -879,9 +960,6 @@
     <t>NOHEMI ANGELICA</t>
   </si>
   <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
     <t>SERGIO JOSUE</t>
   </si>
   <si>
@@ -1000,9 +1078,6 @@
   </si>
   <si>
     <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
   </si>
   <si>
     <t>MENDEZ</t>
@@ -3068,7 +3143,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3093,19 +3168,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>23330051920214</v>
+        <v>23330051920207</v>
       </c>
       <c r="B2" t="s">
-        <v>218</v>
+        <v>188</v>
       </c>
       <c r="C2" t="s">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="D2" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="E2" t="s">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3113,19 +3188,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>23330051920214</v>
+        <v>23330051920213</v>
       </c>
       <c r="B3" t="s">
         <v>218</v>
       </c>
       <c r="C3" t="s">
-        <v>178</v>
+        <v>228</v>
       </c>
       <c r="D3" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="E3" t="s">
-        <v>235</v>
+        <v>262</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3142,10 +3217,10 @@
         <v>172</v>
       </c>
       <c r="D4" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>262</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3153,19 +3228,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>23330051920216</v>
+        <v>23330051920215</v>
       </c>
       <c r="B5" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="C5" t="s">
-        <v>203</v>
+        <v>172</v>
       </c>
       <c r="D5" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="E5" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3173,16 +3248,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>23330051920226</v>
+        <v>23330051920216</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>203</v>
       </c>
       <c r="C6" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="D6" t="s">
-        <v>123</v>
+        <v>241</v>
       </c>
       <c r="E6" t="s">
         <v>216</v>
@@ -3193,19 +3268,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>23330051920239</v>
+        <v>23330051920226</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>229</v>
       </c>
       <c r="D7" t="s">
-        <v>228</v>
+        <v>123</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>216</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3213,19 +3288,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>23330051920239</v>
+        <v>23330051920226</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>229</v>
       </c>
       <c r="D8" t="s">
-        <v>228</v>
+        <v>123</v>
       </c>
       <c r="E8" t="s">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3233,19 +3308,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>23330051920242</v>
+        <v>23330051920227</v>
       </c>
       <c r="B9" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="C9" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="D9" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="E9" t="s">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3253,19 +3328,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>23330051920248</v>
+        <v>23330051920237</v>
       </c>
       <c r="B10" t="s">
-        <v>221</v>
+        <v>124</v>
       </c>
       <c r="C10" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="D10" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>262</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3273,19 +3348,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>23330051920254</v>
+        <v>23330051920240</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>232</v>
       </c>
       <c r="D11" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="E11" t="s">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3293,19 +3368,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>23330051920254</v>
+        <v>23330051920242</v>
       </c>
       <c r="B12" t="s">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>233</v>
       </c>
       <c r="D12" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>262</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3313,16 +3388,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>23330051920280</v>
+        <v>23330051920242</v>
       </c>
       <c r="B13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>233</v>
       </c>
       <c r="D13" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="E13" t="s">
         <v>216</v>
@@ -3333,19 +3408,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>23330051920328</v>
+        <v>23330051920244</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>221</v>
       </c>
       <c r="C14" t="s">
-        <v>204</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="E14" t="s">
-        <v>35</v>
+        <v>262</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -3353,21 +3428,401 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
+        <v>23330051920248</v>
+      </c>
+      <c r="B15" t="s">
+        <v>222</v>
+      </c>
+      <c r="C15" t="s">
+        <v>199</v>
+      </c>
+      <c r="D15" t="s">
+        <v>247</v>
+      </c>
+      <c r="E15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>23330051920248</v>
+      </c>
+      <c r="B16" t="s">
+        <v>222</v>
+      </c>
+      <c r="C16" t="s">
+        <v>199</v>
+      </c>
+      <c r="D16" t="s">
+        <v>247</v>
+      </c>
+      <c r="E16" t="s">
+        <v>262</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>23330051920250</v>
+      </c>
+      <c r="B17" t="s">
+        <v>149</v>
+      </c>
+      <c r="C17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" t="s">
+        <v>248</v>
+      </c>
+      <c r="E17" t="s">
+        <v>262</v>
+      </c>
+      <c r="F17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>23330051920252</v>
+      </c>
+      <c r="B18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" t="s">
+        <v>179</v>
+      </c>
+      <c r="D18" t="s">
+        <v>249</v>
+      </c>
+      <c r="E18" t="s">
+        <v>262</v>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>23330051920256</v>
+      </c>
+      <c r="B19" t="s">
+        <v>179</v>
+      </c>
+      <c r="C19" t="s">
+        <v>234</v>
+      </c>
+      <c r="D19" t="s">
+        <v>250</v>
+      </c>
+      <c r="E19" t="s">
+        <v>262</v>
+      </c>
+      <c r="F19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>23330051920257</v>
+      </c>
+      <c r="B20" t="s">
+        <v>223</v>
+      </c>
+      <c r="C20" t="s">
+        <v>235</v>
+      </c>
+      <c r="D20" t="s">
+        <v>251</v>
+      </c>
+      <c r="E20" t="s">
+        <v>262</v>
+      </c>
+      <c r="F20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>23330051920260</v>
+      </c>
+      <c r="B21" t="s">
+        <v>224</v>
+      </c>
+      <c r="C21" t="s">
+        <v>236</v>
+      </c>
+      <c r="D21" t="s">
+        <v>252</v>
+      </c>
+      <c r="E21" t="s">
+        <v>262</v>
+      </c>
+      <c r="F21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>23330051920270</v>
+      </c>
+      <c r="B22" t="s">
+        <v>225</v>
+      </c>
+      <c r="C22" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" t="s">
+        <v>85</v>
+      </c>
+      <c r="E22" t="s">
+        <v>262</v>
+      </c>
+      <c r="F22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>23330051920272</v>
+      </c>
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" t="s">
+        <v>253</v>
+      </c>
+      <c r="E23" t="s">
+        <v>262</v>
+      </c>
+      <c r="F23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>23330051920275</v>
+      </c>
+      <c r="B24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" t="s">
+        <v>237</v>
+      </c>
+      <c r="D24" t="s">
+        <v>254</v>
+      </c>
+      <c r="E24" t="s">
+        <v>262</v>
+      </c>
+      <c r="F24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>23330051920276</v>
+      </c>
+      <c r="B25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" t="s">
+        <v>255</v>
+      </c>
+      <c r="E25" t="s">
+        <v>262</v>
+      </c>
+      <c r="F25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>23330051920277</v>
+      </c>
+      <c r="B26" t="s">
+        <v>226</v>
+      </c>
+      <c r="C26" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" t="s">
+        <v>256</v>
+      </c>
+      <c r="E26" t="s">
+        <v>262</v>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27">
+        <v>23330051920280</v>
+      </c>
+      <c r="B27" t="s">
+        <v>227</v>
+      </c>
+      <c r="C27" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" t="s">
+        <v>257</v>
+      </c>
+      <c r="E27" t="s">
+        <v>216</v>
+      </c>
+      <c r="F27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>23330051920280</v>
+      </c>
+      <c r="B28" t="s">
+        <v>227</v>
+      </c>
+      <c r="C28" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" t="s">
+        <v>257</v>
+      </c>
+      <c r="E28" t="s">
+        <v>262</v>
+      </c>
+      <c r="F28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>23330051920328</v>
+      </c>
+      <c r="B29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" t="s">
+        <v>204</v>
+      </c>
+      <c r="D29" t="s">
+        <v>258</v>
+      </c>
+      <c r="E29" t="s">
+        <v>262</v>
+      </c>
+      <c r="F29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>23330051920328</v>
+      </c>
+      <c r="B30" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" t="s">
+        <v>204</v>
+      </c>
+      <c r="D30" t="s">
+        <v>258</v>
+      </c>
+      <c r="E30" t="s">
+        <v>35</v>
+      </c>
+      <c r="F30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>23330051920330</v>
+      </c>
+      <c r="B31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" t="s">
+        <v>259</v>
+      </c>
+      <c r="E31" t="s">
+        <v>262</v>
+      </c>
+      <c r="F31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>23330051920333</v>
+      </c>
+      <c r="B32" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" t="s">
+        <v>179</v>
+      </c>
+      <c r="D32" t="s">
+        <v>260</v>
+      </c>
+      <c r="E32" t="s">
+        <v>262</v>
+      </c>
+      <c r="F32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33">
         <v>23330051920357</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B33" t="s">
         <v>179</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C33" t="s">
         <v>39</v>
       </c>
-      <c r="D15" t="s">
-        <v>234</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="D33" t="s">
+        <v>261</v>
+      </c>
+      <c r="E33" t="s">
+        <v>262</v>
+      </c>
+      <c r="F33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34">
+        <v>23330051920357</v>
+      </c>
+      <c r="B34" t="s">
+        <v>179</v>
+      </c>
+      <c r="C34" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" t="s">
+        <v>261</v>
+      </c>
+      <c r="E34" t="s">
         <v>216</v>
       </c>
-      <c r="F15">
+      <c r="F34">
         <v>5</v>
       </c>
     </row>
@@ -3406,10 +3861,10 @@
         <v>23330051920220</v>
       </c>
       <c r="B2" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="C2" t="s">
-        <v>240</v>
+        <v>267</v>
       </c>
       <c r="D2" t="s">
         <v>85</v>
@@ -3432,7 +3887,7 @@
         <v>188</v>
       </c>
       <c r="D3" t="s">
-        <v>245</v>
+        <v>272</v>
       </c>
       <c r="E3" t="s">
         <v>35</v>
@@ -3449,10 +3904,10 @@
         <v>149</v>
       </c>
       <c r="C4" t="s">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="D4" t="s">
-        <v>246</v>
+        <v>273</v>
       </c>
       <c r="E4" t="s">
         <v>216</v>
@@ -3469,10 +3924,10 @@
         <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>242</v>
+        <v>269</v>
       </c>
       <c r="D5" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="E5" t="s">
         <v>216</v>
@@ -3486,13 +3941,13 @@
         <v>23330051920241</v>
       </c>
       <c r="B6" t="s">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="E6" t="s">
         <v>35</v>
@@ -3506,13 +3961,13 @@
         <v>23330051920241</v>
       </c>
       <c r="B7" t="s">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="E7" t="s">
         <v>216</v>
@@ -3532,7 +3987,7 @@
         <v>197</v>
       </c>
       <c r="D8" t="s">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="E8" t="s">
         <v>216</v>
@@ -3552,7 +4007,7 @@
         <v>197</v>
       </c>
       <c r="D9" t="s">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="E9" t="s">
         <v>35</v>
@@ -3569,10 +4024,10 @@
         <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="D10" t="s">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="E10" t="s">
         <v>35</v>
@@ -3586,13 +4041,13 @@
         <v>23330051920249</v>
       </c>
       <c r="B11" t="s">
-        <v>238</v>
+        <v>265</v>
       </c>
       <c r="C11" t="s">
         <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="E11" t="s">
         <v>35</v>
@@ -3609,10 +4064,10 @@
         <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>243</v>
+        <v>270</v>
       </c>
       <c r="D12" t="s">
-        <v>252</v>
+        <v>279</v>
       </c>
       <c r="E12" t="s">
         <v>35</v>
@@ -3626,13 +4081,13 @@
         <v>23330051920264</v>
       </c>
       <c r="B13" t="s">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="C13" t="s">
-        <v>244</v>
+        <v>271</v>
       </c>
       <c r="D13" t="s">
-        <v>253</v>
+        <v>280</v>
       </c>
       <c r="E13" t="s">
         <v>216</v>
@@ -3652,7 +4107,7 @@
         <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>254</v>
+        <v>281</v>
       </c>
       <c r="E14" t="s">
         <v>35</v>
@@ -3672,7 +4127,7 @@
         <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>254</v>
+        <v>281</v>
       </c>
       <c r="E15" t="s">
         <v>216</v>
@@ -3692,7 +4147,7 @@
         <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>255</v>
+        <v>282</v>
       </c>
       <c r="E16" t="s">
         <v>216</v>
@@ -3736,13 +4191,13 @@
         <v>23330051920282</v>
       </c>
       <c r="B2" t="s">
-        <v>256</v>
+        <v>283</v>
       </c>
       <c r="C2" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="D2" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="E2" t="s">
         <v>217</v>
@@ -3756,13 +4211,13 @@
         <v>23330051920285</v>
       </c>
       <c r="B3" t="s">
-        <v>257</v>
+        <v>284</v>
       </c>
       <c r="C3" t="s">
         <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="E3" t="s">
         <v>217</v>
@@ -3782,7 +4237,7 @@
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="E4" t="s">
         <v>217</v>
@@ -3796,13 +4251,13 @@
         <v>23330051920308</v>
       </c>
       <c r="B5" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="E5" t="s">
         <v>35</v>
@@ -3816,13 +4271,13 @@
         <v>23330051920310</v>
       </c>
       <c r="B6" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="C6" t="s">
         <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="E6" t="s">
         <v>217</v>
@@ -3842,7 +4297,7 @@
         <v>149</v>
       </c>
       <c r="D7" t="s">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="E7" t="s">
         <v>35</v>
@@ -3856,13 +4311,13 @@
         <v>23330051920347</v>
       </c>
       <c r="B8" t="s">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="C8" t="s">
         <v>171</v>
       </c>
       <c r="D8" t="s">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="E8" t="s">
         <v>33</v>
@@ -3876,13 +4331,13 @@
         <v>23330051920347</v>
       </c>
       <c r="B9" t="s">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="C9" t="s">
         <v>171</v>
       </c>
       <c r="D9" t="s">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="E9" t="s">
         <v>216</v>
@@ -3916,13 +4371,13 @@
         <v>23330051920356</v>
       </c>
       <c r="B11" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="C11" t="s">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="D11" t="s">
-        <v>270</v>
+        <v>297</v>
       </c>
       <c r="E11" t="s">
         <v>216</v>
@@ -3942,7 +4397,7 @@
         <v>179</v>
       </c>
       <c r="D12" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="E12" t="s">
         <v>217</v>
@@ -3989,10 +4444,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="D2" t="s">
-        <v>275</v>
+        <v>302</v>
       </c>
       <c r="E2" t="s">
         <v>216</v>
@@ -4009,10 +4464,10 @@
         <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="D3" t="s">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="E3" t="s">
         <v>216</v>
@@ -4029,10 +4484,10 @@
         <v>147</v>
       </c>
       <c r="C4" t="s">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="D4" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="E4" t="s">
         <v>35</v>
@@ -4049,10 +4504,10 @@
         <v>147</v>
       </c>
       <c r="C5" t="s">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="D5" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="E5" t="s">
         <v>216</v>
@@ -4069,10 +4524,10 @@
         <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="D6" t="s">
-        <v>278</v>
+        <v>304</v>
       </c>
       <c r="E6" t="s">
         <v>217</v>
@@ -4092,7 +4547,7 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>279</v>
+        <v>305</v>
       </c>
       <c r="E7" t="s">
         <v>216</v>
@@ -4142,7 +4597,7 @@
         <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>283</v>
+        <v>309</v>
       </c>
       <c r="E2" t="s">
         <v>130</v>
@@ -4162,7 +4617,7 @@
         <v>204</v>
       </c>
       <c r="D3" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="E3" t="s">
         <v>130</v>
@@ -4176,13 +4631,13 @@
         <v>22330051920363</v>
       </c>
       <c r="B4" t="s">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>285</v>
+        <v>311</v>
       </c>
       <c r="E4" t="s">
         <v>130</v>
@@ -4199,10 +4654,10 @@
         <v>179</v>
       </c>
       <c r="C5" t="s">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="D5" t="s">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="E5" t="s">
         <v>130</v>
@@ -4219,10 +4674,10 @@
         <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>282</v>
+        <v>308</v>
       </c>
       <c r="D6" t="s">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="E6" t="s">
         <v>130</v>
@@ -4266,13 +4721,13 @@
         <v>21330051420317</v>
       </c>
       <c r="B2" t="s">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="C2" t="s">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="D2" t="s">
-        <v>293</v>
+        <v>319</v>
       </c>
       <c r="E2" t="s">
         <v>138</v>
@@ -4286,13 +4741,13 @@
         <v>21330051420317</v>
       </c>
       <c r="B3" t="s">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="C3" t="s">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="D3" t="s">
-        <v>293</v>
+        <v>319</v>
       </c>
       <c r="E3" t="s">
         <v>139</v>
@@ -4309,10 +4764,10 @@
         <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>291</v>
+        <v>317</v>
       </c>
       <c r="D4" t="s">
-        <v>294</v>
+        <v>320</v>
       </c>
       <c r="E4" t="s">
         <v>168</v>
@@ -4329,10 +4784,10 @@
         <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>291</v>
+        <v>317</v>
       </c>
       <c r="D5" t="s">
-        <v>294</v>
+        <v>320</v>
       </c>
       <c r="E5" t="s">
         <v>140</v>
@@ -4346,13 +4801,13 @@
         <v>22330051920233</v>
       </c>
       <c r="B6" t="s">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="C6" t="s">
-        <v>292</v>
+        <v>318</v>
       </c>
       <c r="D6" t="s">
-        <v>295</v>
+        <v>321</v>
       </c>
       <c r="E6" t="s">
         <v>139</v>
@@ -4366,13 +4821,13 @@
         <v>22330051920236</v>
       </c>
       <c r="B7" t="s">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="C7" t="s">
         <v>179</v>
       </c>
       <c r="D7" t="s">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="E7" t="s">
         <v>138</v>
@@ -4386,13 +4841,13 @@
         <v>22330051920236</v>
       </c>
       <c r="B8" t="s">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="C8" t="s">
         <v>179</v>
       </c>
       <c r="D8" t="s">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="E8" t="s">
         <v>130</v>
@@ -4412,7 +4867,7 @@
         <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>297</v>
+        <v>323</v>
       </c>
       <c r="E9" t="s">
         <v>138</v>
@@ -4459,10 +4914,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>298</v>
+        <v>324</v>
       </c>
       <c r="D2" t="s">
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="E2" t="s">
         <v>130</v>
@@ -4479,10 +4934,10 @@
         <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>299</v>
+        <v>325</v>
       </c>
       <c r="D3" t="s">
-        <v>301</v>
+        <v>327</v>
       </c>
       <c r="E3" t="s">
         <v>138</v>
@@ -4499,10 +4954,10 @@
         <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>299</v>
+        <v>325</v>
       </c>
       <c r="D4" t="s">
-        <v>301</v>
+        <v>327</v>
       </c>
       <c r="E4" t="s">
         <v>130</v>
@@ -4522,7 +4977,7 @@
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="E5" t="s">
         <v>130</v>
@@ -4566,13 +5021,13 @@
         <v>21330051920002</v>
       </c>
       <c r="B2" t="s">
-        <v>294</v>
+        <v>320</v>
       </c>
       <c r="C2" t="s">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="D2" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="E2" t="s">
         <v>130</v>
@@ -4592,7 +5047,7 @@
         <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>307</v>
+        <v>333</v>
       </c>
       <c r="E3" t="s">
         <v>138</v>
@@ -4612,7 +5067,7 @@
         <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>307</v>
+        <v>333</v>
       </c>
       <c r="E4" t="s">
         <v>130</v>
@@ -4626,13 +5081,13 @@
         <v>22330051920222</v>
       </c>
       <c r="B5" t="s">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="C5" t="s">
-        <v>305</v>
+        <v>331</v>
       </c>
       <c r="D5" t="s">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="E5" t="s">
         <v>138</v>
@@ -4652,7 +5107,7 @@
         <v>146</v>
       </c>
       <c r="D6" t="s">
-        <v>309</v>
+        <v>335</v>
       </c>
       <c r="E6" t="s">
         <v>130</v>
@@ -4726,13 +5181,13 @@
         <v>20330051920049</v>
       </c>
       <c r="B2" t="s">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="C2" t="s">
         <v>126</v>
       </c>
       <c r="D2" t="s">
-        <v>312</v>
+        <v>338</v>
       </c>
       <c r="E2" t="s">
         <v>177</v>
@@ -4746,13 +5201,13 @@
         <v>20330051920366</v>
       </c>
       <c r="B3" t="s">
-        <v>311</v>
+        <v>337</v>
       </c>
       <c r="C3" t="s">
         <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="E3" t="s">
         <v>177</v>
@@ -4766,13 +5221,13 @@
         <v>20330051920366</v>
       </c>
       <c r="B4" t="s">
-        <v>311</v>
+        <v>337</v>
       </c>
       <c r="C4" t="s">
         <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="E4" t="s">
         <v>195</v>
@@ -4786,13 +5241,13 @@
         <v>20330051920367</v>
       </c>
       <c r="B5" t="s">
-        <v>311</v>
+        <v>337</v>
       </c>
       <c r="C5" t="s">
         <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="E5" t="s">
         <v>195</v>
@@ -4806,13 +5261,13 @@
         <v>20330051920367</v>
       </c>
       <c r="B6" t="s">
-        <v>311</v>
+        <v>337</v>
       </c>
       <c r="C6" t="s">
         <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="E6" t="s">
         <v>177</v>
@@ -4832,7 +5287,7 @@
         <v>179</v>
       </c>
       <c r="D7" t="s">
-        <v>315</v>
+        <v>341</v>
       </c>
       <c r="E7" t="s">
         <v>177</v>
@@ -5089,10 +5544,10 @@
         <v>124</v>
       </c>
       <c r="C2" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="D2" t="s">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="E2" t="s">
         <v>177</v>
@@ -5112,7 +5567,7 @@
         <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="E3" t="s">
         <v>193</v>
@@ -5126,13 +5581,13 @@
         <v>21330051920075</v>
       </c>
       <c r="B4" t="s">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="E4" t="s">
         <v>193</v>
@@ -5152,7 +5607,7 @@
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>323</v>
+        <v>348</v>
       </c>
       <c r="E5" t="s">
         <v>177</v>
@@ -5186,13 +5641,13 @@
         <v>21330051920103</v>
       </c>
       <c r="B7" t="s">
-        <v>317</v>
+        <v>343</v>
       </c>
       <c r="C7" t="s">
         <v>179</v>
       </c>
       <c r="D7" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="E7" t="s">
         <v>177</v>
@@ -5206,13 +5661,13 @@
         <v>21330051920109</v>
       </c>
       <c r="B8" t="s">
-        <v>318</v>
+        <v>226</v>
       </c>
       <c r="C8" t="s">
         <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="E8" t="s">
         <v>177</v>
@@ -5226,16 +5681,16 @@
         <v>21330051920109</v>
       </c>
       <c r="B9" t="s">
-        <v>318</v>
+        <v>226</v>
       </c>
       <c r="C9" t="s">
         <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="E9" t="s">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5252,7 +5707,7 @@
         <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="E10" t="s">
         <v>177</v>
@@ -5272,10 +5727,10 @@
         <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="E11" t="s">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -5322,10 +5777,10 @@
         <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>328</v>
+        <v>353</v>
       </c>
       <c r="E2" t="s">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5345,7 +5800,7 @@
         <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5406,16 +5861,16 @@
         <v>21330051920059</v>
       </c>
       <c r="B2" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="C2" t="s">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="D2" t="s">
         <v>152</v>
       </c>
       <c r="E2" t="s">
-        <v>331</v>
+        <v>356</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5456,13 +5911,13 @@
         <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C2" t="s">
         <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>332</v>
+        <v>357</v>
       </c>
       <c r="E2" t="s">
         <v>177</v>
@@ -5482,7 +5937,7 @@
         <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>333</v>
+        <v>358</v>
       </c>
       <c r="E3" t="s">
         <v>193</v>
@@ -5502,7 +5957,7 @@
         <v>106</v>
       </c>
       <c r="D4" t="s">
-        <v>334</v>
+        <v>359</v>
       </c>
       <c r="E4" t="s">
         <v>176</v>
@@ -5522,7 +5977,7 @@
         <v>106</v>
       </c>
       <c r="D5" t="s">
-        <v>334</v>
+        <v>359</v>
       </c>
       <c r="E5" t="s">
         <v>193</v>

--- a/Rescatables20231.xlsx
+++ b/Rescatables20231.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="356">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -660,6 +660,9 @@
     <t>CARRERA</t>
   </si>
   <si>
+    <t>VILLA</t>
+  </si>
+  <si>
     <t>CIRUELO</t>
   </si>
   <si>
@@ -693,6 +696,9 @@
     <t>ROBBIE ALONSO</t>
   </si>
   <si>
+    <t>ALEX URIEL</t>
+  </si>
+  <si>
     <t>SABDY</t>
   </si>
   <si>
@@ -738,9 +744,6 @@
     <t>BERMUDEZ</t>
   </si>
   <si>
-    <t>VILLA</t>
-  </si>
-  <si>
     <t>FERRER</t>
   </si>
   <si>
@@ -858,9 +861,6 @@
     <t>TZITZIHUA</t>
   </si>
   <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
   </si>
   <si>
@@ -885,9 +885,6 @@
     <t>DIANA LAURA</t>
   </si>
   <si>
-    <t>AIDE SCARLET</t>
-  </si>
-  <si>
     <t>KARINA MONSERRATH</t>
   </si>
   <si>
@@ -1108,15 +1105,6 @@
   </si>
   <si>
     <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>SUPERVISA EL CUMPLIMIENTO DE LAS MEDIDAS DE HIGIENE Y SEGURIDAD EN LA ORGANIZACIÓN</t>
   </si>
   <si>
     <t>PEDRO ANGEL</t>
@@ -2423,7 +2411,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2488,16 +2476,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920100</v>
+        <v>21330051920203</v>
       </c>
       <c r="B4" t="s">
-        <v>183</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E4" t="s">
         <v>193</v>
@@ -2508,19 +2496,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920203</v>
+        <v>21330051920213</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D5" t="s">
-        <v>191</v>
+        <v>142</v>
       </c>
       <c r="E5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2528,41 +2516,21 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920213</v>
+        <v>21330051920386</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>184</v>
       </c>
       <c r="C6" t="s">
-        <v>188</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>142</v>
+        <v>192</v>
       </c>
       <c r="E6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920386</v>
-      </c>
-      <c r="B7" t="s">
-        <v>184</v>
-      </c>
-      <c r="C7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" t="s">
-        <v>192</v>
-      </c>
-      <c r="E7" t="s">
-        <v>195</v>
-      </c>
-      <c r="F7">
         <v>5</v>
       </c>
     </row>
@@ -2603,7 +2571,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2637,7 +2605,7 @@
         <v>199</v>
       </c>
       <c r="D2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E2" t="s">
         <v>35</v>
@@ -2657,10 +2625,10 @@
         <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2677,10 +2645,10 @@
         <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2697,10 +2665,10 @@
         <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2720,7 +2688,7 @@
         <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2737,10 +2705,10 @@
         <v>201</v>
       </c>
       <c r="D7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E7" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2757,10 +2725,10 @@
         <v>201</v>
       </c>
       <c r="D8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2777,10 +2745,10 @@
         <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2797,10 +2765,10 @@
         <v>202</v>
       </c>
       <c r="D10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2817,10 +2785,10 @@
         <v>202</v>
       </c>
       <c r="D11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E11" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2837,7 +2805,7 @@
         <v>203</v>
       </c>
       <c r="D12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E12" t="s">
         <v>35</v>
@@ -2857,10 +2825,10 @@
         <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E13" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -2877,10 +2845,10 @@
         <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E14" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -2897,7 +2865,7 @@
         <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E15" t="s">
         <v>35</v>
@@ -2917,10 +2885,10 @@
         <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E16" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -2928,21 +2896,61 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>23330051920329</v>
+        <v>23330051920212</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
         <v>204</v>
       </c>
       <c r="D17" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E17" t="s">
+        <v>219</v>
+      </c>
+      <c r="F17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>23330051920212</v>
+      </c>
+      <c r="B18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" t="s">
+        <v>204</v>
+      </c>
+      <c r="D18" t="s">
         <v>216</v>
       </c>
-      <c r="F17">
+      <c r="E18" t="s">
+        <v>218</v>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>23330051920329</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>205</v>
+      </c>
+      <c r="D19" t="s">
+        <v>217</v>
+      </c>
+      <c r="E19" t="s">
+        <v>218</v>
+      </c>
+      <c r="F19">
         <v>5</v>
       </c>
     </row>
@@ -3177,10 +3185,10 @@
         <v>149</v>
       </c>
       <c r="D2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3191,16 +3199,16 @@
         <v>23330051920213</v>
       </c>
       <c r="B3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3211,16 +3219,16 @@
         <v>23330051920215</v>
       </c>
       <c r="B4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C4" t="s">
         <v>172</v>
       </c>
       <c r="D4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3231,13 +3239,13 @@
         <v>23330051920215</v>
       </c>
       <c r="B5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C5" t="s">
         <v>172</v>
       </c>
       <c r="D5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E5" t="s">
         <v>35</v>
@@ -3257,10 +3265,10 @@
         <v>203</v>
       </c>
       <c r="D6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3274,13 +3282,13 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D7" t="s">
         <v>123</v>
       </c>
       <c r="E7" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3294,13 +3302,13 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D8" t="s">
         <v>123</v>
       </c>
       <c r="E8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3314,13 +3322,13 @@
         <v>187</v>
       </c>
       <c r="C9" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="D9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3334,13 +3342,13 @@
         <v>124</v>
       </c>
       <c r="C10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3351,16 +3359,16 @@
         <v>23330051920240</v>
       </c>
       <c r="B11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3371,16 +3379,16 @@
         <v>23330051920242</v>
       </c>
       <c r="B12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E12" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3391,16 +3399,16 @@
         <v>23330051920242</v>
       </c>
       <c r="B13" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E13" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -3411,16 +3419,16 @@
         <v>23330051920244</v>
       </c>
       <c r="B14" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -3431,13 +3439,13 @@
         <v>23330051920248</v>
       </c>
       <c r="B15" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C15" t="s">
         <v>199</v>
       </c>
       <c r="D15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E15" t="s">
         <v>35</v>
@@ -3451,16 +3459,16 @@
         <v>23330051920248</v>
       </c>
       <c r="B16" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C16" t="s">
         <v>199</v>
       </c>
       <c r="D16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -3477,10 +3485,10 @@
         <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E17" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -3497,10 +3505,10 @@
         <v>179</v>
       </c>
       <c r="D18" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -3514,13 +3522,13 @@
         <v>179</v>
       </c>
       <c r="C19" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D19" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E19" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -3531,16 +3539,16 @@
         <v>23330051920257</v>
       </c>
       <c r="B20" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C20" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D20" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E20" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -3551,16 +3559,16 @@
         <v>23330051920260</v>
       </c>
       <c r="B21" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C21" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D21" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E21" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -3571,7 +3579,7 @@
         <v>23330051920270</v>
       </c>
       <c r="B22" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C22" t="s">
         <v>39</v>
@@ -3580,7 +3588,7 @@
         <v>85</v>
       </c>
       <c r="E22" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F22">
         <v>5</v>
@@ -3597,10 +3605,10 @@
         <v>16</v>
       </c>
       <c r="D23" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F23">
         <v>5</v>
@@ -3614,13 +3622,13 @@
         <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D24" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E24" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -3637,10 +3645,10 @@
         <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E25" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -3651,16 +3659,16 @@
         <v>23330051920277</v>
       </c>
       <c r="B26" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C26" t="s">
         <v>106</v>
       </c>
       <c r="D26" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E26" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F26">
         <v>5</v>
@@ -3671,16 +3679,16 @@
         <v>23330051920280</v>
       </c>
       <c r="B27" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C27" t="s">
         <v>64</v>
       </c>
       <c r="D27" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E27" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F27">
         <v>5</v>
@@ -3691,16 +3699,16 @@
         <v>23330051920280</v>
       </c>
       <c r="B28" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C28" t="s">
         <v>64</v>
       </c>
       <c r="D28" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F28">
         <v>5</v>
@@ -3714,13 +3722,13 @@
         <v>64</v>
       </c>
       <c r="C29" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D29" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E29" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F29">
         <v>5</v>
@@ -3734,10 +3742,10 @@
         <v>64</v>
       </c>
       <c r="C30" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D30" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E30" t="s">
         <v>35</v>
@@ -3757,10 +3765,10 @@
         <v>20</v>
       </c>
       <c r="D31" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E31" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F31">
         <v>5</v>
@@ -3777,10 +3785,10 @@
         <v>179</v>
       </c>
       <c r="D32" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F32">
         <v>5</v>
@@ -3797,10 +3805,10 @@
         <v>39</v>
       </c>
       <c r="D33" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E33" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F33">
         <v>5</v>
@@ -3817,10 +3825,10 @@
         <v>39</v>
       </c>
       <c r="D34" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E34" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F34">
         <v>5</v>
@@ -3833,7 +3841,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3861,16 +3869,16 @@
         <v>23330051920220</v>
       </c>
       <c r="B2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D2" t="s">
         <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3904,13 +3912,13 @@
         <v>149</v>
       </c>
       <c r="C4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D4" t="s">
         <v>273</v>
       </c>
       <c r="E4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3924,13 +3932,13 @@
         <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D5" t="s">
         <v>274</v>
       </c>
       <c r="E5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3941,7 +3949,7 @@
         <v>23330051920241</v>
       </c>
       <c r="B6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -3961,7 +3969,7 @@
         <v>23330051920241</v>
       </c>
       <c r="B7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -3970,7 +3978,7 @@
         <v>275</v>
       </c>
       <c r="E7" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3990,7 +3998,7 @@
         <v>276</v>
       </c>
       <c r="E8" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4024,7 +4032,7 @@
         <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D10" t="s">
         <v>277</v>
@@ -4041,7 +4049,7 @@
         <v>23330051920249</v>
       </c>
       <c r="B11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C11" t="s">
         <v>45</v>
@@ -4058,19 +4066,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>23330051920258</v>
+        <v>23330051920264</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>267</v>
       </c>
       <c r="C12" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D12" t="s">
         <v>279</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>218</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -4078,19 +4086,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>23330051920264</v>
+        <v>23330051920267</v>
       </c>
       <c r="B13" t="s">
-        <v>266</v>
+        <v>150</v>
       </c>
       <c r="C13" t="s">
-        <v>271</v>
+        <v>7</v>
       </c>
       <c r="D13" t="s">
         <v>280</v>
       </c>
       <c r="E13" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -4107,10 +4115,10 @@
         <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E14" t="s">
-        <v>35</v>
+        <v>218</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -4118,41 +4126,21 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>23330051920267</v>
+        <v>23330051920271</v>
       </c>
       <c r="B15" t="s">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="C15" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
         <v>281</v>
       </c>
       <c r="E15" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>23330051920271</v>
-      </c>
-      <c r="B16" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" t="s">
-        <v>282</v>
-      </c>
-      <c r="E16" t="s">
-        <v>216</v>
-      </c>
-      <c r="F16">
         <v>5</v>
       </c>
     </row>
@@ -4191,16 +4179,16 @@
         <v>23330051920282</v>
       </c>
       <c r="B2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D2" t="s">
         <v>289</v>
       </c>
-      <c r="D2" t="s">
-        <v>290</v>
-      </c>
       <c r="E2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4211,16 +4199,16 @@
         <v>23330051920285</v>
       </c>
       <c r="B3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C3" t="s">
         <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4237,10 +4225,10 @@
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4251,13 +4239,13 @@
         <v>23330051920308</v>
       </c>
       <c r="B5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E5" t="s">
         <v>35</v>
@@ -4271,16 +4259,16 @@
         <v>23330051920310</v>
       </c>
       <c r="B6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C6" t="s">
         <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4297,7 +4285,7 @@
         <v>149</v>
       </c>
       <c r="D7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E7" t="s">
         <v>35</v>
@@ -4311,13 +4299,13 @@
         <v>23330051920347</v>
       </c>
       <c r="B8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C8" t="s">
         <v>171</v>
       </c>
       <c r="D8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E8" t="s">
         <v>33</v>
@@ -4331,16 +4319,16 @@
         <v>23330051920347</v>
       </c>
       <c r="B9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C9" t="s">
         <v>171</v>
       </c>
       <c r="D9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E9" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4371,16 +4359,16 @@
         <v>23330051920356</v>
       </c>
       <c r="B11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E11" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -4397,10 +4385,10 @@
         <v>179</v>
       </c>
       <c r="D12" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E12" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -4444,13 +4432,13 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4464,13 +4452,13 @@
         <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4484,10 +4472,10 @@
         <v>147</v>
       </c>
       <c r="C4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E4" t="s">
         <v>35</v>
@@ -4504,13 +4492,13 @@
         <v>147</v>
       </c>
       <c r="C5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4524,13 +4512,13 @@
         <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4547,10 +4535,10 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E7" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4597,7 +4585,7 @@
         <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E2" t="s">
         <v>130</v>
@@ -4614,10 +4602,10 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E3" t="s">
         <v>130</v>
@@ -4631,13 +4619,13 @@
         <v>22330051920363</v>
       </c>
       <c r="B4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E4" t="s">
         <v>130</v>
@@ -4654,10 +4642,10 @@
         <v>179</v>
       </c>
       <c r="C5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E5" t="s">
         <v>130</v>
@@ -4674,10 +4662,10 @@
         <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E6" t="s">
         <v>130</v>
@@ -4721,13 +4709,13 @@
         <v>21330051420317</v>
       </c>
       <c r="B2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E2" t="s">
         <v>138</v>
@@ -4741,13 +4729,13 @@
         <v>21330051420317</v>
       </c>
       <c r="B3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E3" t="s">
         <v>139</v>
@@ -4764,10 +4752,10 @@
         <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E4" t="s">
         <v>168</v>
@@ -4784,10 +4772,10 @@
         <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E5" t="s">
         <v>140</v>
@@ -4801,13 +4789,13 @@
         <v>22330051920233</v>
       </c>
       <c r="B6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E6" t="s">
         <v>139</v>
@@ -4821,13 +4809,13 @@
         <v>22330051920236</v>
       </c>
       <c r="B7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C7" t="s">
         <v>179</v>
       </c>
       <c r="D7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E7" t="s">
         <v>138</v>
@@ -4841,13 +4829,13 @@
         <v>22330051920236</v>
       </c>
       <c r="B8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C8" t="s">
         <v>179</v>
       </c>
       <c r="D8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E8" t="s">
         <v>130</v>
@@ -4867,7 +4855,7 @@
         <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E9" t="s">
         <v>138</v>
@@ -4914,10 +4902,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E2" t="s">
         <v>130</v>
@@ -4934,10 +4922,10 @@
         <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E3" t="s">
         <v>138</v>
@@ -4954,10 +4942,10 @@
         <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E4" t="s">
         <v>130</v>
@@ -4977,7 +4965,7 @@
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E5" t="s">
         <v>130</v>
@@ -5021,13 +5009,13 @@
         <v>21330051920002</v>
       </c>
       <c r="B2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E2" t="s">
         <v>130</v>
@@ -5047,7 +5035,7 @@
         <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E3" t="s">
         <v>138</v>
@@ -5067,7 +5055,7 @@
         <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E4" t="s">
         <v>130</v>
@@ -5081,13 +5069,13 @@
         <v>22330051920222</v>
       </c>
       <c r="B5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E5" t="s">
         <v>138</v>
@@ -5107,7 +5095,7 @@
         <v>146</v>
       </c>
       <c r="D6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E6" t="s">
         <v>130</v>
@@ -5181,13 +5169,13 @@
         <v>20330051920049</v>
       </c>
       <c r="B2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C2" t="s">
         <v>126</v>
       </c>
       <c r="D2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E2" t="s">
         <v>177</v>
@@ -5201,13 +5189,13 @@
         <v>20330051920366</v>
       </c>
       <c r="B3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C3" t="s">
         <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E3" t="s">
         <v>177</v>
@@ -5221,13 +5209,13 @@
         <v>20330051920366</v>
       </c>
       <c r="B4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C4" t="s">
         <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E4" t="s">
         <v>195</v>
@@ -5241,13 +5229,13 @@
         <v>20330051920367</v>
       </c>
       <c r="B5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C5" t="s">
         <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E5" t="s">
         <v>195</v>
@@ -5261,13 +5249,13 @@
         <v>20330051920367</v>
       </c>
       <c r="B6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C6" t="s">
         <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E6" t="s">
         <v>177</v>
@@ -5287,7 +5275,7 @@
         <v>179</v>
       </c>
       <c r="D7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E7" t="s">
         <v>177</v>
@@ -5544,10 +5532,10 @@
         <v>124</v>
       </c>
       <c r="C2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D2" t="s">
         <v>344</v>
-      </c>
-      <c r="D2" t="s">
-        <v>345</v>
       </c>
       <c r="E2" t="s">
         <v>177</v>
@@ -5567,7 +5555,7 @@
         <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E3" t="s">
         <v>193</v>
@@ -5581,13 +5569,13 @@
         <v>21330051920075</v>
       </c>
       <c r="B4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E4" t="s">
         <v>193</v>
@@ -5607,7 +5595,7 @@
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E5" t="s">
         <v>177</v>
@@ -5641,13 +5629,13 @@
         <v>21330051920103</v>
       </c>
       <c r="B7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C7" t="s">
         <v>179</v>
       </c>
       <c r="D7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E7" t="s">
         <v>177</v>
@@ -5661,13 +5649,13 @@
         <v>21330051920109</v>
       </c>
       <c r="B8" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C8" t="s">
         <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E8" t="s">
         <v>177</v>
@@ -5681,16 +5669,16 @@
         <v>21330051920109</v>
       </c>
       <c r="B9" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C9" t="s">
         <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5707,7 +5695,7 @@
         <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E10" t="s">
         <v>177</v>
@@ -5727,10 +5715,10 @@
         <v>36</v>
       </c>
       <c r="D11" t="s">
+        <v>350</v>
+      </c>
+      <c r="E11" t="s">
         <v>351</v>
-      </c>
-      <c r="E11" t="s">
-        <v>352</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -5777,10 +5765,10 @@
         <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5800,7 +5788,7 @@
         <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5833,7 +5821,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5853,26 +5841,6 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920059</v>
-      </c>
-      <c r="B2" t="s">
-        <v>354</v>
-      </c>
-      <c r="C2" t="s">
-        <v>355</v>
-      </c>
-      <c r="D2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E2" t="s">
-        <v>356</v>
-      </c>
-      <c r="F2">
         <v>5</v>
       </c>
     </row>
@@ -5911,13 +5879,13 @@
         <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C2" t="s">
         <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="E2" t="s">
         <v>177</v>
@@ -5937,7 +5905,7 @@
         <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="E3" t="s">
         <v>193</v>
@@ -5957,7 +5925,7 @@
         <v>106</v>
       </c>
       <c r="D4" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E4" t="s">
         <v>176</v>
@@ -5977,7 +5945,7 @@
         <v>106</v>
       </c>
       <c r="D5" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E5" t="s">
         <v>193</v>
